--- a/sdtm-findings-graph/machine_actionable/Measurement_Findings.xlsx
+++ b/sdtm-findings-graph/machine_actionable/Measurement_Findings.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test_Identity'!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Measurement_Specs'!$A$1:$AL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Measurement_Specs'!$A$1:$BN$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-26 12:00</t>
+          <t>Generated: 2026-04-30 22:51</t>
         </is>
       </c>
     </row>
@@ -627,14 +627,14 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSSs yet — it appears only in Test_Identity. Pin columns included only</t>
+          <t xml:space="preserve">  DSSs yet — it appears only in Test_Identity. Slot columns included only</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  when the pin actually fires on the scope subset (data-driven shape).</t>
+          <t xml:space="preserve">  when the slot actually fires on the scope subset — pin or value_list (data-driven shape).</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Yellow = COSMoS-side columns (BC, DSS, pin pivot).</t>
+          <t>Yellow = COSMoS-side columns (BC, DSS, slot pivot — pin and value_list).</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL129"/>
+  <dimension ref="A1:BN129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25386,21 +25386,49 @@
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
     <col width="18" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="26" customWidth="1" min="37" max="37"/>
-    <col width="50" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="18" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
+    <col width="18" customWidth="1" min="53" max="53"/>
+    <col width="18" customWidth="1" min="54" max="54"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="56" max="56"/>
+    <col width="22" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="14" customWidth="1" min="59" max="59"/>
+    <col width="18" customWidth="1" min="60" max="60"/>
+    <col width="18" customWidth="1" min="61" max="61"/>
+    <col width="18" customWidth="1" min="62" max="62"/>
+    <col width="18" customWidth="1" min="63" max="63"/>
+    <col width="14" customWidth="1" min="64" max="64"/>
+    <col width="26" customWidth="1" min="65" max="65"/>
+    <col width="50" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25521,75 +25549,215 @@
       </c>
       <c r="X1" s="6" t="inlineStr">
         <is>
+          <t>METHOD_value_list</t>
+        </is>
+      </c>
+      <c r="Y1" s="6" t="inlineStr">
+        <is>
+          <t>METHOD_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="Z1" s="6" t="inlineStr">
+        <is>
+          <t>ORRES_value</t>
+        </is>
+      </c>
+      <c r="AA1" s="6" t="inlineStr">
+        <is>
+          <t>ORRES_ncit</t>
+        </is>
+      </c>
+      <c r="AB1" s="6" t="inlineStr">
+        <is>
+          <t>ORRES_codelist</t>
+        </is>
+      </c>
+      <c r="AC1" s="6" t="inlineStr">
+        <is>
+          <t>ORRES_value_list</t>
+        </is>
+      </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>ORRES_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>STRESC_value</t>
+        </is>
+      </c>
+      <c r="AF1" s="6" t="inlineStr">
+        <is>
+          <t>STRESC_ncit</t>
+        </is>
+      </c>
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>STRESC_codelist</t>
+        </is>
+      </c>
+      <c r="AH1" s="6" t="inlineStr">
+        <is>
+          <t>STRESC_value_list</t>
+        </is>
+      </c>
+      <c r="AI1" s="6" t="inlineStr">
+        <is>
+          <t>STRESC_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="AJ1" s="6" t="inlineStr">
+        <is>
+          <t>STRESN_value_list</t>
+        </is>
+      </c>
+      <c r="AK1" s="6" t="inlineStr">
+        <is>
+          <t>STRESN_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="AL1" s="6" t="inlineStr">
+        <is>
           <t>ORRESU_value</t>
         </is>
       </c>
-      <c r="Y1" s="6" t="inlineStr">
+      <c r="AM1" s="6" t="inlineStr">
         <is>
           <t>ORRESU_ncit</t>
         </is>
       </c>
-      <c r="Z1" s="6" t="inlineStr">
+      <c r="AN1" s="6" t="inlineStr">
         <is>
           <t>ORRESU_codelist</t>
         </is>
       </c>
-      <c r="AA1" s="6" t="inlineStr">
+      <c r="AO1" s="6" t="inlineStr">
+        <is>
+          <t>ORRESU_value_list</t>
+        </is>
+      </c>
+      <c r="AP1" s="6" t="inlineStr">
+        <is>
+          <t>ORRESU_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="AQ1" s="6" t="inlineStr">
         <is>
           <t>STRESU_value</t>
         </is>
       </c>
-      <c r="AB1" s="6" t="inlineStr">
+      <c r="AR1" s="6" t="inlineStr">
         <is>
           <t>STRESU_ncit</t>
         </is>
       </c>
-      <c r="AC1" s="6" t="inlineStr">
+      <c r="AS1" s="6" t="inlineStr">
         <is>
           <t>STRESU_codelist</t>
         </is>
       </c>
-      <c r="AD1" s="6" t="inlineStr">
+      <c r="AT1" s="6" t="inlineStr">
+        <is>
+          <t>STRESU_value_list</t>
+        </is>
+      </c>
+      <c r="AU1" s="6" t="inlineStr">
+        <is>
+          <t>STRESU_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="AV1" s="6" t="inlineStr">
         <is>
           <t>LOC_value</t>
         </is>
       </c>
-      <c r="AE1" s="6" t="inlineStr">
+      <c r="AW1" s="6" t="inlineStr">
         <is>
           <t>LOC_ncit</t>
         </is>
       </c>
-      <c r="AF1" s="6" t="inlineStr">
+      <c r="AX1" s="6" t="inlineStr">
         <is>
           <t>LOC_codelist</t>
         </is>
       </c>
-      <c r="AG1" s="6" t="inlineStr">
+      <c r="AY1" s="6" t="inlineStr">
+        <is>
+          <t>LOC_value_list</t>
+        </is>
+      </c>
+      <c r="AZ1" s="6" t="inlineStr">
+        <is>
+          <t>LOC_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="BA1" s="6" t="inlineStr">
+        <is>
+          <t>LAT_value_list</t>
+        </is>
+      </c>
+      <c r="BB1" s="6" t="inlineStr">
+        <is>
+          <t>LAT_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="BC1" s="6" t="inlineStr">
+        <is>
+          <t>POS_value_list</t>
+        </is>
+      </c>
+      <c r="BD1" s="6" t="inlineStr">
+        <is>
+          <t>POS_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="BE1" s="6" t="inlineStr">
         <is>
           <t>EVAL_value</t>
         </is>
       </c>
-      <c r="AH1" s="6" t="inlineStr">
+      <c r="BF1" s="6" t="inlineStr">
         <is>
           <t>EVAL_ncit</t>
         </is>
       </c>
-      <c r="AI1" s="6" t="inlineStr">
+      <c r="BG1" s="6" t="inlineStr">
         <is>
           <t>EVAL_codelist</t>
         </is>
       </c>
-      <c r="AJ1" s="6" t="inlineStr">
+      <c r="BH1" s="6" t="inlineStr">
+        <is>
+          <t>EVAL_value_list</t>
+        </is>
+      </c>
+      <c r="BI1" s="6" t="inlineStr">
+        <is>
+          <t>EVAL_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="BJ1" s="6" t="inlineStr">
+        <is>
+          <t>EVALID_value_list</t>
+        </is>
+      </c>
+      <c r="BK1" s="6" t="inlineStr">
+        <is>
+          <t>EVALID_value_list_ncit</t>
+        </is>
+      </c>
+      <c r="BL1" s="6" t="inlineStr">
         <is>
           <t>LOINC_DSS</t>
         </is>
       </c>
-      <c r="AK1" s="6" t="inlineStr">
+      <c r="BM1" s="6" t="inlineStr">
         <is>
           <t>LOINC_BC</t>
         </is>
       </c>
-      <c r="AL1" s="6" t="inlineStr">
+      <c r="BN1" s="6" t="inlineStr">
         <is>
           <t>Allowed_Units</t>
         </is>
@@ -25695,57 +25863,93 @@
       <c r="U2" s="7" t="n"/>
       <c r="V2" s="7" t="n"/>
       <c r="W2" s="7" t="n"/>
-      <c r="X2" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="Y2" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="Z2" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="AB2" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="AC2" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AD2" s="7" t="inlineStr">
-        <is>
-          <t>HIP</t>
-        </is>
-      </c>
-      <c r="AE2" s="7" t="inlineStr">
-        <is>
-          <t>C64193</t>
-        </is>
-      </c>
-      <c r="AF2" s="7" t="inlineStr">
-        <is>
-          <t>LOC</t>
-        </is>
-      </c>
+      <c r="X2" s="7" t="n"/>
+      <c r="Y2" s="7" t="n"/>
+      <c r="Z2" s="7" t="n"/>
+      <c r="AA2" s="7" t="n"/>
+      <c r="AB2" s="7" t="n"/>
+      <c r="AC2" s="7" t="n"/>
+      <c r="AD2" s="7" t="n"/>
+      <c r="AE2" s="7" t="n"/>
+      <c r="AF2" s="7" t="n"/>
       <c r="AG2" s="7" t="n"/>
       <c r="AH2" s="7" t="n"/>
       <c r="AI2" s="7" t="n"/>
       <c r="AJ2" s="7" t="n"/>
       <c r="AK2" s="7" t="n"/>
-      <c r="AL2" s="7" t="n"/>
+      <c r="AL2" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AM2" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AN2" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO2" s="7" t="n"/>
+      <c r="AP2" s="7" t="n"/>
+      <c r="AQ2" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AR2" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AS2" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT2" s="7" t="n"/>
+      <c r="AU2" s="7" t="n"/>
+      <c r="AV2" s="7" t="inlineStr">
+        <is>
+          <t>HIP</t>
+        </is>
+      </c>
+      <c r="AW2" s="7" t="inlineStr">
+        <is>
+          <t>C64193</t>
+        </is>
+      </c>
+      <c r="AX2" s="7" t="inlineStr">
+        <is>
+          <t>LOC</t>
+        </is>
+      </c>
+      <c r="AY2" s="7" t="n"/>
+      <c r="AZ2" s="7" t="n"/>
+      <c r="BA2" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB2" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC2" s="7" t="n"/>
+      <c r="BD2" s="7" t="n"/>
+      <c r="BE2" s="7" t="n"/>
+      <c r="BF2" s="7" t="n"/>
+      <c r="BG2" s="7" t="n"/>
+      <c r="BH2" s="7" t="n"/>
+      <c r="BI2" s="7" t="n"/>
+      <c r="BJ2" s="7" t="n"/>
+      <c r="BK2" s="7" t="n"/>
+      <c r="BL2" s="7" t="n"/>
+      <c r="BM2" s="7" t="n"/>
+      <c r="BN2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -25850,17 +26054,9 @@
       <c r="X3" s="7" t="n"/>
       <c r="Y3" s="7" t="n"/>
       <c r="Z3" s="7" t="n"/>
-      <c r="AA3" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA3" s="7" t="n"/>
       <c r="AB3" s="7" t="n"/>
-      <c r="AC3" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC3" s="7" t="n"/>
       <c r="AD3" s="7" t="n"/>
       <c r="AE3" s="7" t="n"/>
       <c r="AF3" s="7" t="n"/>
@@ -25870,6 +26066,58 @@
       <c r="AJ3" s="7" t="n"/>
       <c r="AK3" s="7" t="n"/>
       <c r="AL3" s="7" t="n"/>
+      <c r="AM3" s="7" t="n"/>
+      <c r="AN3" s="7" t="n"/>
+      <c r="AO3" s="7" t="inlineStr">
+        <is>
+          <t>Kg;g;LB;oz</t>
+        </is>
+      </c>
+      <c r="AP3" s="7" t="inlineStr">
+        <is>
+          <t>;C48155;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AQ3" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR3" s="7" t="n"/>
+      <c r="AS3" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT3" s="7" t="n"/>
+      <c r="AU3" s="7" t="n"/>
+      <c r="AV3" s="7" t="n"/>
+      <c r="AW3" s="7" t="n"/>
+      <c r="AX3" s="7" t="n"/>
+      <c r="AY3" s="7" t="n"/>
+      <c r="AZ3" s="7" t="n"/>
+      <c r="BA3" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB3" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC3" s="7" t="n"/>
+      <c r="BD3" s="7" t="n"/>
+      <c r="BE3" s="7" t="n"/>
+      <c r="BF3" s="7" t="n"/>
+      <c r="BG3" s="7" t="n"/>
+      <c r="BH3" s="7" t="n"/>
+      <c r="BI3" s="7" t="n"/>
+      <c r="BJ3" s="7" t="n"/>
+      <c r="BK3" s="7" t="n"/>
+      <c r="BL3" s="7" t="n"/>
+      <c r="BM3" s="7" t="n"/>
+      <c r="BN3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -25971,57 +26219,93 @@
       <c r="U4" s="7" t="n"/>
       <c r="V4" s="7" t="n"/>
       <c r="W4" s="7" t="n"/>
-      <c r="X4" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="Y4" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="Z4" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA4" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="AB4" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="AC4" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AD4" s="7" t="inlineStr">
-        <is>
-          <t>HIP</t>
-        </is>
-      </c>
-      <c r="AE4" s="7" t="inlineStr">
-        <is>
-          <t>C64193</t>
-        </is>
-      </c>
-      <c r="AF4" s="7" t="inlineStr">
-        <is>
-          <t>LOC</t>
-        </is>
-      </c>
+      <c r="X4" s="7" t="n"/>
+      <c r="Y4" s="7" t="n"/>
+      <c r="Z4" s="7" t="n"/>
+      <c r="AA4" s="7" t="n"/>
+      <c r="AB4" s="7" t="n"/>
+      <c r="AC4" s="7" t="n"/>
+      <c r="AD4" s="7" t="n"/>
+      <c r="AE4" s="7" t="n"/>
+      <c r="AF4" s="7" t="n"/>
       <c r="AG4" s="7" t="n"/>
       <c r="AH4" s="7" t="n"/>
       <c r="AI4" s="7" t="n"/>
       <c r="AJ4" s="7" t="n"/>
       <c r="AK4" s="7" t="n"/>
-      <c r="AL4" s="7" t="n"/>
+      <c r="AL4" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AM4" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AN4" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO4" s="7" t="n"/>
+      <c r="AP4" s="7" t="n"/>
+      <c r="AQ4" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AR4" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AS4" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT4" s="7" t="n"/>
+      <c r="AU4" s="7" t="n"/>
+      <c r="AV4" s="7" t="inlineStr">
+        <is>
+          <t>HIP</t>
+        </is>
+      </c>
+      <c r="AW4" s="7" t="inlineStr">
+        <is>
+          <t>C64193</t>
+        </is>
+      </c>
+      <c r="AX4" s="7" t="inlineStr">
+        <is>
+          <t>LOC</t>
+        </is>
+      </c>
+      <c r="AY4" s="7" t="n"/>
+      <c r="AZ4" s="7" t="n"/>
+      <c r="BA4" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB4" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC4" s="7" t="n"/>
+      <c r="BD4" s="7" t="n"/>
+      <c r="BE4" s="7" t="n"/>
+      <c r="BF4" s="7" t="n"/>
+      <c r="BG4" s="7" t="n"/>
+      <c r="BH4" s="7" t="n"/>
+      <c r="BI4" s="7" t="n"/>
+      <c r="BJ4" s="7" t="n"/>
+      <c r="BK4" s="7" t="n"/>
+      <c r="BL4" s="7" t="n"/>
+      <c r="BM4" s="7" t="n"/>
+      <c r="BN4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -26126,17 +26410,9 @@
       <c r="X5" s="7" t="n"/>
       <c r="Y5" s="7" t="n"/>
       <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA5" s="7" t="n"/>
       <c r="AB5" s="7" t="n"/>
-      <c r="AC5" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC5" s="7" t="n"/>
       <c r="AD5" s="7" t="n"/>
       <c r="AE5" s="7" t="n"/>
       <c r="AF5" s="7" t="n"/>
@@ -26146,6 +26422,58 @@
       <c r="AJ5" s="7" t="n"/>
       <c r="AK5" s="7" t="n"/>
       <c r="AL5" s="7" t="n"/>
+      <c r="AM5" s="7" t="n"/>
+      <c r="AN5" s="7" t="n"/>
+      <c r="AO5" s="7" t="inlineStr">
+        <is>
+          <t>Kg;g</t>
+        </is>
+      </c>
+      <c r="AP5" s="7" t="inlineStr">
+        <is>
+          <t>;C48155</t>
+        </is>
+      </c>
+      <c r="AQ5" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR5" s="7" t="n"/>
+      <c r="AS5" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT5" s="7" t="n"/>
+      <c r="AU5" s="7" t="n"/>
+      <c r="AV5" s="7" t="n"/>
+      <c r="AW5" s="7" t="n"/>
+      <c r="AX5" s="7" t="n"/>
+      <c r="AY5" s="7" t="n"/>
+      <c r="AZ5" s="7" t="n"/>
+      <c r="BA5" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB5" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC5" s="7" t="n"/>
+      <c r="BD5" s="7" t="n"/>
+      <c r="BE5" s="7" t="n"/>
+      <c r="BF5" s="7" t="n"/>
+      <c r="BG5" s="7" t="n"/>
+      <c r="BH5" s="7" t="n"/>
+      <c r="BI5" s="7" t="n"/>
+      <c r="BJ5" s="7" t="n"/>
+      <c r="BK5" s="7" t="n"/>
+      <c r="BL5" s="7" t="n"/>
+      <c r="BM5" s="7" t="n"/>
+      <c r="BN5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -26250,21 +26578,9 @@
       <c r="X6" s="7" t="n"/>
       <c r="Y6" s="7" t="n"/>
       <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="7" t="inlineStr">
-        <is>
-          <t>g/cm2</t>
-        </is>
-      </c>
-      <c r="AB6" s="7" t="inlineStr">
-        <is>
-          <t>C71201</t>
-        </is>
-      </c>
-      <c r="AC6" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AA6" s="7" t="n"/>
+      <c r="AB6" s="7" t="n"/>
+      <c r="AC6" s="7" t="n"/>
       <c r="AD6" s="7" t="n"/>
       <c r="AE6" s="7" t="n"/>
       <c r="AF6" s="7" t="n"/>
@@ -26274,6 +26590,62 @@
       <c r="AJ6" s="7" t="n"/>
       <c r="AK6" s="7" t="n"/>
       <c r="AL6" s="7" t="n"/>
+      <c r="AM6" s="7" t="n"/>
+      <c r="AN6" s="7" t="n"/>
+      <c r="AO6" s="7" t="inlineStr">
+        <is>
+          <t>g/m2;g/cm2;kg/L;g/L</t>
+        </is>
+      </c>
+      <c r="AP6" s="7" t="inlineStr">
+        <is>
+          <t>C67282;C71201;C64566;C42576</t>
+        </is>
+      </c>
+      <c r="AQ6" s="7" t="inlineStr">
+        <is>
+          <t>g/cm2</t>
+        </is>
+      </c>
+      <c r="AR6" s="7" t="inlineStr">
+        <is>
+          <t>C71201</t>
+        </is>
+      </c>
+      <c r="AS6" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT6" s="7" t="n"/>
+      <c r="AU6" s="7" t="n"/>
+      <c r="AV6" s="7" t="n"/>
+      <c r="AW6" s="7" t="n"/>
+      <c r="AX6" s="7" t="n"/>
+      <c r="AY6" s="7" t="n"/>
+      <c r="AZ6" s="7" t="n"/>
+      <c r="BA6" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB6" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC6" s="7" t="n"/>
+      <c r="BD6" s="7" t="n"/>
+      <c r="BE6" s="7" t="n"/>
+      <c r="BF6" s="7" t="n"/>
+      <c r="BG6" s="7" t="n"/>
+      <c r="BH6" s="7" t="n"/>
+      <c r="BI6" s="7" t="n"/>
+      <c r="BJ6" s="7" t="n"/>
+      <c r="BK6" s="7" t="n"/>
+      <c r="BL6" s="7" t="n"/>
+      <c r="BM6" s="7" t="n"/>
+      <c r="BN6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -26390,6 +26762,42 @@
       <c r="AJ7" s="7" t="n"/>
       <c r="AK7" s="7" t="n"/>
       <c r="AL7" s="7" t="n"/>
+      <c r="AM7" s="7" t="n"/>
+      <c r="AN7" s="7" t="n"/>
+      <c r="AO7" s="7" t="n"/>
+      <c r="AP7" s="7" t="n"/>
+      <c r="AQ7" s="7" t="n"/>
+      <c r="AR7" s="7" t="n"/>
+      <c r="AS7" s="7" t="n"/>
+      <c r="AT7" s="7" t="n"/>
+      <c r="AU7" s="7" t="n"/>
+      <c r="AV7" s="7" t="n"/>
+      <c r="AW7" s="7" t="n"/>
+      <c r="AX7" s="7" t="n"/>
+      <c r="AY7" s="7" t="n"/>
+      <c r="AZ7" s="7" t="n"/>
+      <c r="BA7" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB7" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC7" s="7" t="n"/>
+      <c r="BD7" s="7" t="n"/>
+      <c r="BE7" s="7" t="n"/>
+      <c r="BF7" s="7" t="n"/>
+      <c r="BG7" s="7" t="n"/>
+      <c r="BH7" s="7" t="n"/>
+      <c r="BI7" s="7" t="n"/>
+      <c r="BJ7" s="7" t="n"/>
+      <c r="BK7" s="7" t="n"/>
+      <c r="BL7" s="7" t="n"/>
+      <c r="BM7" s="7" t="n"/>
+      <c r="BN7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -26506,6 +26914,42 @@
       <c r="AJ8" s="7" t="n"/>
       <c r="AK8" s="7" t="n"/>
       <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="7" t="n"/>
+      <c r="AN8" s="7" t="n"/>
+      <c r="AO8" s="7" t="n"/>
+      <c r="AP8" s="7" t="n"/>
+      <c r="AQ8" s="7" t="n"/>
+      <c r="AR8" s="7" t="n"/>
+      <c r="AS8" s="7" t="n"/>
+      <c r="AT8" s="7" t="n"/>
+      <c r="AU8" s="7" t="n"/>
+      <c r="AV8" s="7" t="n"/>
+      <c r="AW8" s="7" t="n"/>
+      <c r="AX8" s="7" t="n"/>
+      <c r="AY8" s="7" t="n"/>
+      <c r="AZ8" s="7" t="n"/>
+      <c r="BA8" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB8" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC8" s="7" t="n"/>
+      <c r="BD8" s="7" t="n"/>
+      <c r="BE8" s="7" t="n"/>
+      <c r="BF8" s="7" t="n"/>
+      <c r="BG8" s="7" t="n"/>
+      <c r="BH8" s="7" t="n"/>
+      <c r="BI8" s="7" t="n"/>
+      <c r="BJ8" s="7" t="n"/>
+      <c r="BK8" s="7" t="n"/>
+      <c r="BL8" s="7" t="n"/>
+      <c r="BM8" s="7" t="n"/>
+      <c r="BN8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -26612,16 +27056,64 @@
       <c r="Z9" s="7" t="n"/>
       <c r="AA9" s="7" t="n"/>
       <c r="AB9" s="7" t="n"/>
-      <c r="AC9" s="7" t="n"/>
+      <c r="AC9" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD9" s="7" t="n"/>
       <c r="AE9" s="7" t="n"/>
       <c r="AF9" s="7" t="n"/>
       <c r="AG9" s="7" t="n"/>
-      <c r="AH9" s="7" t="n"/>
+      <c r="AH9" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI9" s="7" t="n"/>
-      <c r="AJ9" s="7" t="n"/>
+      <c r="AJ9" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK9" s="7" t="n"/>
       <c r="AL9" s="7" t="n"/>
+      <c r="AM9" s="7" t="n"/>
+      <c r="AN9" s="7" t="n"/>
+      <c r="AO9" s="7" t="n"/>
+      <c r="AP9" s="7" t="n"/>
+      <c r="AQ9" s="7" t="n"/>
+      <c r="AR9" s="7" t="n"/>
+      <c r="AS9" s="7" t="n"/>
+      <c r="AT9" s="7" t="n"/>
+      <c r="AU9" s="7" t="n"/>
+      <c r="AV9" s="7" t="n"/>
+      <c r="AW9" s="7" t="n"/>
+      <c r="AX9" s="7" t="n"/>
+      <c r="AY9" s="7" t="n"/>
+      <c r="AZ9" s="7" t="n"/>
+      <c r="BA9" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB9" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC9" s="7" t="n"/>
+      <c r="BD9" s="7" t="n"/>
+      <c r="BE9" s="7" t="n"/>
+      <c r="BF9" s="7" t="n"/>
+      <c r="BG9" s="7" t="n"/>
+      <c r="BH9" s="7" t="n"/>
+      <c r="BI9" s="7" t="n"/>
+      <c r="BJ9" s="7" t="n"/>
+      <c r="BK9" s="7" t="n"/>
+      <c r="BL9" s="7" t="n"/>
+      <c r="BM9" s="7" t="n"/>
+      <c r="BN9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -26728,16 +27220,64 @@
       <c r="Z10" s="7" t="n"/>
       <c r="AA10" s="7" t="n"/>
       <c r="AB10" s="7" t="n"/>
-      <c r="AC10" s="7" t="n"/>
+      <c r="AC10" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD10" s="7" t="n"/>
       <c r="AE10" s="7" t="n"/>
       <c r="AF10" s="7" t="n"/>
       <c r="AG10" s="7" t="n"/>
-      <c r="AH10" s="7" t="n"/>
+      <c r="AH10" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI10" s="7" t="n"/>
-      <c r="AJ10" s="7" t="n"/>
+      <c r="AJ10" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK10" s="7" t="n"/>
       <c r="AL10" s="7" t="n"/>
+      <c r="AM10" s="7" t="n"/>
+      <c r="AN10" s="7" t="n"/>
+      <c r="AO10" s="7" t="n"/>
+      <c r="AP10" s="7" t="n"/>
+      <c r="AQ10" s="7" t="n"/>
+      <c r="AR10" s="7" t="n"/>
+      <c r="AS10" s="7" t="n"/>
+      <c r="AT10" s="7" t="n"/>
+      <c r="AU10" s="7" t="n"/>
+      <c r="AV10" s="7" t="n"/>
+      <c r="AW10" s="7" t="n"/>
+      <c r="AX10" s="7" t="n"/>
+      <c r="AY10" s="7" t="n"/>
+      <c r="AZ10" s="7" t="n"/>
+      <c r="BA10" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB10" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC10" s="7" t="n"/>
+      <c r="BD10" s="7" t="n"/>
+      <c r="BE10" s="7" t="n"/>
+      <c r="BF10" s="7" t="n"/>
+      <c r="BG10" s="7" t="n"/>
+      <c r="BH10" s="7" t="n"/>
+      <c r="BI10" s="7" t="n"/>
+      <c r="BJ10" s="7" t="n"/>
+      <c r="BK10" s="7" t="n"/>
+      <c r="BL10" s="7" t="n"/>
+      <c r="BM10" s="7" t="n"/>
+      <c r="BN10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -26844,16 +27384,64 @@
       <c r="Z11" s="7" t="n"/>
       <c r="AA11" s="7" t="n"/>
       <c r="AB11" s="7" t="n"/>
-      <c r="AC11" s="7" t="n"/>
+      <c r="AC11" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD11" s="7" t="n"/>
       <c r="AE11" s="7" t="n"/>
       <c r="AF11" s="7" t="n"/>
       <c r="AG11" s="7" t="n"/>
-      <c r="AH11" s="7" t="n"/>
+      <c r="AH11" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI11" s="7" t="n"/>
-      <c r="AJ11" s="7" t="n"/>
+      <c r="AJ11" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK11" s="7" t="n"/>
       <c r="AL11" s="7" t="n"/>
+      <c r="AM11" s="7" t="n"/>
+      <c r="AN11" s="7" t="n"/>
+      <c r="AO11" s="7" t="n"/>
+      <c r="AP11" s="7" t="n"/>
+      <c r="AQ11" s="7" t="n"/>
+      <c r="AR11" s="7" t="n"/>
+      <c r="AS11" s="7" t="n"/>
+      <c r="AT11" s="7" t="n"/>
+      <c r="AU11" s="7" t="n"/>
+      <c r="AV11" s="7" t="n"/>
+      <c r="AW11" s="7" t="n"/>
+      <c r="AX11" s="7" t="n"/>
+      <c r="AY11" s="7" t="n"/>
+      <c r="AZ11" s="7" t="n"/>
+      <c r="BA11" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB11" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC11" s="7" t="n"/>
+      <c r="BD11" s="7" t="n"/>
+      <c r="BE11" s="7" t="n"/>
+      <c r="BF11" s="7" t="n"/>
+      <c r="BG11" s="7" t="n"/>
+      <c r="BH11" s="7" t="n"/>
+      <c r="BI11" s="7" t="n"/>
+      <c r="BJ11" s="7" t="n"/>
+      <c r="BK11" s="7" t="n"/>
+      <c r="BL11" s="7" t="n"/>
+      <c r="BM11" s="7" t="n"/>
+      <c r="BN11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -26960,16 +27548,64 @@
       <c r="Z12" s="7" t="n"/>
       <c r="AA12" s="7" t="n"/>
       <c r="AB12" s="7" t="n"/>
-      <c r="AC12" s="7" t="n"/>
+      <c r="AC12" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD12" s="7" t="n"/>
       <c r="AE12" s="7" t="n"/>
       <c r="AF12" s="7" t="n"/>
       <c r="AG12" s="7" t="n"/>
-      <c r="AH12" s="7" t="n"/>
+      <c r="AH12" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI12" s="7" t="n"/>
-      <c r="AJ12" s="7" t="n"/>
+      <c r="AJ12" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK12" s="7" t="n"/>
       <c r="AL12" s="7" t="n"/>
+      <c r="AM12" s="7" t="n"/>
+      <c r="AN12" s="7" t="n"/>
+      <c r="AO12" s="7" t="n"/>
+      <c r="AP12" s="7" t="n"/>
+      <c r="AQ12" s="7" t="n"/>
+      <c r="AR12" s="7" t="n"/>
+      <c r="AS12" s="7" t="n"/>
+      <c r="AT12" s="7" t="n"/>
+      <c r="AU12" s="7" t="n"/>
+      <c r="AV12" s="7" t="n"/>
+      <c r="AW12" s="7" t="n"/>
+      <c r="AX12" s="7" t="n"/>
+      <c r="AY12" s="7" t="n"/>
+      <c r="AZ12" s="7" t="n"/>
+      <c r="BA12" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB12" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC12" s="7" t="n"/>
+      <c r="BD12" s="7" t="n"/>
+      <c r="BE12" s="7" t="n"/>
+      <c r="BF12" s="7" t="n"/>
+      <c r="BG12" s="7" t="n"/>
+      <c r="BH12" s="7" t="n"/>
+      <c r="BI12" s="7" t="n"/>
+      <c r="BJ12" s="7" t="n"/>
+      <c r="BK12" s="7" t="n"/>
+      <c r="BL12" s="7" t="n"/>
+      <c r="BM12" s="7" t="n"/>
+      <c r="BN12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -27076,16 +27712,64 @@
       <c r="Z13" s="7" t="n"/>
       <c r="AA13" s="7" t="n"/>
       <c r="AB13" s="7" t="n"/>
-      <c r="AC13" s="7" t="n"/>
+      <c r="AC13" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD13" s="7" t="n"/>
       <c r="AE13" s="7" t="n"/>
       <c r="AF13" s="7" t="n"/>
       <c r="AG13" s="7" t="n"/>
-      <c r="AH13" s="7" t="n"/>
+      <c r="AH13" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI13" s="7" t="n"/>
-      <c r="AJ13" s="7" t="n"/>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK13" s="7" t="n"/>
       <c r="AL13" s="7" t="n"/>
+      <c r="AM13" s="7" t="n"/>
+      <c r="AN13" s="7" t="n"/>
+      <c r="AO13" s="7" t="n"/>
+      <c r="AP13" s="7" t="n"/>
+      <c r="AQ13" s="7" t="n"/>
+      <c r="AR13" s="7" t="n"/>
+      <c r="AS13" s="7" t="n"/>
+      <c r="AT13" s="7" t="n"/>
+      <c r="AU13" s="7" t="n"/>
+      <c r="AV13" s="7" t="n"/>
+      <c r="AW13" s="7" t="n"/>
+      <c r="AX13" s="7" t="n"/>
+      <c r="AY13" s="7" t="n"/>
+      <c r="AZ13" s="7" t="n"/>
+      <c r="BA13" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB13" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC13" s="7" t="n"/>
+      <c r="BD13" s="7" t="n"/>
+      <c r="BE13" s="7" t="n"/>
+      <c r="BF13" s="7" t="n"/>
+      <c r="BG13" s="7" t="n"/>
+      <c r="BH13" s="7" t="n"/>
+      <c r="BI13" s="7" t="n"/>
+      <c r="BJ13" s="7" t="n"/>
+      <c r="BK13" s="7" t="n"/>
+      <c r="BL13" s="7" t="n"/>
+      <c r="BM13" s="7" t="n"/>
+      <c r="BN13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -27192,16 +27876,64 @@
       <c r="Z14" s="7" t="n"/>
       <c r="AA14" s="7" t="n"/>
       <c r="AB14" s="7" t="n"/>
-      <c r="AC14" s="7" t="n"/>
+      <c r="AC14" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD14" s="7" t="n"/>
       <c r="AE14" s="7" t="n"/>
       <c r="AF14" s="7" t="n"/>
       <c r="AG14" s="7" t="n"/>
-      <c r="AH14" s="7" t="n"/>
+      <c r="AH14" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI14" s="7" t="n"/>
-      <c r="AJ14" s="7" t="n"/>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK14" s="7" t="n"/>
       <c r="AL14" s="7" t="n"/>
+      <c r="AM14" s="7" t="n"/>
+      <c r="AN14" s="7" t="n"/>
+      <c r="AO14" s="7" t="n"/>
+      <c r="AP14" s="7" t="n"/>
+      <c r="AQ14" s="7" t="n"/>
+      <c r="AR14" s="7" t="n"/>
+      <c r="AS14" s="7" t="n"/>
+      <c r="AT14" s="7" t="n"/>
+      <c r="AU14" s="7" t="n"/>
+      <c r="AV14" s="7" t="n"/>
+      <c r="AW14" s="7" t="n"/>
+      <c r="AX14" s="7" t="n"/>
+      <c r="AY14" s="7" t="n"/>
+      <c r="AZ14" s="7" t="n"/>
+      <c r="BA14" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB14" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC14" s="7" t="n"/>
+      <c r="BD14" s="7" t="n"/>
+      <c r="BE14" s="7" t="n"/>
+      <c r="BF14" s="7" t="n"/>
+      <c r="BG14" s="7" t="n"/>
+      <c r="BH14" s="7" t="n"/>
+      <c r="BI14" s="7" t="n"/>
+      <c r="BJ14" s="7" t="n"/>
+      <c r="BK14" s="7" t="n"/>
+      <c r="BL14" s="7" t="n"/>
+      <c r="BM14" s="7" t="n"/>
+      <c r="BN14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -27308,16 +28040,64 @@
       <c r="Z15" s="7" t="n"/>
       <c r="AA15" s="7" t="n"/>
       <c r="AB15" s="7" t="n"/>
-      <c r="AC15" s="7" t="n"/>
+      <c r="AC15" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD15" s="7" t="n"/>
       <c r="AE15" s="7" t="n"/>
       <c r="AF15" s="7" t="n"/>
       <c r="AG15" s="7" t="n"/>
-      <c r="AH15" s="7" t="n"/>
+      <c r="AH15" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI15" s="7" t="n"/>
-      <c r="AJ15" s="7" t="n"/>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK15" s="7" t="n"/>
       <c r="AL15" s="7" t="n"/>
+      <c r="AM15" s="7" t="n"/>
+      <c r="AN15" s="7" t="n"/>
+      <c r="AO15" s="7" t="n"/>
+      <c r="AP15" s="7" t="n"/>
+      <c r="AQ15" s="7" t="n"/>
+      <c r="AR15" s="7" t="n"/>
+      <c r="AS15" s="7" t="n"/>
+      <c r="AT15" s="7" t="n"/>
+      <c r="AU15" s="7" t="n"/>
+      <c r="AV15" s="7" t="n"/>
+      <c r="AW15" s="7" t="n"/>
+      <c r="AX15" s="7" t="n"/>
+      <c r="AY15" s="7" t="n"/>
+      <c r="AZ15" s="7" t="n"/>
+      <c r="BA15" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB15" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC15" s="7" t="n"/>
+      <c r="BD15" s="7" t="n"/>
+      <c r="BE15" s="7" t="n"/>
+      <c r="BF15" s="7" t="n"/>
+      <c r="BG15" s="7" t="n"/>
+      <c r="BH15" s="7" t="n"/>
+      <c r="BI15" s="7" t="n"/>
+      <c r="BJ15" s="7" t="n"/>
+      <c r="BK15" s="7" t="n"/>
+      <c r="BL15" s="7" t="n"/>
+      <c r="BM15" s="7" t="n"/>
+      <c r="BN15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -27424,16 +28204,64 @@
       <c r="Z16" s="7" t="n"/>
       <c r="AA16" s="7" t="n"/>
       <c r="AB16" s="7" t="n"/>
-      <c r="AC16" s="7" t="n"/>
+      <c r="AC16" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD16" s="7" t="n"/>
       <c r="AE16" s="7" t="n"/>
       <c r="AF16" s="7" t="n"/>
       <c r="AG16" s="7" t="n"/>
-      <c r="AH16" s="7" t="n"/>
+      <c r="AH16" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI16" s="7" t="n"/>
-      <c r="AJ16" s="7" t="n"/>
+      <c r="AJ16" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK16" s="7" t="n"/>
       <c r="AL16" s="7" t="n"/>
+      <c r="AM16" s="7" t="n"/>
+      <c r="AN16" s="7" t="n"/>
+      <c r="AO16" s="7" t="n"/>
+      <c r="AP16" s="7" t="n"/>
+      <c r="AQ16" s="7" t="n"/>
+      <c r="AR16" s="7" t="n"/>
+      <c r="AS16" s="7" t="n"/>
+      <c r="AT16" s="7" t="n"/>
+      <c r="AU16" s="7" t="n"/>
+      <c r="AV16" s="7" t="n"/>
+      <c r="AW16" s="7" t="n"/>
+      <c r="AX16" s="7" t="n"/>
+      <c r="AY16" s="7" t="n"/>
+      <c r="AZ16" s="7" t="n"/>
+      <c r="BA16" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB16" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC16" s="7" t="n"/>
+      <c r="BD16" s="7" t="n"/>
+      <c r="BE16" s="7" t="n"/>
+      <c r="BF16" s="7" t="n"/>
+      <c r="BG16" s="7" t="n"/>
+      <c r="BH16" s="7" t="n"/>
+      <c r="BI16" s="7" t="n"/>
+      <c r="BJ16" s="7" t="n"/>
+      <c r="BK16" s="7" t="n"/>
+      <c r="BL16" s="7" t="n"/>
+      <c r="BM16" s="7" t="n"/>
+      <c r="BN16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -27535,36 +28363,12 @@
       <c r="U17" s="7" t="n"/>
       <c r="V17" s="7" t="n"/>
       <c r="W17" s="7" t="n"/>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>C25613</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA17" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="AB17" s="7" t="inlineStr">
-        <is>
-          <t>C25613</t>
-        </is>
-      </c>
-      <c r="AC17" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="7" t="n"/>
+      <c r="Z17" s="7" t="n"/>
+      <c r="AA17" s="7" t="n"/>
+      <c r="AB17" s="7" t="n"/>
+      <c r="AC17" s="7" t="n"/>
       <c r="AD17" s="7" t="n"/>
       <c r="AE17" s="7" t="n"/>
       <c r="AF17" s="7" t="n"/>
@@ -27573,7 +28377,59 @@
       <c r="AI17" s="7" t="n"/>
       <c r="AJ17" s="7" t="n"/>
       <c r="AK17" s="7" t="n"/>
-      <c r="AL17" s="7" t="n"/>
+      <c r="AL17" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AM17" s="7" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="n"/>
+      <c r="AP17" s="7" t="n"/>
+      <c r="AQ17" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AR17" s="7" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
+      <c r="AS17" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT17" s="7" t="n"/>
+      <c r="AU17" s="7" t="n"/>
+      <c r="AV17" s="7" t="n"/>
+      <c r="AW17" s="7" t="n"/>
+      <c r="AX17" s="7" t="n"/>
+      <c r="AY17" s="7" t="n"/>
+      <c r="AZ17" s="7" t="n"/>
+      <c r="BA17" s="7" t="n"/>
+      <c r="BB17" s="7" t="n"/>
+      <c r="BC17" s="7" t="n"/>
+      <c r="BD17" s="7" t="n"/>
+      <c r="BE17" s="7" t="n"/>
+      <c r="BF17" s="7" t="n"/>
+      <c r="BG17" s="7" t="n"/>
+      <c r="BH17" s="7" t="n"/>
+      <c r="BI17" s="7" t="n"/>
+      <c r="BJ17" s="7" t="n"/>
+      <c r="BK17" s="7" t="n"/>
+      <c r="BL17" s="7" t="n"/>
+      <c r="BM17" s="7" t="n"/>
+      <c r="BN17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -27675,36 +28531,12 @@
       <c r="U18" s="7" t="n"/>
       <c r="V18" s="7" t="n"/>
       <c r="W18" s="7" t="n"/>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>C42535</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA18" s="7" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="AB18" s="7" t="inlineStr">
-        <is>
-          <t>C42535</t>
-        </is>
-      </c>
-      <c r="AC18" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" s="7" t="n"/>
+      <c r="AB18" s="7" t="n"/>
+      <c r="AC18" s="7" t="n"/>
       <c r="AD18" s="7" t="n"/>
       <c r="AE18" s="7" t="n"/>
       <c r="AF18" s="7" t="n"/>
@@ -27713,7 +28545,67 @@
       <c r="AI18" s="7" t="n"/>
       <c r="AJ18" s="7" t="n"/>
       <c r="AK18" s="7" t="n"/>
-      <c r="AL18" s="7" t="n"/>
+      <c r="AL18" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>C42535</t>
+        </is>
+      </c>
+      <c r="AN18" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO18" s="7" t="n"/>
+      <c r="AP18" s="7" t="n"/>
+      <c r="AQ18" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="AR18" s="7" t="inlineStr">
+        <is>
+          <t>C42535</t>
+        </is>
+      </c>
+      <c r="AS18" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT18" s="7" t="n"/>
+      <c r="AU18" s="7" t="n"/>
+      <c r="AV18" s="7" t="n"/>
+      <c r="AW18" s="7" t="n"/>
+      <c r="AX18" s="7" t="n"/>
+      <c r="AY18" s="7" t="n"/>
+      <c r="AZ18" s="7" t="n"/>
+      <c r="BA18" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB18" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC18" s="7" t="n"/>
+      <c r="BD18" s="7" t="n"/>
+      <c r="BE18" s="7" t="n"/>
+      <c r="BF18" s="7" t="n"/>
+      <c r="BG18" s="7" t="n"/>
+      <c r="BH18" s="7" t="n"/>
+      <c r="BI18" s="7" t="n"/>
+      <c r="BJ18" s="7" t="n"/>
+      <c r="BK18" s="7" t="n"/>
+      <c r="BL18" s="7" t="n"/>
+      <c r="BM18" s="7" t="n"/>
+      <c r="BN18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -27818,17 +28710,9 @@
       <c r="X19" s="7" t="n"/>
       <c r="Y19" s="7" t="n"/>
       <c r="Z19" s="7" t="n"/>
-      <c r="AA19" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA19" s="7" t="n"/>
       <c r="AB19" s="7" t="n"/>
-      <c r="AC19" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC19" s="7" t="n"/>
       <c r="AD19" s="7" t="n"/>
       <c r="AE19" s="7" t="n"/>
       <c r="AF19" s="7" t="n"/>
@@ -27838,6 +28722,58 @@
       <c r="AJ19" s="7" t="n"/>
       <c r="AK19" s="7" t="n"/>
       <c r="AL19" s="7" t="n"/>
+      <c r="AM19" s="7" t="n"/>
+      <c r="AN19" s="7" t="n"/>
+      <c r="AO19" s="7" t="inlineStr">
+        <is>
+          <t>Kg;g;LB;oz</t>
+        </is>
+      </c>
+      <c r="AP19" s="7" t="inlineStr">
+        <is>
+          <t>;C48155;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AQ19" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR19" s="7" t="n"/>
+      <c r="AS19" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT19" s="7" t="n"/>
+      <c r="AU19" s="7" t="n"/>
+      <c r="AV19" s="7" t="n"/>
+      <c r="AW19" s="7" t="n"/>
+      <c r="AX19" s="7" t="n"/>
+      <c r="AY19" s="7" t="n"/>
+      <c r="AZ19" s="7" t="n"/>
+      <c r="BA19" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB19" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC19" s="7" t="n"/>
+      <c r="BD19" s="7" t="n"/>
+      <c r="BE19" s="7" t="n"/>
+      <c r="BF19" s="7" t="n"/>
+      <c r="BG19" s="7" t="n"/>
+      <c r="BH19" s="7" t="n"/>
+      <c r="BI19" s="7" t="n"/>
+      <c r="BJ19" s="7" t="n"/>
+      <c r="BK19" s="7" t="n"/>
+      <c r="BL19" s="7" t="n"/>
+      <c r="BM19" s="7" t="n"/>
+      <c r="BN19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -27944,28 +28880,72 @@
       <c r="Z20" s="7" t="n"/>
       <c r="AA20" s="7" t="n"/>
       <c r="AB20" s="7" t="n"/>
-      <c r="AC20" s="7" t="n"/>
+      <c r="AC20" s="7" t="inlineStr">
+        <is>
+          <t>N;Y;U</t>
+        </is>
+      </c>
       <c r="AD20" s="7" t="inlineStr">
         <is>
-          <t>FONTANELLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>C32621</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
-        <is>
-          <t>LOC</t>
-        </is>
-      </c>
+          <t>C49487;C49488;C17998</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="n"/>
+      <c r="AF20" s="7" t="n"/>
       <c r="AG20" s="7" t="n"/>
-      <c r="AH20" s="7" t="n"/>
-      <c r="AI20" s="7" t="n"/>
+      <c r="AH20" s="7" t="inlineStr">
+        <is>
+          <t>N;Y;U</t>
+        </is>
+      </c>
+      <c r="AI20" s="7" t="inlineStr">
+        <is>
+          <t>C49487;C49488;C17998</t>
+        </is>
+      </c>
       <c r="AJ20" s="7" t="n"/>
       <c r="AK20" s="7" t="n"/>
       <c r="AL20" s="7" t="n"/>
+      <c r="AM20" s="7" t="n"/>
+      <c r="AN20" s="7" t="n"/>
+      <c r="AO20" s="7" t="n"/>
+      <c r="AP20" s="7" t="n"/>
+      <c r="AQ20" s="7" t="n"/>
+      <c r="AR20" s="7" t="n"/>
+      <c r="AS20" s="7" t="n"/>
+      <c r="AT20" s="7" t="n"/>
+      <c r="AU20" s="7" t="n"/>
+      <c r="AV20" s="7" t="inlineStr">
+        <is>
+          <t>FONTANELLE</t>
+        </is>
+      </c>
+      <c r="AW20" s="7" t="inlineStr">
+        <is>
+          <t>C32621</t>
+        </is>
+      </c>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>LOC</t>
+        </is>
+      </c>
+      <c r="AY20" s="7" t="n"/>
+      <c r="AZ20" s="7" t="n"/>
+      <c r="BA20" s="7" t="n"/>
+      <c r="BB20" s="7" t="n"/>
+      <c r="BC20" s="7" t="n"/>
+      <c r="BD20" s="7" t="n"/>
+      <c r="BE20" s="7" t="n"/>
+      <c r="BF20" s="7" t="n"/>
+      <c r="BG20" s="7" t="n"/>
+      <c r="BH20" s="7" t="n"/>
+      <c r="BI20" s="7" t="n"/>
+      <c r="BJ20" s="7" t="n"/>
+      <c r="BK20" s="7" t="n"/>
+      <c r="BL20" s="7" t="n"/>
+      <c r="BM20" s="7" t="n"/>
+      <c r="BN20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -28082,6 +29062,58 @@
       <c r="AJ21" s="7" t="n"/>
       <c r="AK21" s="7" t="n"/>
       <c r="AL21" s="7" t="n"/>
+      <c r="AM21" s="7" t="n"/>
+      <c r="AN21" s="7" t="n"/>
+      <c r="AO21" s="7" t="inlineStr">
+        <is>
+          <t>MONTHS;YEARS</t>
+        </is>
+      </c>
+      <c r="AP21" s="7" t="inlineStr">
+        <is>
+          <t>C29846;C29848</t>
+        </is>
+      </c>
+      <c r="AQ21" s="7" t="n"/>
+      <c r="AR21" s="7" t="n"/>
+      <c r="AS21" s="7" t="n"/>
+      <c r="AT21" s="7" t="inlineStr">
+        <is>
+          <t>MONTHS;YEARS</t>
+        </is>
+      </c>
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>C29846;C29848</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="n"/>
+      <c r="AW21" s="7" t="n"/>
+      <c r="AX21" s="7" t="n"/>
+      <c r="AY21" s="7" t="n"/>
+      <c r="AZ21" s="7" t="n"/>
+      <c r="BA21" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB21" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC21" s="7" t="n"/>
+      <c r="BD21" s="7" t="n"/>
+      <c r="BE21" s="7" t="n"/>
+      <c r="BF21" s="7" t="n"/>
+      <c r="BG21" s="7" t="n"/>
+      <c r="BH21" s="7" t="n"/>
+      <c r="BI21" s="7" t="n"/>
+      <c r="BJ21" s="7" t="n"/>
+      <c r="BK21" s="7" t="n"/>
+      <c r="BL21" s="7" t="n"/>
+      <c r="BM21" s="7" t="n"/>
+      <c r="BN21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -28183,20 +29215,20 @@
       <c r="U22" s="7" t="n"/>
       <c r="V22" s="7" t="n"/>
       <c r="W22" s="7" t="n"/>
-      <c r="X22" s="7" t="n"/>
-      <c r="Y22" s="7" t="n"/>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z22" s="7" t="n"/>
-      <c r="AA22" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA22" s="7" t="n"/>
       <c r="AB22" s="7" t="n"/>
-      <c r="AC22" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC22" s="7" t="n"/>
       <c r="AD22" s="7" t="n"/>
       <c r="AE22" s="7" t="n"/>
       <c r="AF22" s="7" t="n"/>
@@ -28206,6 +29238,58 @@
       <c r="AJ22" s="7" t="n"/>
       <c r="AK22" s="7" t="n"/>
       <c r="AL22" s="7" t="n"/>
+      <c r="AM22" s="7" t="n"/>
+      <c r="AN22" s="7" t="n"/>
+      <c r="AO22" s="7" t="inlineStr">
+        <is>
+          <t>kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP22" s="7" t="inlineStr">
+        <is>
+          <t>C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ22" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR22" s="7" t="n"/>
+      <c r="AS22" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT22" s="7" t="n"/>
+      <c r="AU22" s="7" t="n"/>
+      <c r="AV22" s="7" t="n"/>
+      <c r="AW22" s="7" t="n"/>
+      <c r="AX22" s="7" t="n"/>
+      <c r="AY22" s="7" t="n"/>
+      <c r="AZ22" s="7" t="n"/>
+      <c r="BA22" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB22" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC22" s="7" t="n"/>
+      <c r="BD22" s="7" t="n"/>
+      <c r="BE22" s="7" t="n"/>
+      <c r="BF22" s="7" t="n"/>
+      <c r="BG22" s="7" t="n"/>
+      <c r="BH22" s="7" t="n"/>
+      <c r="BI22" s="7" t="n"/>
+      <c r="BJ22" s="7" t="n"/>
+      <c r="BK22" s="7" t="n"/>
+      <c r="BL22" s="7" t="n"/>
+      <c r="BM22" s="7" t="n"/>
+      <c r="BN22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -28307,20 +29391,20 @@
       <c r="U23" s="7" t="n"/>
       <c r="V23" s="7" t="n"/>
       <c r="W23" s="7" t="n"/>
-      <c r="X23" s="7" t="n"/>
-      <c r="Y23" s="7" t="n"/>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z23" s="7" t="n"/>
-      <c r="AA23" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA23" s="7" t="n"/>
       <c r="AB23" s="7" t="n"/>
-      <c r="AC23" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC23" s="7" t="n"/>
       <c r="AD23" s="7" t="n"/>
       <c r="AE23" s="7" t="n"/>
       <c r="AF23" s="7" t="n"/>
@@ -28330,6 +29414,58 @@
       <c r="AJ23" s="7" t="n"/>
       <c r="AK23" s="7" t="n"/>
       <c r="AL23" s="7" t="n"/>
+      <c r="AM23" s="7" t="n"/>
+      <c r="AN23" s="7" t="n"/>
+      <c r="AO23" s="7" t="inlineStr">
+        <is>
+          <t>kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP23" s="7" t="inlineStr">
+        <is>
+          <t>C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ23" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR23" s="7" t="n"/>
+      <c r="AS23" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT23" s="7" t="n"/>
+      <c r="AU23" s="7" t="n"/>
+      <c r="AV23" s="7" t="n"/>
+      <c r="AW23" s="7" t="n"/>
+      <c r="AX23" s="7" t="n"/>
+      <c r="AY23" s="7" t="n"/>
+      <c r="AZ23" s="7" t="n"/>
+      <c r="BA23" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB23" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC23" s="7" t="n"/>
+      <c r="BD23" s="7" t="n"/>
+      <c r="BE23" s="7" t="n"/>
+      <c r="BF23" s="7" t="n"/>
+      <c r="BG23" s="7" t="n"/>
+      <c r="BH23" s="7" t="n"/>
+      <c r="BI23" s="7" t="n"/>
+      <c r="BJ23" s="7" t="n"/>
+      <c r="BK23" s="7" t="n"/>
+      <c r="BL23" s="7" t="n"/>
+      <c r="BM23" s="7" t="n"/>
+      <c r="BN23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -28431,20 +29567,20 @@
       <c r="U24" s="7" t="n"/>
       <c r="V24" s="7" t="n"/>
       <c r="W24" s="7" t="n"/>
-      <c r="X24" s="7" t="n"/>
-      <c r="Y24" s="7" t="n"/>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z24" s="7" t="n"/>
-      <c r="AA24" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA24" s="7" t="n"/>
       <c r="AB24" s="7" t="n"/>
-      <c r="AC24" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC24" s="7" t="n"/>
       <c r="AD24" s="7" t="n"/>
       <c r="AE24" s="7" t="n"/>
       <c r="AF24" s="7" t="n"/>
@@ -28454,6 +29590,58 @@
       <c r="AJ24" s="7" t="n"/>
       <c r="AK24" s="7" t="n"/>
       <c r="AL24" s="7" t="n"/>
+      <c r="AM24" s="7" t="n"/>
+      <c r="AN24" s="7" t="n"/>
+      <c r="AO24" s="7" t="inlineStr">
+        <is>
+          <t>kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP24" s="7" t="inlineStr">
+        <is>
+          <t>C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ24" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR24" s="7" t="n"/>
+      <c r="AS24" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT24" s="7" t="n"/>
+      <c r="AU24" s="7" t="n"/>
+      <c r="AV24" s="7" t="n"/>
+      <c r="AW24" s="7" t="n"/>
+      <c r="AX24" s="7" t="n"/>
+      <c r="AY24" s="7" t="n"/>
+      <c r="AZ24" s="7" t="n"/>
+      <c r="BA24" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB24" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC24" s="7" t="n"/>
+      <c r="BD24" s="7" t="n"/>
+      <c r="BE24" s="7" t="n"/>
+      <c r="BF24" s="7" t="n"/>
+      <c r="BG24" s="7" t="n"/>
+      <c r="BH24" s="7" t="n"/>
+      <c r="BI24" s="7" t="n"/>
+      <c r="BJ24" s="7" t="n"/>
+      <c r="BK24" s="7" t="n"/>
+      <c r="BL24" s="7" t="n"/>
+      <c r="BM24" s="7" t="n"/>
+      <c r="BN24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -28555,20 +29743,20 @@
       <c r="U25" s="7" t="n"/>
       <c r="V25" s="7" t="n"/>
       <c r="W25" s="7" t="n"/>
-      <c r="X25" s="7" t="n"/>
-      <c r="Y25" s="7" t="n"/>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z25" s="7" t="n"/>
-      <c r="AA25" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA25" s="7" t="n"/>
       <c r="AB25" s="7" t="n"/>
-      <c r="AC25" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC25" s="7" t="n"/>
       <c r="AD25" s="7" t="n"/>
       <c r="AE25" s="7" t="n"/>
       <c r="AF25" s="7" t="n"/>
@@ -28578,6 +29766,58 @@
       <c r="AJ25" s="7" t="n"/>
       <c r="AK25" s="7" t="n"/>
       <c r="AL25" s="7" t="n"/>
+      <c r="AM25" s="7" t="n"/>
+      <c r="AN25" s="7" t="n"/>
+      <c r="AO25" s="7" t="inlineStr">
+        <is>
+          <t>kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP25" s="7" t="inlineStr">
+        <is>
+          <t>C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ25" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR25" s="7" t="n"/>
+      <c r="AS25" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT25" s="7" t="n"/>
+      <c r="AU25" s="7" t="n"/>
+      <c r="AV25" s="7" t="n"/>
+      <c r="AW25" s="7" t="n"/>
+      <c r="AX25" s="7" t="n"/>
+      <c r="AY25" s="7" t="n"/>
+      <c r="AZ25" s="7" t="n"/>
+      <c r="BA25" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB25" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC25" s="7" t="n"/>
+      <c r="BD25" s="7" t="n"/>
+      <c r="BE25" s="7" t="n"/>
+      <c r="BF25" s="7" t="n"/>
+      <c r="BG25" s="7" t="n"/>
+      <c r="BH25" s="7" t="n"/>
+      <c r="BI25" s="7" t="n"/>
+      <c r="BJ25" s="7" t="n"/>
+      <c r="BK25" s="7" t="n"/>
+      <c r="BL25" s="7" t="n"/>
+      <c r="BM25" s="7" t="n"/>
+      <c r="BN25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -28679,8 +29919,16 @@
       <c r="U26" s="7" t="n"/>
       <c r="V26" s="7" t="n"/>
       <c r="W26" s="7" t="n"/>
-      <c r="X26" s="7" t="n"/>
-      <c r="Y26" s="7" t="n"/>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z26" s="7" t="n"/>
       <c r="AA26" s="7" t="n"/>
       <c r="AB26" s="7" t="n"/>
@@ -28694,6 +29942,42 @@
       <c r="AJ26" s="7" t="n"/>
       <c r="AK26" s="7" t="n"/>
       <c r="AL26" s="7" t="n"/>
+      <c r="AM26" s="7" t="n"/>
+      <c r="AN26" s="7" t="n"/>
+      <c r="AO26" s="7" t="n"/>
+      <c r="AP26" s="7" t="n"/>
+      <c r="AQ26" s="7" t="n"/>
+      <c r="AR26" s="7" t="n"/>
+      <c r="AS26" s="7" t="n"/>
+      <c r="AT26" s="7" t="n"/>
+      <c r="AU26" s="7" t="n"/>
+      <c r="AV26" s="7" t="n"/>
+      <c r="AW26" s="7" t="n"/>
+      <c r="AX26" s="7" t="n"/>
+      <c r="AY26" s="7" t="n"/>
+      <c r="AZ26" s="7" t="n"/>
+      <c r="BA26" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB26" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC26" s="7" t="n"/>
+      <c r="BD26" s="7" t="n"/>
+      <c r="BE26" s="7" t="n"/>
+      <c r="BF26" s="7" t="n"/>
+      <c r="BG26" s="7" t="n"/>
+      <c r="BH26" s="7" t="n"/>
+      <c r="BI26" s="7" t="n"/>
+      <c r="BJ26" s="7" t="n"/>
+      <c r="BK26" s="7" t="n"/>
+      <c r="BL26" s="7" t="n"/>
+      <c r="BM26" s="7" t="n"/>
+      <c r="BN26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -28795,20 +30079,20 @@
       <c r="U27" s="7" t="n"/>
       <c r="V27" s="7" t="n"/>
       <c r="W27" s="7" t="n"/>
-      <c r="X27" s="7" t="n"/>
-      <c r="Y27" s="7" t="n"/>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z27" s="7" t="n"/>
-      <c r="AA27" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA27" s="7" t="n"/>
       <c r="AB27" s="7" t="n"/>
-      <c r="AC27" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC27" s="7" t="n"/>
       <c r="AD27" s="7" t="n"/>
       <c r="AE27" s="7" t="n"/>
       <c r="AF27" s="7" t="n"/>
@@ -28818,6 +30102,58 @@
       <c r="AJ27" s="7" t="n"/>
       <c r="AK27" s="7" t="n"/>
       <c r="AL27" s="7" t="n"/>
+      <c r="AM27" s="7" t="n"/>
+      <c r="AN27" s="7" t="n"/>
+      <c r="AO27" s="7" t="inlineStr">
+        <is>
+          <t>kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP27" s="7" t="inlineStr">
+        <is>
+          <t>C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ27" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR27" s="7" t="n"/>
+      <c r="AS27" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT27" s="7" t="n"/>
+      <c r="AU27" s="7" t="n"/>
+      <c r="AV27" s="7" t="n"/>
+      <c r="AW27" s="7" t="n"/>
+      <c r="AX27" s="7" t="n"/>
+      <c r="AY27" s="7" t="n"/>
+      <c r="AZ27" s="7" t="n"/>
+      <c r="BA27" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB27" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC27" s="7" t="n"/>
+      <c r="BD27" s="7" t="n"/>
+      <c r="BE27" s="7" t="n"/>
+      <c r="BF27" s="7" t="n"/>
+      <c r="BG27" s="7" t="n"/>
+      <c r="BH27" s="7" t="n"/>
+      <c r="BI27" s="7" t="n"/>
+      <c r="BJ27" s="7" t="n"/>
+      <c r="BK27" s="7" t="n"/>
+      <c r="BL27" s="7" t="n"/>
+      <c r="BM27" s="7" t="n"/>
+      <c r="BN27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -28919,20 +30255,20 @@
       <c r="U28" s="7" t="n"/>
       <c r="V28" s="7" t="n"/>
       <c r="W28" s="7" t="n"/>
-      <c r="X28" s="7" t="n"/>
-      <c r="Y28" s="7" t="n"/>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y28" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z28" s="7" t="n"/>
-      <c r="AA28" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA28" s="7" t="n"/>
       <c r="AB28" s="7" t="n"/>
-      <c r="AC28" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC28" s="7" t="n"/>
       <c r="AD28" s="7" t="n"/>
       <c r="AE28" s="7" t="n"/>
       <c r="AF28" s="7" t="n"/>
@@ -28942,6 +30278,58 @@
       <c r="AJ28" s="7" t="n"/>
       <c r="AK28" s="7" t="n"/>
       <c r="AL28" s="7" t="n"/>
+      <c r="AM28" s="7" t="n"/>
+      <c r="AN28" s="7" t="n"/>
+      <c r="AO28" s="7" t="inlineStr">
+        <is>
+          <t>kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP28" s="7" t="inlineStr">
+        <is>
+          <t>C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ28" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR28" s="7" t="n"/>
+      <c r="AS28" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT28" s="7" t="n"/>
+      <c r="AU28" s="7" t="n"/>
+      <c r="AV28" s="7" t="n"/>
+      <c r="AW28" s="7" t="n"/>
+      <c r="AX28" s="7" t="n"/>
+      <c r="AY28" s="7" t="n"/>
+      <c r="AZ28" s="7" t="n"/>
+      <c r="BA28" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB28" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC28" s="7" t="n"/>
+      <c r="BD28" s="7" t="n"/>
+      <c r="BE28" s="7" t="n"/>
+      <c r="BF28" s="7" t="n"/>
+      <c r="BG28" s="7" t="n"/>
+      <c r="BH28" s="7" t="n"/>
+      <c r="BI28" s="7" t="n"/>
+      <c r="BJ28" s="7" t="n"/>
+      <c r="BK28" s="7" t="n"/>
+      <c r="BL28" s="7" t="n"/>
+      <c r="BM28" s="7" t="n"/>
+      <c r="BN28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -29043,8 +30431,16 @@
       <c r="U29" s="7" t="n"/>
       <c r="V29" s="7" t="n"/>
       <c r="W29" s="7" t="n"/>
-      <c r="X29" s="7" t="n"/>
-      <c r="Y29" s="7" t="n"/>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;HAND-HELD DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>C161407;C186193</t>
+        </is>
+      </c>
       <c r="Z29" s="7" t="n"/>
       <c r="AA29" s="7" t="n"/>
       <c r="AB29" s="7" t="n"/>
@@ -29058,6 +30454,42 @@
       <c r="AJ29" s="7" t="n"/>
       <c r="AK29" s="7" t="n"/>
       <c r="AL29" s="7" t="n"/>
+      <c r="AM29" s="7" t="n"/>
+      <c r="AN29" s="7" t="n"/>
+      <c r="AO29" s="7" t="n"/>
+      <c r="AP29" s="7" t="n"/>
+      <c r="AQ29" s="7" t="n"/>
+      <c r="AR29" s="7" t="n"/>
+      <c r="AS29" s="7" t="n"/>
+      <c r="AT29" s="7" t="n"/>
+      <c r="AU29" s="7" t="n"/>
+      <c r="AV29" s="7" t="n"/>
+      <c r="AW29" s="7" t="n"/>
+      <c r="AX29" s="7" t="n"/>
+      <c r="AY29" s="7" t="n"/>
+      <c r="AZ29" s="7" t="n"/>
+      <c r="BA29" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB29" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC29" s="7" t="n"/>
+      <c r="BD29" s="7" t="n"/>
+      <c r="BE29" s="7" t="n"/>
+      <c r="BF29" s="7" t="n"/>
+      <c r="BG29" s="7" t="n"/>
+      <c r="BH29" s="7" t="n"/>
+      <c r="BI29" s="7" t="n"/>
+      <c r="BJ29" s="7" t="n"/>
+      <c r="BK29" s="7" t="n"/>
+      <c r="BL29" s="7" t="n"/>
+      <c r="BM29" s="7" t="n"/>
+      <c r="BN29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -29162,17 +30594,9 @@
       <c r="X30" s="7" t="n"/>
       <c r="Y30" s="7" t="n"/>
       <c r="Z30" s="7" t="n"/>
-      <c r="AA30" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA30" s="7" t="n"/>
       <c r="AB30" s="7" t="n"/>
-      <c r="AC30" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC30" s="7" t="n"/>
       <c r="AD30" s="7" t="n"/>
       <c r="AE30" s="7" t="n"/>
       <c r="AF30" s="7" t="n"/>
@@ -29182,6 +30606,58 @@
       <c r="AJ30" s="7" t="n"/>
       <c r="AK30" s="7" t="n"/>
       <c r="AL30" s="7" t="n"/>
+      <c r="AM30" s="7" t="n"/>
+      <c r="AN30" s="7" t="n"/>
+      <c r="AO30" s="7" t="inlineStr">
+        <is>
+          <t>Kg;g;LB;oz</t>
+        </is>
+      </c>
+      <c r="AP30" s="7" t="inlineStr">
+        <is>
+          <t>;C48155;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AQ30" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR30" s="7" t="n"/>
+      <c r="AS30" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT30" s="7" t="n"/>
+      <c r="AU30" s="7" t="n"/>
+      <c r="AV30" s="7" t="n"/>
+      <c r="AW30" s="7" t="n"/>
+      <c r="AX30" s="7" t="n"/>
+      <c r="AY30" s="7" t="n"/>
+      <c r="AZ30" s="7" t="n"/>
+      <c r="BA30" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB30" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC30" s="7" t="n"/>
+      <c r="BD30" s="7" t="n"/>
+      <c r="BE30" s="7" t="n"/>
+      <c r="BF30" s="7" t="n"/>
+      <c r="BG30" s="7" t="n"/>
+      <c r="BH30" s="7" t="n"/>
+      <c r="BI30" s="7" t="n"/>
+      <c r="BJ30" s="7" t="n"/>
+      <c r="BK30" s="7" t="n"/>
+      <c r="BL30" s="7" t="n"/>
+      <c r="BM30" s="7" t="n"/>
+      <c r="BN30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -29292,24 +30768,60 @@
       <c r="AD31" s="7" t="n"/>
       <c r="AE31" s="7" t="n"/>
       <c r="AF31" s="7" t="n"/>
-      <c r="AG31" s="7" t="inlineStr">
-        <is>
-          <t>INVESTIGATOR</t>
-        </is>
-      </c>
-      <c r="AH31" s="7" t="inlineStr">
-        <is>
-          <t>C25936</t>
-        </is>
-      </c>
-      <c r="AI31" s="7" t="inlineStr">
-        <is>
-          <t>EVAL</t>
-        </is>
-      </c>
+      <c r="AG31" s="7" t="n"/>
+      <c r="AH31" s="7" t="n"/>
+      <c r="AI31" s="7" t="n"/>
       <c r="AJ31" s="7" t="n"/>
       <c r="AK31" s="7" t="n"/>
       <c r="AL31" s="7" t="n"/>
+      <c r="AM31" s="7" t="n"/>
+      <c r="AN31" s="7" t="n"/>
+      <c r="AO31" s="7" t="n"/>
+      <c r="AP31" s="7" t="n"/>
+      <c r="AQ31" s="7" t="n"/>
+      <c r="AR31" s="7" t="n"/>
+      <c r="AS31" s="7" t="n"/>
+      <c r="AT31" s="7" t="n"/>
+      <c r="AU31" s="7" t="n"/>
+      <c r="AV31" s="7" t="n"/>
+      <c r="AW31" s="7" t="n"/>
+      <c r="AX31" s="7" t="n"/>
+      <c r="AY31" s="7" t="n"/>
+      <c r="AZ31" s="7" t="n"/>
+      <c r="BA31" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB31" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC31" s="7" t="n"/>
+      <c r="BD31" s="7" t="n"/>
+      <c r="BE31" s="7" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR</t>
+        </is>
+      </c>
+      <c r="BF31" s="7" t="inlineStr">
+        <is>
+          <t>C25936</t>
+        </is>
+      </c>
+      <c r="BG31" s="7" t="inlineStr">
+        <is>
+          <t>EVAL</t>
+        </is>
+      </c>
+      <c r="BH31" s="7" t="n"/>
+      <c r="BI31" s="7" t="n"/>
+      <c r="BJ31" s="7" t="n"/>
+      <c r="BK31" s="7" t="n"/>
+      <c r="BL31" s="7" t="n"/>
+      <c r="BM31" s="7" t="n"/>
+      <c r="BN31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -29416,16 +30928,64 @@
       <c r="Z32" s="7" t="n"/>
       <c r="AA32" s="7" t="n"/>
       <c r="AB32" s="7" t="n"/>
-      <c r="AC32" s="7" t="n"/>
+      <c r="AC32" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD32" s="7" t="n"/>
       <c r="AE32" s="7" t="n"/>
       <c r="AF32" s="7" t="n"/>
       <c r="AG32" s="7" t="n"/>
-      <c r="AH32" s="7" t="n"/>
+      <c r="AH32" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI32" s="7" t="n"/>
-      <c r="AJ32" s="7" t="n"/>
+      <c r="AJ32" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK32" s="7" t="n"/>
       <c r="AL32" s="7" t="n"/>
+      <c r="AM32" s="7" t="n"/>
+      <c r="AN32" s="7" t="n"/>
+      <c r="AO32" s="7" t="n"/>
+      <c r="AP32" s="7" t="n"/>
+      <c r="AQ32" s="7" t="n"/>
+      <c r="AR32" s="7" t="n"/>
+      <c r="AS32" s="7" t="n"/>
+      <c r="AT32" s="7" t="n"/>
+      <c r="AU32" s="7" t="n"/>
+      <c r="AV32" s="7" t="n"/>
+      <c r="AW32" s="7" t="n"/>
+      <c r="AX32" s="7" t="n"/>
+      <c r="AY32" s="7" t="n"/>
+      <c r="AZ32" s="7" t="n"/>
+      <c r="BA32" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB32" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC32" s="7" t="n"/>
+      <c r="BD32" s="7" t="n"/>
+      <c r="BE32" s="7" t="n"/>
+      <c r="BF32" s="7" t="n"/>
+      <c r="BG32" s="7" t="n"/>
+      <c r="BH32" s="7" t="n"/>
+      <c r="BI32" s="7" t="n"/>
+      <c r="BJ32" s="7" t="n"/>
+      <c r="BK32" s="7" t="n"/>
+      <c r="BL32" s="7" t="n"/>
+      <c r="BM32" s="7" t="n"/>
+      <c r="BN32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -29532,16 +31092,64 @@
       <c r="Z33" s="7" t="n"/>
       <c r="AA33" s="7" t="n"/>
       <c r="AB33" s="7" t="n"/>
-      <c r="AC33" s="7" t="n"/>
+      <c r="AC33" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD33" s="7" t="n"/>
       <c r="AE33" s="7" t="n"/>
       <c r="AF33" s="7" t="n"/>
       <c r="AG33" s="7" t="n"/>
-      <c r="AH33" s="7" t="n"/>
+      <c r="AH33" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI33" s="7" t="n"/>
-      <c r="AJ33" s="7" t="n"/>
+      <c r="AJ33" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK33" s="7" t="n"/>
       <c r="AL33" s="7" t="n"/>
+      <c r="AM33" s="7" t="n"/>
+      <c r="AN33" s="7" t="n"/>
+      <c r="AO33" s="7" t="n"/>
+      <c r="AP33" s="7" t="n"/>
+      <c r="AQ33" s="7" t="n"/>
+      <c r="AR33" s="7" t="n"/>
+      <c r="AS33" s="7" t="n"/>
+      <c r="AT33" s="7" t="n"/>
+      <c r="AU33" s="7" t="n"/>
+      <c r="AV33" s="7" t="n"/>
+      <c r="AW33" s="7" t="n"/>
+      <c r="AX33" s="7" t="n"/>
+      <c r="AY33" s="7" t="n"/>
+      <c r="AZ33" s="7" t="n"/>
+      <c r="BA33" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB33" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC33" s="7" t="n"/>
+      <c r="BD33" s="7" t="n"/>
+      <c r="BE33" s="7" t="n"/>
+      <c r="BF33" s="7" t="n"/>
+      <c r="BG33" s="7" t="n"/>
+      <c r="BH33" s="7" t="n"/>
+      <c r="BI33" s="7" t="n"/>
+      <c r="BJ33" s="7" t="n"/>
+      <c r="BK33" s="7" t="n"/>
+      <c r="BL33" s="7" t="n"/>
+      <c r="BM33" s="7" t="n"/>
+      <c r="BN33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -29648,16 +31256,64 @@
       <c r="Z34" s="7" t="n"/>
       <c r="AA34" s="7" t="n"/>
       <c r="AB34" s="7" t="n"/>
-      <c r="AC34" s="7" t="n"/>
+      <c r="AC34" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD34" s="7" t="n"/>
       <c r="AE34" s="7" t="n"/>
       <c r="AF34" s="7" t="n"/>
       <c r="AG34" s="7" t="n"/>
-      <c r="AH34" s="7" t="n"/>
+      <c r="AH34" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI34" s="7" t="n"/>
-      <c r="AJ34" s="7" t="n"/>
+      <c r="AJ34" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK34" s="7" t="n"/>
       <c r="AL34" s="7" t="n"/>
+      <c r="AM34" s="7" t="n"/>
+      <c r="AN34" s="7" t="n"/>
+      <c r="AO34" s="7" t="n"/>
+      <c r="AP34" s="7" t="n"/>
+      <c r="AQ34" s="7" t="n"/>
+      <c r="AR34" s="7" t="n"/>
+      <c r="AS34" s="7" t="n"/>
+      <c r="AT34" s="7" t="n"/>
+      <c r="AU34" s="7" t="n"/>
+      <c r="AV34" s="7" t="n"/>
+      <c r="AW34" s="7" t="n"/>
+      <c r="AX34" s="7" t="n"/>
+      <c r="AY34" s="7" t="n"/>
+      <c r="AZ34" s="7" t="n"/>
+      <c r="BA34" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB34" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC34" s="7" t="n"/>
+      <c r="BD34" s="7" t="n"/>
+      <c r="BE34" s="7" t="n"/>
+      <c r="BF34" s="7" t="n"/>
+      <c r="BG34" s="7" t="n"/>
+      <c r="BH34" s="7" t="n"/>
+      <c r="BI34" s="7" t="n"/>
+      <c r="BJ34" s="7" t="n"/>
+      <c r="BK34" s="7" t="n"/>
+      <c r="BL34" s="7" t="n"/>
+      <c r="BM34" s="7" t="n"/>
+      <c r="BN34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -29764,16 +31420,64 @@
       <c r="Z35" s="7" t="n"/>
       <c r="AA35" s="7" t="n"/>
       <c r="AB35" s="7" t="n"/>
-      <c r="AC35" s="7" t="n"/>
+      <c r="AC35" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD35" s="7" t="n"/>
       <c r="AE35" s="7" t="n"/>
       <c r="AF35" s="7" t="n"/>
       <c r="AG35" s="7" t="n"/>
-      <c r="AH35" s="7" t="n"/>
+      <c r="AH35" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI35" s="7" t="n"/>
-      <c r="AJ35" s="7" t="n"/>
+      <c r="AJ35" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK35" s="7" t="n"/>
       <c r="AL35" s="7" t="n"/>
+      <c r="AM35" s="7" t="n"/>
+      <c r="AN35" s="7" t="n"/>
+      <c r="AO35" s="7" t="n"/>
+      <c r="AP35" s="7" t="n"/>
+      <c r="AQ35" s="7" t="n"/>
+      <c r="AR35" s="7" t="n"/>
+      <c r="AS35" s="7" t="n"/>
+      <c r="AT35" s="7" t="n"/>
+      <c r="AU35" s="7" t="n"/>
+      <c r="AV35" s="7" t="n"/>
+      <c r="AW35" s="7" t="n"/>
+      <c r="AX35" s="7" t="n"/>
+      <c r="AY35" s="7" t="n"/>
+      <c r="AZ35" s="7" t="n"/>
+      <c r="BA35" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB35" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC35" s="7" t="n"/>
+      <c r="BD35" s="7" t="n"/>
+      <c r="BE35" s="7" t="n"/>
+      <c r="BF35" s="7" t="n"/>
+      <c r="BG35" s="7" t="n"/>
+      <c r="BH35" s="7" t="n"/>
+      <c r="BI35" s="7" t="n"/>
+      <c r="BJ35" s="7" t="n"/>
+      <c r="BK35" s="7" t="n"/>
+      <c r="BL35" s="7" t="n"/>
+      <c r="BM35" s="7" t="n"/>
+      <c r="BN35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -29880,16 +31584,64 @@
       <c r="Z36" s="7" t="n"/>
       <c r="AA36" s="7" t="n"/>
       <c r="AB36" s="7" t="n"/>
-      <c r="AC36" s="7" t="n"/>
+      <c r="AC36" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD36" s="7" t="n"/>
       <c r="AE36" s="7" t="n"/>
       <c r="AF36" s="7" t="n"/>
       <c r="AG36" s="7" t="n"/>
-      <c r="AH36" s="7" t="n"/>
+      <c r="AH36" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI36" s="7" t="n"/>
-      <c r="AJ36" s="7" t="n"/>
+      <c r="AJ36" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK36" s="7" t="n"/>
       <c r="AL36" s="7" t="n"/>
+      <c r="AM36" s="7" t="n"/>
+      <c r="AN36" s="7" t="n"/>
+      <c r="AO36" s="7" t="n"/>
+      <c r="AP36" s="7" t="n"/>
+      <c r="AQ36" s="7" t="n"/>
+      <c r="AR36" s="7" t="n"/>
+      <c r="AS36" s="7" t="n"/>
+      <c r="AT36" s="7" t="n"/>
+      <c r="AU36" s="7" t="n"/>
+      <c r="AV36" s="7" t="n"/>
+      <c r="AW36" s="7" t="n"/>
+      <c r="AX36" s="7" t="n"/>
+      <c r="AY36" s="7" t="n"/>
+      <c r="AZ36" s="7" t="n"/>
+      <c r="BA36" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB36" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC36" s="7" t="n"/>
+      <c r="BD36" s="7" t="n"/>
+      <c r="BE36" s="7" t="n"/>
+      <c r="BF36" s="7" t="n"/>
+      <c r="BG36" s="7" t="n"/>
+      <c r="BH36" s="7" t="n"/>
+      <c r="BI36" s="7" t="n"/>
+      <c r="BJ36" s="7" t="n"/>
+      <c r="BK36" s="7" t="n"/>
+      <c r="BL36" s="7" t="n"/>
+      <c r="BM36" s="7" t="n"/>
+      <c r="BN36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -29996,16 +31748,64 @@
       <c r="Z37" s="7" t="n"/>
       <c r="AA37" s="7" t="n"/>
       <c r="AB37" s="7" t="n"/>
-      <c r="AC37" s="7" t="n"/>
+      <c r="AC37" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD37" s="7" t="n"/>
       <c r="AE37" s="7" t="n"/>
       <c r="AF37" s="7" t="n"/>
       <c r="AG37" s="7" t="n"/>
-      <c r="AH37" s="7" t="n"/>
+      <c r="AH37" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI37" s="7" t="n"/>
-      <c r="AJ37" s="7" t="n"/>
+      <c r="AJ37" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK37" s="7" t="n"/>
       <c r="AL37" s="7" t="n"/>
+      <c r="AM37" s="7" t="n"/>
+      <c r="AN37" s="7" t="n"/>
+      <c r="AO37" s="7" t="n"/>
+      <c r="AP37" s="7" t="n"/>
+      <c r="AQ37" s="7" t="n"/>
+      <c r="AR37" s="7" t="n"/>
+      <c r="AS37" s="7" t="n"/>
+      <c r="AT37" s="7" t="n"/>
+      <c r="AU37" s="7" t="n"/>
+      <c r="AV37" s="7" t="n"/>
+      <c r="AW37" s="7" t="n"/>
+      <c r="AX37" s="7" t="n"/>
+      <c r="AY37" s="7" t="n"/>
+      <c r="AZ37" s="7" t="n"/>
+      <c r="BA37" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB37" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC37" s="7" t="n"/>
+      <c r="BD37" s="7" t="n"/>
+      <c r="BE37" s="7" t="n"/>
+      <c r="BF37" s="7" t="n"/>
+      <c r="BG37" s="7" t="n"/>
+      <c r="BH37" s="7" t="n"/>
+      <c r="BI37" s="7" t="n"/>
+      <c r="BJ37" s="7" t="n"/>
+      <c r="BK37" s="7" t="n"/>
+      <c r="BL37" s="7" t="n"/>
+      <c r="BM37" s="7" t="n"/>
+      <c r="BN37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -30112,16 +31912,64 @@
       <c r="Z38" s="7" t="n"/>
       <c r="AA38" s="7" t="n"/>
       <c r="AB38" s="7" t="n"/>
-      <c r="AC38" s="7" t="n"/>
+      <c r="AC38" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD38" s="7" t="n"/>
       <c r="AE38" s="7" t="n"/>
       <c r="AF38" s="7" t="n"/>
       <c r="AG38" s="7" t="n"/>
-      <c r="AH38" s="7" t="n"/>
+      <c r="AH38" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI38" s="7" t="n"/>
-      <c r="AJ38" s="7" t="n"/>
+      <c r="AJ38" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK38" s="7" t="n"/>
       <c r="AL38" s="7" t="n"/>
+      <c r="AM38" s="7" t="n"/>
+      <c r="AN38" s="7" t="n"/>
+      <c r="AO38" s="7" t="n"/>
+      <c r="AP38" s="7" t="n"/>
+      <c r="AQ38" s="7" t="n"/>
+      <c r="AR38" s="7" t="n"/>
+      <c r="AS38" s="7" t="n"/>
+      <c r="AT38" s="7" t="n"/>
+      <c r="AU38" s="7" t="n"/>
+      <c r="AV38" s="7" t="n"/>
+      <c r="AW38" s="7" t="n"/>
+      <c r="AX38" s="7" t="n"/>
+      <c r="AY38" s="7" t="n"/>
+      <c r="AZ38" s="7" t="n"/>
+      <c r="BA38" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB38" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC38" s="7" t="n"/>
+      <c r="BD38" s="7" t="n"/>
+      <c r="BE38" s="7" t="n"/>
+      <c r="BF38" s="7" t="n"/>
+      <c r="BG38" s="7" t="n"/>
+      <c r="BH38" s="7" t="n"/>
+      <c r="BI38" s="7" t="n"/>
+      <c r="BJ38" s="7" t="n"/>
+      <c r="BK38" s="7" t="n"/>
+      <c r="BL38" s="7" t="n"/>
+      <c r="BM38" s="7" t="n"/>
+      <c r="BN38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -30228,16 +32076,64 @@
       <c r="Z39" s="7" t="n"/>
       <c r="AA39" s="7" t="n"/>
       <c r="AB39" s="7" t="n"/>
-      <c r="AC39" s="7" t="n"/>
+      <c r="AC39" s="7" t="inlineStr">
+        <is>
+          <t>0 No visible or palpable contraction;1 Visible or palpable contraction without motion;2 Full range of motion, gravity eliminated;3 Full range of motion against gravity;4 Full range of motion against gravity, moderate resistance;5 Full range of motion against gravity, maximal resistance</t>
+        </is>
+      </c>
       <c r="AD39" s="7" t="n"/>
       <c r="AE39" s="7" t="n"/>
       <c r="AF39" s="7" t="n"/>
       <c r="AG39" s="7" t="n"/>
-      <c r="AH39" s="7" t="n"/>
+      <c r="AH39" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI39" s="7" t="n"/>
-      <c r="AJ39" s="7" t="n"/>
+      <c r="AJ39" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK39" s="7" t="n"/>
       <c r="AL39" s="7" t="n"/>
+      <c r="AM39" s="7" t="n"/>
+      <c r="AN39" s="7" t="n"/>
+      <c r="AO39" s="7" t="n"/>
+      <c r="AP39" s="7" t="n"/>
+      <c r="AQ39" s="7" t="n"/>
+      <c r="AR39" s="7" t="n"/>
+      <c r="AS39" s="7" t="n"/>
+      <c r="AT39" s="7" t="n"/>
+      <c r="AU39" s="7" t="n"/>
+      <c r="AV39" s="7" t="n"/>
+      <c r="AW39" s="7" t="n"/>
+      <c r="AX39" s="7" t="n"/>
+      <c r="AY39" s="7" t="n"/>
+      <c r="AZ39" s="7" t="n"/>
+      <c r="BA39" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB39" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC39" s="7" t="n"/>
+      <c r="BD39" s="7" t="n"/>
+      <c r="BE39" s="7" t="n"/>
+      <c r="BF39" s="7" t="n"/>
+      <c r="BG39" s="7" t="n"/>
+      <c r="BH39" s="7" t="n"/>
+      <c r="BI39" s="7" t="n"/>
+      <c r="BJ39" s="7" t="n"/>
+      <c r="BK39" s="7" t="n"/>
+      <c r="BL39" s="7" t="n"/>
+      <c r="BM39" s="7" t="n"/>
+      <c r="BN39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -30339,20 +32235,20 @@
       <c r="U40" s="7" t="n"/>
       <c r="V40" s="7" t="n"/>
       <c r="W40" s="7" t="n"/>
-      <c r="X40" s="7" t="n"/>
-      <c r="Y40" s="7" t="n"/>
+      <c r="X40" s="7" t="inlineStr">
+        <is>
+          <t>DYNAMOMETRY;PINCH DYNAMOMETRY</t>
+        </is>
+      </c>
+      <c r="Y40" s="7" t="inlineStr">
+        <is>
+          <t>C161407;</t>
+        </is>
+      </c>
       <c r="Z40" s="7" t="n"/>
-      <c r="AA40" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA40" s="7" t="n"/>
       <c r="AB40" s="7" t="n"/>
-      <c r="AC40" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC40" s="7" t="n"/>
       <c r="AD40" s="7" t="n"/>
       <c r="AE40" s="7" t="n"/>
       <c r="AF40" s="7" t="n"/>
@@ -30362,6 +32258,58 @@
       <c r="AJ40" s="7" t="n"/>
       <c r="AK40" s="7" t="n"/>
       <c r="AL40" s="7" t="n"/>
+      <c r="AM40" s="7" t="n"/>
+      <c r="AN40" s="7" t="n"/>
+      <c r="AO40" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB;mmHg;Newton</t>
+        </is>
+      </c>
+      <c r="AP40" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531;C49670;C42546</t>
+        </is>
+      </c>
+      <c r="AQ40" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR40" s="7" t="n"/>
+      <c r="AS40" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT40" s="7" t="n"/>
+      <c r="AU40" s="7" t="n"/>
+      <c r="AV40" s="7" t="n"/>
+      <c r="AW40" s="7" t="n"/>
+      <c r="AX40" s="7" t="n"/>
+      <c r="AY40" s="7" t="n"/>
+      <c r="AZ40" s="7" t="n"/>
+      <c r="BA40" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB40" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC40" s="7" t="n"/>
+      <c r="BD40" s="7" t="n"/>
+      <c r="BE40" s="7" t="n"/>
+      <c r="BF40" s="7" t="n"/>
+      <c r="BG40" s="7" t="n"/>
+      <c r="BH40" s="7" t="n"/>
+      <c r="BI40" s="7" t="n"/>
+      <c r="BJ40" s="7" t="n"/>
+      <c r="BK40" s="7" t="n"/>
+      <c r="BL40" s="7" t="n"/>
+      <c r="BM40" s="7" t="n"/>
+      <c r="BN40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -30463,36 +32411,12 @@
       <c r="U41" s="7" t="n"/>
       <c r="V41" s="7" t="n"/>
       <c r="W41" s="7" t="n"/>
-      <c r="X41" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="Y41" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="Z41" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA41" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="AB41" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="AC41" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="X41" s="7" t="n"/>
+      <c r="Y41" s="7" t="n"/>
+      <c r="Z41" s="7" t="n"/>
+      <c r="AA41" s="7" t="n"/>
+      <c r="AB41" s="7" t="n"/>
+      <c r="AC41" s="7" t="n"/>
       <c r="AD41" s="7" t="n"/>
       <c r="AE41" s="7" t="n"/>
       <c r="AF41" s="7" t="n"/>
@@ -30501,7 +32425,67 @@
       <c r="AI41" s="7" t="n"/>
       <c r="AJ41" s="7" t="n"/>
       <c r="AK41" s="7" t="n"/>
-      <c r="AL41" s="7" t="n"/>
+      <c r="AL41" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AM41" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AN41" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO41" s="7" t="n"/>
+      <c r="AP41" s="7" t="n"/>
+      <c r="AQ41" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AR41" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AS41" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT41" s="7" t="n"/>
+      <c r="AU41" s="7" t="n"/>
+      <c r="AV41" s="7" t="n"/>
+      <c r="AW41" s="7" t="n"/>
+      <c r="AX41" s="7" t="n"/>
+      <c r="AY41" s="7" t="n"/>
+      <c r="AZ41" s="7" t="n"/>
+      <c r="BA41" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB41" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC41" s="7" t="n"/>
+      <c r="BD41" s="7" t="n"/>
+      <c r="BE41" s="7" t="n"/>
+      <c r="BF41" s="7" t="n"/>
+      <c r="BG41" s="7" t="n"/>
+      <c r="BH41" s="7" t="n"/>
+      <c r="BI41" s="7" t="n"/>
+      <c r="BJ41" s="7" t="n"/>
+      <c r="BK41" s="7" t="n"/>
+      <c r="BL41" s="7" t="n"/>
+      <c r="BM41" s="7" t="n"/>
+      <c r="BN41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -30603,36 +32587,12 @@
       <c r="U42" s="7" t="n"/>
       <c r="V42" s="7" t="n"/>
       <c r="W42" s="7" t="n"/>
-      <c r="X42" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="Y42" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="Z42" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA42" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="AB42" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="AC42" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="X42" s="7" t="n"/>
+      <c r="Y42" s="7" t="n"/>
+      <c r="Z42" s="7" t="n"/>
+      <c r="AA42" s="7" t="n"/>
+      <c r="AB42" s="7" t="n"/>
+      <c r="AC42" s="7" t="n"/>
       <c r="AD42" s="7" t="n"/>
       <c r="AE42" s="7" t="n"/>
       <c r="AF42" s="7" t="n"/>
@@ -30641,7 +32601,67 @@
       <c r="AI42" s="7" t="n"/>
       <c r="AJ42" s="7" t="n"/>
       <c r="AK42" s="7" t="n"/>
-      <c r="AL42" s="7" t="n"/>
+      <c r="AL42" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AM42" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AN42" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO42" s="7" t="n"/>
+      <c r="AP42" s="7" t="n"/>
+      <c r="AQ42" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AR42" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AS42" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT42" s="7" t="n"/>
+      <c r="AU42" s="7" t="n"/>
+      <c r="AV42" s="7" t="n"/>
+      <c r="AW42" s="7" t="n"/>
+      <c r="AX42" s="7" t="n"/>
+      <c r="AY42" s="7" t="n"/>
+      <c r="AZ42" s="7" t="n"/>
+      <c r="BA42" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB42" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC42" s="7" t="n"/>
+      <c r="BD42" s="7" t="n"/>
+      <c r="BE42" s="7" t="n"/>
+      <c r="BF42" s="7" t="n"/>
+      <c r="BG42" s="7" t="n"/>
+      <c r="BH42" s="7" t="n"/>
+      <c r="BI42" s="7" t="n"/>
+      <c r="BJ42" s="7" t="n"/>
+      <c r="BK42" s="7" t="n"/>
+      <c r="BL42" s="7" t="n"/>
+      <c r="BM42" s="7" t="n"/>
+      <c r="BN42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -30743,36 +32763,12 @@
       <c r="U43" s="7" t="n"/>
       <c r="V43" s="7" t="n"/>
       <c r="W43" s="7" t="n"/>
-      <c r="X43" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="Y43" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="Z43" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AA43" s="7" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="AB43" s="7" t="inlineStr">
-        <is>
-          <t>C68667</t>
-        </is>
-      </c>
-      <c r="AC43" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="X43" s="7" t="n"/>
+      <c r="Y43" s="7" t="n"/>
+      <c r="Z43" s="7" t="n"/>
+      <c r="AA43" s="7" t="n"/>
+      <c r="AB43" s="7" t="n"/>
+      <c r="AC43" s="7" t="n"/>
       <c r="AD43" s="7" t="n"/>
       <c r="AE43" s="7" t="n"/>
       <c r="AF43" s="7" t="n"/>
@@ -30781,7 +32777,67 @@
       <c r="AI43" s="7" t="n"/>
       <c r="AJ43" s="7" t="n"/>
       <c r="AK43" s="7" t="n"/>
-      <c r="AL43" s="7" t="n"/>
+      <c r="AL43" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AM43" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AN43" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AO43" s="7" t="n"/>
+      <c r="AP43" s="7" t="n"/>
+      <c r="AQ43" s="7" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="AR43" s="7" t="inlineStr">
+        <is>
+          <t>C68667</t>
+        </is>
+      </c>
+      <c r="AS43" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT43" s="7" t="n"/>
+      <c r="AU43" s="7" t="n"/>
+      <c r="AV43" s="7" t="n"/>
+      <c r="AW43" s="7" t="n"/>
+      <c r="AX43" s="7" t="n"/>
+      <c r="AY43" s="7" t="n"/>
+      <c r="AZ43" s="7" t="n"/>
+      <c r="BA43" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB43" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC43" s="7" t="n"/>
+      <c r="BD43" s="7" t="n"/>
+      <c r="BE43" s="7" t="n"/>
+      <c r="BF43" s="7" t="n"/>
+      <c r="BG43" s="7" t="n"/>
+      <c r="BH43" s="7" t="n"/>
+      <c r="BI43" s="7" t="n"/>
+      <c r="BJ43" s="7" t="n"/>
+      <c r="BK43" s="7" t="n"/>
+      <c r="BL43" s="7" t="n"/>
+      <c r="BM43" s="7" t="n"/>
+      <c r="BN43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -30883,21 +32939,77 @@
       <c r="U44" s="7" t="n"/>
       <c r="V44" s="7" t="n"/>
       <c r="W44" s="7" t="n"/>
-      <c r="X44" s="7" t="n"/>
-      <c r="Y44" s="7" t="n"/>
+      <c r="X44" s="7" t="inlineStr">
+        <is>
+          <t>X-RAY;MRI</t>
+        </is>
+      </c>
+      <c r="Y44" s="7" t="inlineStr">
+        <is>
+          <t>C38101;C16809</t>
+        </is>
+      </c>
       <c r="Z44" s="7" t="n"/>
       <c r="AA44" s="7" t="n"/>
       <c r="AB44" s="7" t="n"/>
-      <c r="AC44" s="7" t="n"/>
+      <c r="AC44" s="7" t="inlineStr">
+        <is>
+          <t>0 Normal;0.5 Subtle loss of cortical continuity or equivocal findings of bone erosion;1.0 mild: definite but small erosions involving less than 25% of the articular bone;1.5 Mild-to-moderate: small-medium erosions involving less than 25% of the articular bone;2.0 Moderate: medium-large erosions involving approximately 26-50% of the articular bone;2.5 Moderate-to-severe: erosion of approximately 51-75% of the articular bone;3.0 Severe: erosion of approximately 76-90% of the articular bone;3.5 Very severe: erosion of 100% of the articular bone</t>
+        </is>
+      </c>
       <c r="AD44" s="7" t="n"/>
       <c r="AE44" s="7" t="n"/>
       <c r="AF44" s="7" t="n"/>
       <c r="AG44" s="7" t="n"/>
-      <c r="AH44" s="7" t="n"/>
+      <c r="AH44" s="7" t="inlineStr">
+        <is>
+          <t>0;0.5;1.0;2.0;2.5;3.0;3.5</t>
+        </is>
+      </c>
       <c r="AI44" s="7" t="n"/>
-      <c r="AJ44" s="7" t="n"/>
+      <c r="AJ44" s="7" t="inlineStr">
+        <is>
+          <t>0;0.5;1.0;2.0;2.5;3.0;3.5</t>
+        </is>
+      </c>
       <c r="AK44" s="7" t="n"/>
       <c r="AL44" s="7" t="n"/>
+      <c r="AM44" s="7" t="n"/>
+      <c r="AN44" s="7" t="n"/>
+      <c r="AO44" s="7" t="n"/>
+      <c r="AP44" s="7" t="n"/>
+      <c r="AQ44" s="7" t="n"/>
+      <c r="AR44" s="7" t="n"/>
+      <c r="AS44" s="7" t="n"/>
+      <c r="AT44" s="7" t="n"/>
+      <c r="AU44" s="7" t="n"/>
+      <c r="AV44" s="7" t="n"/>
+      <c r="AW44" s="7" t="n"/>
+      <c r="AX44" s="7" t="n"/>
+      <c r="AY44" s="7" t="n"/>
+      <c r="AZ44" s="7" t="n"/>
+      <c r="BA44" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB44" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC44" s="7" t="n"/>
+      <c r="BD44" s="7" t="n"/>
+      <c r="BE44" s="7" t="n"/>
+      <c r="BF44" s="7" t="n"/>
+      <c r="BG44" s="7" t="n"/>
+      <c r="BH44" s="7" t="n"/>
+      <c r="BI44" s="7" t="n"/>
+      <c r="BJ44" s="7" t="n"/>
+      <c r="BK44" s="7" t="n"/>
+      <c r="BL44" s="7" t="n"/>
+      <c r="BM44" s="7" t="n"/>
+      <c r="BN44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -30999,21 +33111,101 @@
       <c r="U45" s="7" t="n"/>
       <c r="V45" s="7" t="n"/>
       <c r="W45" s="7" t="n"/>
-      <c r="X45" s="7" t="n"/>
-      <c r="Y45" s="7" t="n"/>
+      <c r="X45" s="7" t="inlineStr">
+        <is>
+          <t>X-RAY;MRI</t>
+        </is>
+      </c>
+      <c r="Y45" s="7" t="inlineStr">
+        <is>
+          <t>C38101;C16809</t>
+        </is>
+      </c>
       <c r="Z45" s="7" t="n"/>
       <c r="AA45" s="7" t="n"/>
       <c r="AB45" s="7" t="n"/>
-      <c r="AC45" s="7" t="n"/>
+      <c r="AC45" s="7" t="inlineStr">
+        <is>
+          <t>0 Normal;0.5 Questionable;1.0 Mild, definite small erosions, &lt;25% of articular bone;1.5 Mild-moderate, definite medium erosion;2.0 Moderate, definite erosion, 26-50% of articular bone;2.5 Moderate-severe, definite erosion, 51-75% of articular bone;3.0 Severe, definite erosion, 76-90% of articular bone;3.5 Very severe, definite erosion, nearly complete loss of articular bone</t>
+        </is>
+      </c>
       <c r="AD45" s="7" t="n"/>
       <c r="AE45" s="7" t="n"/>
       <c r="AF45" s="7" t="n"/>
       <c r="AG45" s="7" t="n"/>
-      <c r="AH45" s="7" t="n"/>
+      <c r="AH45" s="7" t="inlineStr">
+        <is>
+          <t>0;0.5;1.0;2.0;2.5;3.0;3.5</t>
+        </is>
+      </c>
       <c r="AI45" s="7" t="n"/>
-      <c r="AJ45" s="7" t="n"/>
+      <c r="AJ45" s="7" t="inlineStr">
+        <is>
+          <t>0;0.5;1.0;2.0;2.5;3.0;3.5</t>
+        </is>
+      </c>
       <c r="AK45" s="7" t="n"/>
       <c r="AL45" s="7" t="n"/>
+      <c r="AM45" s="7" t="n"/>
+      <c r="AN45" s="7" t="n"/>
+      <c r="AO45" s="7" t="n"/>
+      <c r="AP45" s="7" t="n"/>
+      <c r="AQ45" s="7" t="n"/>
+      <c r="AR45" s="7" t="n"/>
+      <c r="AS45" s="7" t="n"/>
+      <c r="AT45" s="7" t="n"/>
+      <c r="AU45" s="7" t="n"/>
+      <c r="AV45" s="7" t="n"/>
+      <c r="AW45" s="7" t="n"/>
+      <c r="AX45" s="7" t="n"/>
+      <c r="AY45" s="7" t="inlineStr">
+        <is>
+          <t>INTERPHALANGEAL JOINT 1 OF THE FOOT;METATARSOPHALANGEAL JOINT 1;METATARSOPHALANGEAL JOINT 2;METATARSOPHALANGEAL JOINT 3;METATARSOPHALANGEAL JOINT 4;METATARSOPHALANGEAL JOINT 5</t>
+        </is>
+      </c>
+      <c r="AZ45" s="7" t="inlineStr">
+        <is>
+          <t>C114200;C102321;C102322;C102323;C102324;C102325</t>
+        </is>
+      </c>
+      <c r="BA45" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB45" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC45" s="7" t="n"/>
+      <c r="BD45" s="7" t="n"/>
+      <c r="BE45" s="7" t="n"/>
+      <c r="BF45" s="7" t="n"/>
+      <c r="BG45" s="7" t="n"/>
+      <c r="BH45" s="7" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR;INDEPENDENT ASSESSOR</t>
+        </is>
+      </c>
+      <c r="BI45" s="7" t="inlineStr">
+        <is>
+          <t>C25936;C78720</t>
+        </is>
+      </c>
+      <c r="BJ45" s="7" t="inlineStr">
+        <is>
+          <t>READER 1;READER 2</t>
+        </is>
+      </c>
+      <c r="BK45" s="7" t="inlineStr">
+        <is>
+          <t>C94532;C94533</t>
+        </is>
+      </c>
+      <c r="BL45" s="7" t="n"/>
+      <c r="BM45" s="7" t="n"/>
+      <c r="BN45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -31115,21 +33307,101 @@
       <c r="U46" s="7" t="n"/>
       <c r="V46" s="7" t="n"/>
       <c r="W46" s="7" t="n"/>
-      <c r="X46" s="7" t="n"/>
-      <c r="Y46" s="7" t="n"/>
+      <c r="X46" s="7" t="inlineStr">
+        <is>
+          <t>X-RAY;MRI</t>
+        </is>
+      </c>
+      <c r="Y46" s="7" t="inlineStr">
+        <is>
+          <t>C38101;C16809</t>
+        </is>
+      </c>
       <c r="Z46" s="7" t="n"/>
       <c r="AA46" s="7" t="n"/>
       <c r="AB46" s="7" t="n"/>
-      <c r="AC46" s="7" t="n"/>
+      <c r="AC46" s="7" t="inlineStr">
+        <is>
+          <t>0 Normal;0.5 Questionable;1.0 Mild, definite small erosions, &lt;25% of articular bone;1.5 Mild-moderate, definite medium erosion;2.0 Moderate, definite erosion, 26-50% of articular bone;2.5 Moderate-severe, definite erosion, 51-75% of articular bone;3.0 Severe, definite erosion, 76-90% of articular bone;3.5 Very severe, definite erosion, nearly complete loss of articular bone</t>
+        </is>
+      </c>
       <c r="AD46" s="7" t="n"/>
       <c r="AE46" s="7" t="n"/>
       <c r="AF46" s="7" t="n"/>
       <c r="AG46" s="7" t="n"/>
-      <c r="AH46" s="7" t="n"/>
+      <c r="AH46" s="7" t="inlineStr">
+        <is>
+          <t>0;0.5;1.0;2.0;2.5;3.0;3.5</t>
+        </is>
+      </c>
       <c r="AI46" s="7" t="n"/>
-      <c r="AJ46" s="7" t="n"/>
+      <c r="AJ46" s="7" t="inlineStr">
+        <is>
+          <t>0;0.5;1.0;2.0;2.5;3.0;3.5</t>
+        </is>
+      </c>
       <c r="AK46" s="7" t="n"/>
       <c r="AL46" s="7" t="n"/>
+      <c r="AM46" s="7" t="n"/>
+      <c r="AN46" s="7" t="n"/>
+      <c r="AO46" s="7" t="n"/>
+      <c r="AP46" s="7" t="n"/>
+      <c r="AQ46" s="7" t="n"/>
+      <c r="AR46" s="7" t="n"/>
+      <c r="AS46" s="7" t="n"/>
+      <c r="AT46" s="7" t="n"/>
+      <c r="AU46" s="7" t="n"/>
+      <c r="AV46" s="7" t="n"/>
+      <c r="AW46" s="7" t="n"/>
+      <c r="AX46" s="7" t="n"/>
+      <c r="AY46" s="7" t="inlineStr">
+        <is>
+          <t>INTERPHALANGEAL JOINT 1;PROXIMAL INTERPHALANGEAL JOINT 2 OF THE HAND;PROXIMAL INTERPHALANGEAL JOINT 3 OF THE HAND;PROXIMAL INTERPHALANGEAL;PROXIMAL INTERPHALANGEAL JOINT 5 OF THE HAND JOINT 4 OF THE HAND;METACARPOPHALANGEAL JOINT 1;METACARPOPHALANGEAL JOINT 2;METACARPOPHALANGEAL JOINT 4 METACARPOPHALANGEAL JOINT 3;METACARPOPHALANGEAL JOINT 4;METACARPOPHALANGEAL JOINT 5;CARPOMETACARPAL JOINTS 3-5;SCAPHOID-LUNATE-CAPITATE JOINT;RADIOCARPAL JOINT</t>
+        </is>
+      </c>
+      <c r="AZ46" s="7" t="inlineStr">
+        <is>
+          <t>C102301;C114194;C114195;;;C102316;C102317;;C102319;C102320;;C127677;</t>
+        </is>
+      </c>
+      <c r="BA46" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB46" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC46" s="7" t="n"/>
+      <c r="BD46" s="7" t="n"/>
+      <c r="BE46" s="7" t="n"/>
+      <c r="BF46" s="7" t="n"/>
+      <c r="BG46" s="7" t="n"/>
+      <c r="BH46" s="7" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR;INDEPENDENT ASSESSOR</t>
+        </is>
+      </c>
+      <c r="BI46" s="7" t="inlineStr">
+        <is>
+          <t>C25936;C78720</t>
+        </is>
+      </c>
+      <c r="BJ46" s="7" t="inlineStr">
+        <is>
+          <t>READER 1;READER 2</t>
+        </is>
+      </c>
+      <c r="BK46" s="7" t="inlineStr">
+        <is>
+          <t>C94532;C94533</t>
+        </is>
+      </c>
+      <c r="BL46" s="7" t="n"/>
+      <c r="BM46" s="7" t="n"/>
+      <c r="BN46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -31234,17 +33506,9 @@
       <c r="X47" s="7" t="n"/>
       <c r="Y47" s="7" t="n"/>
       <c r="Z47" s="7" t="n"/>
-      <c r="AA47" s="7" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
+      <c r="AA47" s="7" t="n"/>
       <c r="AB47" s="7" t="n"/>
-      <c r="AC47" s="7" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
+      <c r="AC47" s="7" t="n"/>
       <c r="AD47" s="7" t="n"/>
       <c r="AE47" s="7" t="n"/>
       <c r="AF47" s="7" t="n"/>
@@ -31254,6 +33518,58 @@
       <c r="AJ47" s="7" t="n"/>
       <c r="AK47" s="7" t="n"/>
       <c r="AL47" s="7" t="n"/>
+      <c r="AM47" s="7" t="n"/>
+      <c r="AN47" s="7" t="n"/>
+      <c r="AO47" s="7" t="inlineStr">
+        <is>
+          <t>Kg;g;LB;oz</t>
+        </is>
+      </c>
+      <c r="AP47" s="7" t="inlineStr">
+        <is>
+          <t>;C48155;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AQ47" s="7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="AR47" s="7" t="n"/>
+      <c r="AS47" s="7" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AT47" s="7" t="n"/>
+      <c r="AU47" s="7" t="n"/>
+      <c r="AV47" s="7" t="n"/>
+      <c r="AW47" s="7" t="n"/>
+      <c r="AX47" s="7" t="n"/>
+      <c r="AY47" s="7" t="n"/>
+      <c r="AZ47" s="7" t="n"/>
+      <c r="BA47" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB47" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC47" s="7" t="n"/>
+      <c r="BD47" s="7" t="n"/>
+      <c r="BE47" s="7" t="n"/>
+      <c r="BF47" s="7" t="n"/>
+      <c r="BG47" s="7" t="n"/>
+      <c r="BH47" s="7" t="n"/>
+      <c r="BI47" s="7" t="n"/>
+      <c r="BJ47" s="7" t="n"/>
+      <c r="BK47" s="7" t="n"/>
+      <c r="BL47" s="7" t="n"/>
+      <c r="BM47" s="7" t="n"/>
+      <c r="BN47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -31355,21 +33671,77 @@
       <c r="U48" s="7" t="n"/>
       <c r="V48" s="7" t="n"/>
       <c r="W48" s="7" t="n"/>
-      <c r="X48" s="7" t="n"/>
-      <c r="Y48" s="7" t="n"/>
+      <c r="X48" s="7" t="inlineStr">
+        <is>
+          <t>X-RAY;MRI</t>
+        </is>
+      </c>
+      <c r="Y48" s="7" t="inlineStr">
+        <is>
+          <t>C38101;C16809</t>
+        </is>
+      </c>
       <c r="Z48" s="7" t="n"/>
       <c r="AA48" s="7" t="n"/>
       <c r="AB48" s="7" t="n"/>
-      <c r="AC48" s="7" t="n"/>
+      <c r="AC48" s="7" t="inlineStr">
+        <is>
+          <t>0 Normal;1 Discrete erosions;2 Larger erosions;3 Larger erosions;4 Erosions extending over middle of the bone;5 Complete collapse</t>
+        </is>
+      </c>
       <c r="AD48" s="7" t="n"/>
       <c r="AE48" s="7" t="n"/>
       <c r="AF48" s="7" t="n"/>
       <c r="AG48" s="7" t="n"/>
-      <c r="AH48" s="7" t="n"/>
+      <c r="AH48" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AI48" s="7" t="n"/>
-      <c r="AJ48" s="7" t="n"/>
+      <c r="AJ48" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4;5</t>
+        </is>
+      </c>
       <c r="AK48" s="7" t="n"/>
       <c r="AL48" s="7" t="n"/>
+      <c r="AM48" s="7" t="n"/>
+      <c r="AN48" s="7" t="n"/>
+      <c r="AO48" s="7" t="n"/>
+      <c r="AP48" s="7" t="n"/>
+      <c r="AQ48" s="7" t="n"/>
+      <c r="AR48" s="7" t="n"/>
+      <c r="AS48" s="7" t="n"/>
+      <c r="AT48" s="7" t="n"/>
+      <c r="AU48" s="7" t="n"/>
+      <c r="AV48" s="7" t="n"/>
+      <c r="AW48" s="7" t="n"/>
+      <c r="AX48" s="7" t="n"/>
+      <c r="AY48" s="7" t="n"/>
+      <c r="AZ48" s="7" t="n"/>
+      <c r="BA48" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB48" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC48" s="7" t="n"/>
+      <c r="BD48" s="7" t="n"/>
+      <c r="BE48" s="7" t="n"/>
+      <c r="BF48" s="7" t="n"/>
+      <c r="BG48" s="7" t="n"/>
+      <c r="BH48" s="7" t="n"/>
+      <c r="BI48" s="7" t="n"/>
+      <c r="BJ48" s="7" t="n"/>
+      <c r="BK48" s="7" t="n"/>
+      <c r="BL48" s="7" t="n"/>
+      <c r="BM48" s="7" t="n"/>
+      <c r="BN48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -31471,21 +33843,77 @@
       <c r="U49" s="7" t="n"/>
       <c r="V49" s="7" t="n"/>
       <c r="W49" s="7" t="n"/>
-      <c r="X49" s="7" t="n"/>
-      <c r="Y49" s="7" t="n"/>
+      <c r="X49" s="7" t="inlineStr">
+        <is>
+          <t>X-RAY;MRI</t>
+        </is>
+      </c>
+      <c r="Y49" s="7" t="inlineStr">
+        <is>
+          <t>C38101;C16809</t>
+        </is>
+      </c>
       <c r="Z49" s="7" t="n"/>
       <c r="AA49" s="7" t="n"/>
       <c r="AB49" s="7" t="n"/>
-      <c r="AC49" s="7" t="n"/>
+      <c r="AC49" s="7" t="inlineStr">
+        <is>
+          <t>0 Normal;1 Focal or minimal and generalized narrowing;2 Generalized narrowing of less than 50%;3 Generalized narrowing greater than 50%, or subluxation;4 Ankylosis or complete dislocation</t>
+        </is>
+      </c>
       <c r="AD49" s="7" t="n"/>
       <c r="AE49" s="7" t="n"/>
       <c r="AF49" s="7" t="n"/>
       <c r="AG49" s="7" t="n"/>
-      <c r="AH49" s="7" t="n"/>
+      <c r="AH49" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4</t>
+        </is>
+      </c>
       <c r="AI49" s="7" t="n"/>
-      <c r="AJ49" s="7" t="n"/>
+      <c r="AJ49" s="7" t="inlineStr">
+        <is>
+          <t>0;1;2;3;4</t>
+        </is>
+      </c>
       <c r="AK49" s="7" t="n"/>
       <c r="AL49" s="7" t="n"/>
+      <c r="AM49" s="7" t="n"/>
+      <c r="AN49" s="7" t="n"/>
+      <c r="AO49" s="7" t="n"/>
+      <c r="AP49" s="7" t="n"/>
+      <c r="AQ49" s="7" t="n"/>
+      <c r="AR49" s="7" t="n"/>
+      <c r="AS49" s="7" t="n"/>
+      <c r="AT49" s="7" t="n"/>
+      <c r="AU49" s="7" t="n"/>
+      <c r="AV49" s="7" t="n"/>
+      <c r="AW49" s="7" t="n"/>
+      <c r="AX49" s="7" t="n"/>
+      <c r="AY49" s="7" t="n"/>
+      <c r="AZ49" s="7" t="n"/>
+      <c r="BA49" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB49" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC49" s="7" t="n"/>
+      <c r="BD49" s="7" t="n"/>
+      <c r="BE49" s="7" t="n"/>
+      <c r="BF49" s="7" t="n"/>
+      <c r="BG49" s="7" t="n"/>
+      <c r="BH49" s="7" t="n"/>
+      <c r="BI49" s="7" t="n"/>
+      <c r="BJ49" s="7" t="n"/>
+      <c r="BK49" s="7" t="n"/>
+      <c r="BL49" s="7" t="n"/>
+      <c r="BM49" s="7" t="n"/>
+      <c r="BN49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -31592,16 +34020,68 @@
       <c r="Z50" s="7" t="n"/>
       <c r="AA50" s="7" t="n"/>
       <c r="AB50" s="7" t="n"/>
-      <c r="AC50" s="7" t="n"/>
-      <c r="AD50" s="7" t="n"/>
+      <c r="AC50" s="7" t="inlineStr">
+        <is>
+          <t>N;Y;U</t>
+        </is>
+      </c>
+      <c r="AD50" s="7" t="inlineStr">
+        <is>
+          <t>C49487;C49488;C17998</t>
+        </is>
+      </c>
       <c r="AE50" s="7" t="n"/>
       <c r="AF50" s="7" t="n"/>
       <c r="AG50" s="7" t="n"/>
-      <c r="AH50" s="7" t="n"/>
-      <c r="AI50" s="7" t="n"/>
+      <c r="AH50" s="7" t="inlineStr">
+        <is>
+          <t>N;Y;U</t>
+        </is>
+      </c>
+      <c r="AI50" s="7" t="inlineStr">
+        <is>
+          <t>C49487;C49488;C17998</t>
+        </is>
+      </c>
       <c r="AJ50" s="7" t="n"/>
       <c r="AK50" s="7" t="n"/>
       <c r="AL50" s="7" t="n"/>
+      <c r="AM50" s="7" t="n"/>
+      <c r="AN50" s="7" t="n"/>
+      <c r="AO50" s="7" t="n"/>
+      <c r="AP50" s="7" t="n"/>
+      <c r="AQ50" s="7" t="n"/>
+      <c r="AR50" s="7" t="n"/>
+      <c r="AS50" s="7" t="n"/>
+      <c r="AT50" s="7" t="n"/>
+      <c r="AU50" s="7" t="n"/>
+      <c r="AV50" s="7" t="n"/>
+      <c r="AW50" s="7" t="n"/>
+      <c r="AX50" s="7" t="n"/>
+      <c r="AY50" s="7" t="n"/>
+      <c r="AZ50" s="7" t="n"/>
+      <c r="BA50" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB50" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC50" s="7" t="n"/>
+      <c r="BD50" s="7" t="n"/>
+      <c r="BE50" s="7" t="n"/>
+      <c r="BF50" s="7" t="n"/>
+      <c r="BG50" s="7" t="n"/>
+      <c r="BH50" s="7" t="n"/>
+      <c r="BI50" s="7" t="n"/>
+      <c r="BJ50" s="7" t="n"/>
+      <c r="BK50" s="7" t="n"/>
+      <c r="BL50" s="7" t="n"/>
+      <c r="BM50" s="7" t="n"/>
+      <c r="BN50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -31708,16 +34188,68 @@
       <c r="Z51" s="7" t="n"/>
       <c r="AA51" s="7" t="n"/>
       <c r="AB51" s="7" t="n"/>
-      <c r="AC51" s="7" t="n"/>
-      <c r="AD51" s="7" t="n"/>
+      <c r="AC51" s="7" t="inlineStr">
+        <is>
+          <t>N;Y;U</t>
+        </is>
+      </c>
+      <c r="AD51" s="7" t="inlineStr">
+        <is>
+          <t>C49487;C49488;C17998</t>
+        </is>
+      </c>
       <c r="AE51" s="7" t="n"/>
       <c r="AF51" s="7" t="n"/>
       <c r="AG51" s="7" t="n"/>
-      <c r="AH51" s="7" t="n"/>
-      <c r="AI51" s="7" t="n"/>
+      <c r="AH51" s="7" t="inlineStr">
+        <is>
+          <t>N;Y;U</t>
+        </is>
+      </c>
+      <c r="AI51" s="7" t="inlineStr">
+        <is>
+          <t>C49487;C49488;C17998</t>
+        </is>
+      </c>
       <c r="AJ51" s="7" t="n"/>
       <c r="AK51" s="7" t="n"/>
       <c r="AL51" s="7" t="n"/>
+      <c r="AM51" s="7" t="n"/>
+      <c r="AN51" s="7" t="n"/>
+      <c r="AO51" s="7" t="n"/>
+      <c r="AP51" s="7" t="n"/>
+      <c r="AQ51" s="7" t="n"/>
+      <c r="AR51" s="7" t="n"/>
+      <c r="AS51" s="7" t="n"/>
+      <c r="AT51" s="7" t="n"/>
+      <c r="AU51" s="7" t="n"/>
+      <c r="AV51" s="7" t="n"/>
+      <c r="AW51" s="7" t="n"/>
+      <c r="AX51" s="7" t="n"/>
+      <c r="AY51" s="7" t="n"/>
+      <c r="AZ51" s="7" t="n"/>
+      <c r="BA51" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT;LEFT</t>
+        </is>
+      </c>
+      <c r="BB51" s="7" t="inlineStr">
+        <is>
+          <t>C25228;C25229</t>
+        </is>
+      </c>
+      <c r="BC51" s="7" t="n"/>
+      <c r="BD51" s="7" t="n"/>
+      <c r="BE51" s="7" t="n"/>
+      <c r="BF51" s="7" t="n"/>
+      <c r="BG51" s="7" t="n"/>
+      <c r="BH51" s="7" t="n"/>
+      <c r="BI51" s="7" t="n"/>
+      <c r="BJ51" s="7" t="n"/>
+      <c r="BK51" s="7" t="n"/>
+      <c r="BL51" s="7" t="n"/>
+      <c r="BM51" s="7" t="n"/>
+      <c r="BN51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -31832,12 +34364,40 @@
       <c r="AH52" s="7" t="n"/>
       <c r="AI52" s="7" t="n"/>
       <c r="AJ52" s="7" t="n"/>
-      <c r="AK52" s="7" t="inlineStr">
+      <c r="AK52" s="7" t="n"/>
+      <c r="AL52" s="7" t="n"/>
+      <c r="AM52" s="7" t="n"/>
+      <c r="AN52" s="7" t="n"/>
+      <c r="AO52" s="7" t="n"/>
+      <c r="AP52" s="7" t="n"/>
+      <c r="AQ52" s="7" t="n"/>
+      <c r="AR52" s="7" t="n"/>
+      <c r="AS52" s="7" t="n"/>
+      <c r="AT52" s="7" t="n"/>
+      <c r="AU52" s="7" t="n"/>
+      <c r="AV52" s="7" t="n"/>
+      <c r="AW52" s="7" t="n"/>
+      <c r="AX52" s="7" t="n"/>
+      <c r="AY52" s="7" t="n"/>
+      <c r="AZ52" s="7" t="n"/>
+      <c r="BA52" s="7" t="n"/>
+      <c r="BB52" s="7" t="n"/>
+      <c r="BC52" s="7" t="n"/>
+      <c r="BD52" s="7" t="n"/>
+      <c r="BE52" s="7" t="n"/>
+      <c r="BF52" s="7" t="n"/>
+      <c r="BG52" s="7" t="n"/>
+      <c r="BH52" s="7" t="n"/>
+      <c r="BI52" s="7" t="n"/>
+      <c r="BJ52" s="7" t="n"/>
+      <c r="BK52" s="7" t="n"/>
+      <c r="BL52" s="7" t="n"/>
+      <c r="BM52" s="7" t="inlineStr">
         <is>
           <t>77194-9</t>
         </is>
       </c>
-      <c r="AL52" s="7" t="n"/>
+      <c r="BN52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -31952,12 +34512,56 @@
       <c r="AH53" s="7" t="n"/>
       <c r="AI53" s="7" t="n"/>
       <c r="AJ53" s="7" t="n"/>
-      <c r="AK53" s="7" t="inlineStr">
+      <c r="AK53" s="7" t="n"/>
+      <c r="AL53" s="7" t="n"/>
+      <c r="AM53" s="7" t="n"/>
+      <c r="AN53" s="7" t="n"/>
+      <c r="AO53" s="7" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AP53" s="7" t="inlineStr">
+        <is>
+          <t>C28251</t>
+        </is>
+      </c>
+      <c r="AQ53" s="7" t="n"/>
+      <c r="AR53" s="7" t="n"/>
+      <c r="AS53" s="7" t="n"/>
+      <c r="AT53" s="7" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AU53" s="7" t="inlineStr">
+        <is>
+          <t>C28251</t>
+        </is>
+      </c>
+      <c r="AV53" s="7" t="n"/>
+      <c r="AW53" s="7" t="n"/>
+      <c r="AX53" s="7" t="n"/>
+      <c r="AY53" s="7" t="n"/>
+      <c r="AZ53" s="7" t="n"/>
+      <c r="BA53" s="7" t="n"/>
+      <c r="BB53" s="7" t="n"/>
+      <c r="BC53" s="7" t="n"/>
+      <c r="BD53" s="7" t="n"/>
+      <c r="BE53" s="7" t="n"/>
+      <c r="BF53" s="7" t="n"/>
+      <c r="BG53" s="7" t="n"/>
+      <c r="BH53" s="7" t="n"/>
+      <c r="BI53" s="7" t="n"/>
+      <c r="BJ53" s="7" t="n"/>
+      <c r="BK53" s="7" t="n"/>
+      <c r="BL53" s="7" t="n"/>
+      <c r="BM53" s="7" t="inlineStr">
         <is>
           <t>8355-0</t>
         </is>
       </c>
-      <c r="AL53" s="7" t="n"/>
+      <c r="BN53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -32068,12 +34672,56 @@
       <c r="AH54" s="7" t="n"/>
       <c r="AI54" s="7" t="n"/>
       <c r="AJ54" s="7" t="n"/>
-      <c r="AK54" s="7" t="inlineStr">
+      <c r="AK54" s="7" t="n"/>
+      <c r="AL54" s="7" t="n"/>
+      <c r="AM54" s="7" t="n"/>
+      <c r="AN54" s="7" t="n"/>
+      <c r="AO54" s="7" t="inlineStr">
+        <is>
+          <t>cm;ft;in;m</t>
+        </is>
+      </c>
+      <c r="AP54" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C71253;C48500;C41139</t>
+        </is>
+      </c>
+      <c r="AQ54" s="7" t="n"/>
+      <c r="AR54" s="7" t="n"/>
+      <c r="AS54" s="7" t="n"/>
+      <c r="AT54" s="7" t="inlineStr">
+        <is>
+          <t>cm;ft;in;m</t>
+        </is>
+      </c>
+      <c r="AU54" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C71253;C48500;C41139</t>
+        </is>
+      </c>
+      <c r="AV54" s="7" t="n"/>
+      <c r="AW54" s="7" t="n"/>
+      <c r="AX54" s="7" t="n"/>
+      <c r="AY54" s="7" t="n"/>
+      <c r="AZ54" s="7" t="n"/>
+      <c r="BA54" s="7" t="n"/>
+      <c r="BB54" s="7" t="n"/>
+      <c r="BC54" s="7" t="n"/>
+      <c r="BD54" s="7" t="n"/>
+      <c r="BE54" s="7" t="n"/>
+      <c r="BF54" s="7" t="n"/>
+      <c r="BG54" s="7" t="n"/>
+      <c r="BH54" s="7" t="n"/>
+      <c r="BI54" s="7" t="n"/>
+      <c r="BJ54" s="7" t="n"/>
+      <c r="BK54" s="7" t="n"/>
+      <c r="BL54" s="7" t="n"/>
+      <c r="BM54" s="7" t="inlineStr">
         <is>
           <t>56116-7</t>
         </is>
       </c>
-      <c r="AL54" s="7" t="n"/>
+      <c r="BN54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -32190,6 +34838,50 @@
       <c r="AJ55" s="7" t="n"/>
       <c r="AK55" s="7" t="n"/>
       <c r="AL55" s="7" t="n"/>
+      <c r="AM55" s="7" t="n"/>
+      <c r="AN55" s="7" t="n"/>
+      <c r="AO55" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AP55" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AQ55" s="7" t="n"/>
+      <c r="AR55" s="7" t="n"/>
+      <c r="AS55" s="7" t="n"/>
+      <c r="AT55" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AU55" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AV55" s="7" t="n"/>
+      <c r="AW55" s="7" t="n"/>
+      <c r="AX55" s="7" t="n"/>
+      <c r="AY55" s="7" t="n"/>
+      <c r="AZ55" s="7" t="n"/>
+      <c r="BA55" s="7" t="n"/>
+      <c r="BB55" s="7" t="n"/>
+      <c r="BC55" s="7" t="n"/>
+      <c r="BD55" s="7" t="n"/>
+      <c r="BE55" s="7" t="n"/>
+      <c r="BF55" s="7" t="n"/>
+      <c r="BG55" s="7" t="n"/>
+      <c r="BH55" s="7" t="n"/>
+      <c r="BI55" s="7" t="n"/>
+      <c r="BJ55" s="7" t="n"/>
+      <c r="BK55" s="7" t="n"/>
+      <c r="BL55" s="7" t="n"/>
+      <c r="BM55" s="7" t="n"/>
+      <c r="BN55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -32302,6 +34994,34 @@
       <c r="AJ56" s="7" t="n"/>
       <c r="AK56" s="7" t="n"/>
       <c r="AL56" s="7" t="n"/>
+      <c r="AM56" s="7" t="n"/>
+      <c r="AN56" s="7" t="n"/>
+      <c r="AO56" s="7" t="n"/>
+      <c r="AP56" s="7" t="n"/>
+      <c r="AQ56" s="7" t="n"/>
+      <c r="AR56" s="7" t="n"/>
+      <c r="AS56" s="7" t="n"/>
+      <c r="AT56" s="7" t="n"/>
+      <c r="AU56" s="7" t="n"/>
+      <c r="AV56" s="7" t="n"/>
+      <c r="AW56" s="7" t="n"/>
+      <c r="AX56" s="7" t="n"/>
+      <c r="AY56" s="7" t="n"/>
+      <c r="AZ56" s="7" t="n"/>
+      <c r="BA56" s="7" t="n"/>
+      <c r="BB56" s="7" t="n"/>
+      <c r="BC56" s="7" t="n"/>
+      <c r="BD56" s="7" t="n"/>
+      <c r="BE56" s="7" t="n"/>
+      <c r="BF56" s="7" t="n"/>
+      <c r="BG56" s="7" t="n"/>
+      <c r="BH56" s="7" t="n"/>
+      <c r="BI56" s="7" t="n"/>
+      <c r="BJ56" s="7" t="n"/>
+      <c r="BK56" s="7" t="n"/>
+      <c r="BL56" s="7" t="n"/>
+      <c r="BM56" s="7" t="n"/>
+      <c r="BN56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -32412,12 +35132,48 @@
       <c r="AH57" s="7" t="n"/>
       <c r="AI57" s="7" t="n"/>
       <c r="AJ57" s="7" t="n"/>
-      <c r="AK57" s="7" t="inlineStr">
+      <c r="AK57" s="7" t="n"/>
+      <c r="AL57" s="7" t="n"/>
+      <c r="AM57" s="7" t="n"/>
+      <c r="AN57" s="7" t="n"/>
+      <c r="AO57" s="7" t="inlineStr">
+        <is>
+          <t>kg/m2;psi</t>
+        </is>
+      </c>
+      <c r="AP57" s="7" t="inlineStr">
+        <is>
+          <t>C49671;C67334</t>
+        </is>
+      </c>
+      <c r="AQ57" s="7" t="n"/>
+      <c r="AR57" s="7" t="n"/>
+      <c r="AS57" s="7" t="n"/>
+      <c r="AT57" s="7" t="n"/>
+      <c r="AU57" s="7" t="n"/>
+      <c r="AV57" s="7" t="n"/>
+      <c r="AW57" s="7" t="n"/>
+      <c r="AX57" s="7" t="n"/>
+      <c r="AY57" s="7" t="n"/>
+      <c r="AZ57" s="7" t="n"/>
+      <c r="BA57" s="7" t="n"/>
+      <c r="BB57" s="7" t="n"/>
+      <c r="BC57" s="7" t="n"/>
+      <c r="BD57" s="7" t="n"/>
+      <c r="BE57" s="7" t="n"/>
+      <c r="BF57" s="7" t="n"/>
+      <c r="BG57" s="7" t="n"/>
+      <c r="BH57" s="7" t="n"/>
+      <c r="BI57" s="7" t="n"/>
+      <c r="BJ57" s="7" t="n"/>
+      <c r="BK57" s="7" t="n"/>
+      <c r="BL57" s="7" t="n"/>
+      <c r="BM57" s="7" t="inlineStr">
         <is>
           <t>39156-5</t>
         </is>
       </c>
-      <c r="AL57" s="7" t="n"/>
+      <c r="BN57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -32530,6 +35286,34 @@
       <c r="AJ58" s="7" t="n"/>
       <c r="AK58" s="7" t="n"/>
       <c r="AL58" s="7" t="n"/>
+      <c r="AM58" s="7" t="n"/>
+      <c r="AN58" s="7" t="n"/>
+      <c r="AO58" s="7" t="n"/>
+      <c r="AP58" s="7" t="n"/>
+      <c r="AQ58" s="7" t="n"/>
+      <c r="AR58" s="7" t="n"/>
+      <c r="AS58" s="7" t="n"/>
+      <c r="AT58" s="7" t="n"/>
+      <c r="AU58" s="7" t="n"/>
+      <c r="AV58" s="7" t="n"/>
+      <c r="AW58" s="7" t="n"/>
+      <c r="AX58" s="7" t="n"/>
+      <c r="AY58" s="7" t="n"/>
+      <c r="AZ58" s="7" t="n"/>
+      <c r="BA58" s="7" t="n"/>
+      <c r="BB58" s="7" t="n"/>
+      <c r="BC58" s="7" t="n"/>
+      <c r="BD58" s="7" t="n"/>
+      <c r="BE58" s="7" t="n"/>
+      <c r="BF58" s="7" t="n"/>
+      <c r="BG58" s="7" t="n"/>
+      <c r="BH58" s="7" t="n"/>
+      <c r="BI58" s="7" t="n"/>
+      <c r="BJ58" s="7" t="n"/>
+      <c r="BK58" s="7" t="n"/>
+      <c r="BL58" s="7" t="n"/>
+      <c r="BM58" s="7" t="n"/>
+      <c r="BN58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -32644,12 +35428,56 @@
       <c r="AH59" s="7" t="n"/>
       <c r="AI59" s="7" t="n"/>
       <c r="AJ59" s="7" t="n"/>
-      <c r="AK59" s="7" t="inlineStr">
+      <c r="AK59" s="7" t="n"/>
+      <c r="AL59" s="7" t="n"/>
+      <c r="AM59" s="7" t="n"/>
+      <c r="AN59" s="7" t="n"/>
+      <c r="AO59" s="7" t="inlineStr">
+        <is>
+          <t>kcal/day;Watt</t>
+        </is>
+      </c>
+      <c r="AP59" s="7" t="inlineStr">
+        <is>
+          <t>C139135;C42549</t>
+        </is>
+      </c>
+      <c r="AQ59" s="7" t="n"/>
+      <c r="AR59" s="7" t="n"/>
+      <c r="AS59" s="7" t="n"/>
+      <c r="AT59" s="7" t="inlineStr">
+        <is>
+          <t>kcal/day;Watt</t>
+        </is>
+      </c>
+      <c r="AU59" s="7" t="inlineStr">
+        <is>
+          <t>C139135;C42549</t>
+        </is>
+      </c>
+      <c r="AV59" s="7" t="n"/>
+      <c r="AW59" s="7" t="n"/>
+      <c r="AX59" s="7" t="n"/>
+      <c r="AY59" s="7" t="n"/>
+      <c r="AZ59" s="7" t="n"/>
+      <c r="BA59" s="7" t="n"/>
+      <c r="BB59" s="7" t="n"/>
+      <c r="BC59" s="7" t="n"/>
+      <c r="BD59" s="7" t="n"/>
+      <c r="BE59" s="7" t="n"/>
+      <c r="BF59" s="7" t="n"/>
+      <c r="BG59" s="7" t="n"/>
+      <c r="BH59" s="7" t="n"/>
+      <c r="BI59" s="7" t="n"/>
+      <c r="BJ59" s="7" t="n"/>
+      <c r="BK59" s="7" t="n"/>
+      <c r="BL59" s="7" t="n"/>
+      <c r="BM59" s="7" t="inlineStr">
         <is>
           <t>69429-9</t>
         </is>
       </c>
-      <c r="AL59" s="7" t="n"/>
+      <c r="BN59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -32766,6 +35594,50 @@
       <c r="AJ60" s="7" t="n"/>
       <c r="AK60" s="7" t="n"/>
       <c r="AL60" s="7" t="n"/>
+      <c r="AM60" s="7" t="n"/>
+      <c r="AN60" s="7" t="n"/>
+      <c r="AO60" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP60" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ60" s="7" t="n"/>
+      <c r="AR60" s="7" t="n"/>
+      <c r="AS60" s="7" t="n"/>
+      <c r="AT60" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU60" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV60" s="7" t="n"/>
+      <c r="AW60" s="7" t="n"/>
+      <c r="AX60" s="7" t="n"/>
+      <c r="AY60" s="7" t="n"/>
+      <c r="AZ60" s="7" t="n"/>
+      <c r="BA60" s="7" t="n"/>
+      <c r="BB60" s="7" t="n"/>
+      <c r="BC60" s="7" t="n"/>
+      <c r="BD60" s="7" t="n"/>
+      <c r="BE60" s="7" t="n"/>
+      <c r="BF60" s="7" t="n"/>
+      <c r="BG60" s="7" t="n"/>
+      <c r="BH60" s="7" t="n"/>
+      <c r="BI60" s="7" t="n"/>
+      <c r="BJ60" s="7" t="n"/>
+      <c r="BK60" s="7" t="n"/>
+      <c r="BL60" s="7" t="n"/>
+      <c r="BM60" s="7" t="n"/>
+      <c r="BN60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -32880,12 +35752,56 @@
       <c r="AH61" s="7" t="n"/>
       <c r="AI61" s="7" t="n"/>
       <c r="AJ61" s="7" t="n"/>
-      <c r="AK61" s="7" t="inlineStr">
+      <c r="AK61" s="7" t="n"/>
+      <c r="AL61" s="7" t="n"/>
+      <c r="AM61" s="7" t="n"/>
+      <c r="AN61" s="7" t="n"/>
+      <c r="AO61" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AP61" s="7" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
+      <c r="AQ61" s="7" t="n"/>
+      <c r="AR61" s="7" t="n"/>
+      <c r="AS61" s="7" t="n"/>
+      <c r="AT61" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AU61" s="7" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
+      <c r="AV61" s="7" t="n"/>
+      <c r="AW61" s="7" t="n"/>
+      <c r="AX61" s="7" t="n"/>
+      <c r="AY61" s="7" t="n"/>
+      <c r="AZ61" s="7" t="n"/>
+      <c r="BA61" s="7" t="n"/>
+      <c r="BB61" s="7" t="n"/>
+      <c r="BC61" s="7" t="n"/>
+      <c r="BD61" s="7" t="n"/>
+      <c r="BE61" s="7" t="n"/>
+      <c r="BF61" s="7" t="n"/>
+      <c r="BG61" s="7" t="n"/>
+      <c r="BH61" s="7" t="n"/>
+      <c r="BI61" s="7" t="n"/>
+      <c r="BJ61" s="7" t="n"/>
+      <c r="BK61" s="7" t="n"/>
+      <c r="BL61" s="7" t="n"/>
+      <c r="BM61" s="7" t="inlineStr">
         <is>
           <t>41982-0</t>
         </is>
       </c>
-      <c r="AL61" s="7" t="n"/>
+      <c r="BN61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -33000,12 +35916,56 @@
       <c r="AH62" s="7" t="n"/>
       <c r="AI62" s="7" t="n"/>
       <c r="AJ62" s="7" t="n"/>
-      <c r="AK62" s="7" t="inlineStr">
+      <c r="AK62" s="7" t="n"/>
+      <c r="AL62" s="7" t="n"/>
+      <c r="AM62" s="7" t="n"/>
+      <c r="AN62" s="7" t="n"/>
+      <c r="AO62" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB;oz</t>
+        </is>
+      </c>
+      <c r="AP62" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AQ62" s="7" t="n"/>
+      <c r="AR62" s="7" t="n"/>
+      <c r="AS62" s="7" t="n"/>
+      <c r="AT62" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB;oz</t>
+        </is>
+      </c>
+      <c r="AU62" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AV62" s="7" t="n"/>
+      <c r="AW62" s="7" t="n"/>
+      <c r="AX62" s="7" t="n"/>
+      <c r="AY62" s="7" t="n"/>
+      <c r="AZ62" s="7" t="n"/>
+      <c r="BA62" s="7" t="n"/>
+      <c r="BB62" s="7" t="n"/>
+      <c r="BC62" s="7" t="n"/>
+      <c r="BD62" s="7" t="n"/>
+      <c r="BE62" s="7" t="n"/>
+      <c r="BF62" s="7" t="n"/>
+      <c r="BG62" s="7" t="n"/>
+      <c r="BH62" s="7" t="n"/>
+      <c r="BI62" s="7" t="n"/>
+      <c r="BJ62" s="7" t="n"/>
+      <c r="BK62" s="7" t="n"/>
+      <c r="BL62" s="7" t="n"/>
+      <c r="BM62" s="7" t="inlineStr">
         <is>
           <t>8339-4</t>
         </is>
       </c>
-      <c r="AL62" s="7" t="n"/>
+      <c r="BN62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -33120,12 +36080,56 @@
       <c r="AH63" s="7" t="n"/>
       <c r="AI63" s="7" t="n"/>
       <c r="AJ63" s="7" t="n"/>
-      <c r="AK63" s="7" t="inlineStr">
+      <c r="AK63" s="7" t="n"/>
+      <c r="AL63" s="7" t="n"/>
+      <c r="AM63" s="7" t="n"/>
+      <c r="AN63" s="7" t="n"/>
+      <c r="AO63" s="7" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="AP63" s="7" t="inlineStr">
+        <is>
+          <t>C42569</t>
+        </is>
+      </c>
+      <c r="AQ63" s="7" t="n"/>
+      <c r="AR63" s="7" t="n"/>
+      <c r="AS63" s="7" t="n"/>
+      <c r="AT63" s="7" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="AU63" s="7" t="inlineStr">
+        <is>
+          <t>C42569</t>
+        </is>
+      </c>
+      <c r="AV63" s="7" t="n"/>
+      <c r="AW63" s="7" t="n"/>
+      <c r="AX63" s="7" t="n"/>
+      <c r="AY63" s="7" t="n"/>
+      <c r="AZ63" s="7" t="n"/>
+      <c r="BA63" s="7" t="n"/>
+      <c r="BB63" s="7" t="n"/>
+      <c r="BC63" s="7" t="n"/>
+      <c r="BD63" s="7" t="n"/>
+      <c r="BE63" s="7" t="n"/>
+      <c r="BF63" s="7" t="n"/>
+      <c r="BG63" s="7" t="n"/>
+      <c r="BH63" s="7" t="n"/>
+      <c r="BI63" s="7" t="n"/>
+      <c r="BJ63" s="7" t="n"/>
+      <c r="BK63" s="7" t="n"/>
+      <c r="BL63" s="7" t="n"/>
+      <c r="BM63" s="7" t="inlineStr">
         <is>
           <t>8277-6</t>
         </is>
       </c>
-      <c r="AL63" s="7" t="n"/>
+      <c r="BN63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -33242,6 +36246,50 @@
       <c r="AJ64" s="7" t="n"/>
       <c r="AK64" s="7" t="n"/>
       <c r="AL64" s="7" t="n"/>
+      <c r="AM64" s="7" t="n"/>
+      <c r="AN64" s="7" t="n"/>
+      <c r="AO64" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP64" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ64" s="7" t="n"/>
+      <c r="AR64" s="7" t="n"/>
+      <c r="AS64" s="7" t="n"/>
+      <c r="AT64" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU64" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV64" s="7" t="n"/>
+      <c r="AW64" s="7" t="n"/>
+      <c r="AX64" s="7" t="n"/>
+      <c r="AY64" s="7" t="n"/>
+      <c r="AZ64" s="7" t="n"/>
+      <c r="BA64" s="7" t="n"/>
+      <c r="BB64" s="7" t="n"/>
+      <c r="BC64" s="7" t="n"/>
+      <c r="BD64" s="7" t="n"/>
+      <c r="BE64" s="7" t="n"/>
+      <c r="BF64" s="7" t="n"/>
+      <c r="BG64" s="7" t="n"/>
+      <c r="BH64" s="7" t="n"/>
+      <c r="BI64" s="7" t="n"/>
+      <c r="BJ64" s="7" t="n"/>
+      <c r="BK64" s="7" t="n"/>
+      <c r="BL64" s="7" t="n"/>
+      <c r="BM64" s="7" t="n"/>
+      <c r="BN64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -33358,6 +36406,50 @@
       <c r="AJ65" s="7" t="n"/>
       <c r="AK65" s="7" t="n"/>
       <c r="AL65" s="7" t="n"/>
+      <c r="AM65" s="7" t="n"/>
+      <c r="AN65" s="7" t="n"/>
+      <c r="AO65" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP65" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ65" s="7" t="n"/>
+      <c r="AR65" s="7" t="n"/>
+      <c r="AS65" s="7" t="n"/>
+      <c r="AT65" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU65" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV65" s="7" t="n"/>
+      <c r="AW65" s="7" t="n"/>
+      <c r="AX65" s="7" t="n"/>
+      <c r="AY65" s="7" t="n"/>
+      <c r="AZ65" s="7" t="n"/>
+      <c r="BA65" s="7" t="n"/>
+      <c r="BB65" s="7" t="n"/>
+      <c r="BC65" s="7" t="n"/>
+      <c r="BD65" s="7" t="n"/>
+      <c r="BE65" s="7" t="n"/>
+      <c r="BF65" s="7" t="n"/>
+      <c r="BG65" s="7" t="n"/>
+      <c r="BH65" s="7" t="n"/>
+      <c r="BI65" s="7" t="n"/>
+      <c r="BJ65" s="7" t="n"/>
+      <c r="BK65" s="7" t="n"/>
+      <c r="BL65" s="7" t="n"/>
+      <c r="BM65" s="7" t="n"/>
+      <c r="BN65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -33472,12 +36564,56 @@
       <c r="AH66" s="7" t="n"/>
       <c r="AI66" s="7" t="n"/>
       <c r="AJ66" s="7" t="n"/>
-      <c r="AK66" s="7" t="inlineStr">
+      <c r="AK66" s="7" t="n"/>
+      <c r="AL66" s="7" t="n"/>
+      <c r="AM66" s="7" t="n"/>
+      <c r="AN66" s="7" t="n"/>
+      <c r="AO66" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="AP66" s="7" t="inlineStr">
+        <is>
+          <t>C42535</t>
+        </is>
+      </c>
+      <c r="AQ66" s="7" t="n"/>
+      <c r="AR66" s="7" t="n"/>
+      <c r="AS66" s="7" t="n"/>
+      <c r="AT66" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="AU66" s="7" t="inlineStr">
+        <is>
+          <t>C42535</t>
+        </is>
+      </c>
+      <c r="AV66" s="7" t="n"/>
+      <c r="AW66" s="7" t="n"/>
+      <c r="AX66" s="7" t="n"/>
+      <c r="AY66" s="7" t="n"/>
+      <c r="AZ66" s="7" t="n"/>
+      <c r="BA66" s="7" t="n"/>
+      <c r="BB66" s="7" t="n"/>
+      <c r="BC66" s="7" t="n"/>
+      <c r="BD66" s="7" t="n"/>
+      <c r="BE66" s="7" t="n"/>
+      <c r="BF66" s="7" t="n"/>
+      <c r="BG66" s="7" t="n"/>
+      <c r="BH66" s="7" t="n"/>
+      <c r="BI66" s="7" t="n"/>
+      <c r="BJ66" s="7" t="n"/>
+      <c r="BK66" s="7" t="n"/>
+      <c r="BL66" s="7" t="n"/>
+      <c r="BM66" s="7" t="inlineStr">
         <is>
           <t>44971-0</t>
         </is>
       </c>
-      <c r="AL66" s="7" t="n"/>
+      <c r="BN66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -33594,6 +36730,50 @@
       <c r="AJ67" s="7" t="n"/>
       <c r="AK67" s="7" t="n"/>
       <c r="AL67" s="7" t="n"/>
+      <c r="AM67" s="7" t="n"/>
+      <c r="AN67" s="7" t="n"/>
+      <c r="AO67" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP67" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ67" s="7" t="n"/>
+      <c r="AR67" s="7" t="n"/>
+      <c r="AS67" s="7" t="n"/>
+      <c r="AT67" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU67" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV67" s="7" t="n"/>
+      <c r="AW67" s="7" t="n"/>
+      <c r="AX67" s="7" t="n"/>
+      <c r="AY67" s="7" t="n"/>
+      <c r="AZ67" s="7" t="n"/>
+      <c r="BA67" s="7" t="n"/>
+      <c r="BB67" s="7" t="n"/>
+      <c r="BC67" s="7" t="n"/>
+      <c r="BD67" s="7" t="n"/>
+      <c r="BE67" s="7" t="n"/>
+      <c r="BF67" s="7" t="n"/>
+      <c r="BG67" s="7" t="n"/>
+      <c r="BH67" s="7" t="n"/>
+      <c r="BI67" s="7" t="n"/>
+      <c r="BJ67" s="7" t="n"/>
+      <c r="BK67" s="7" t="n"/>
+      <c r="BL67" s="7" t="n"/>
+      <c r="BM67" s="7" t="n"/>
+      <c r="BN67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -33706,6 +36886,34 @@
       <c r="AJ68" s="7" t="n"/>
       <c r="AK68" s="7" t="n"/>
       <c r="AL68" s="7" t="n"/>
+      <c r="AM68" s="7" t="n"/>
+      <c r="AN68" s="7" t="n"/>
+      <c r="AO68" s="7" t="n"/>
+      <c r="AP68" s="7" t="n"/>
+      <c r="AQ68" s="7" t="n"/>
+      <c r="AR68" s="7" t="n"/>
+      <c r="AS68" s="7" t="n"/>
+      <c r="AT68" s="7" t="n"/>
+      <c r="AU68" s="7" t="n"/>
+      <c r="AV68" s="7" t="n"/>
+      <c r="AW68" s="7" t="n"/>
+      <c r="AX68" s="7" t="n"/>
+      <c r="AY68" s="7" t="n"/>
+      <c r="AZ68" s="7" t="n"/>
+      <c r="BA68" s="7" t="n"/>
+      <c r="BB68" s="7" t="n"/>
+      <c r="BC68" s="7" t="n"/>
+      <c r="BD68" s="7" t="n"/>
+      <c r="BE68" s="7" t="n"/>
+      <c r="BF68" s="7" t="n"/>
+      <c r="BG68" s="7" t="n"/>
+      <c r="BH68" s="7" t="n"/>
+      <c r="BI68" s="7" t="n"/>
+      <c r="BJ68" s="7" t="n"/>
+      <c r="BK68" s="7" t="n"/>
+      <c r="BL68" s="7" t="n"/>
+      <c r="BM68" s="7" t="n"/>
+      <c r="BN68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -33818,6 +37026,34 @@
       <c r="AJ69" s="7" t="n"/>
       <c r="AK69" s="7" t="n"/>
       <c r="AL69" s="7" t="n"/>
+      <c r="AM69" s="7" t="n"/>
+      <c r="AN69" s="7" t="n"/>
+      <c r="AO69" s="7" t="n"/>
+      <c r="AP69" s="7" t="n"/>
+      <c r="AQ69" s="7" t="n"/>
+      <c r="AR69" s="7" t="n"/>
+      <c r="AS69" s="7" t="n"/>
+      <c r="AT69" s="7" t="n"/>
+      <c r="AU69" s="7" t="n"/>
+      <c r="AV69" s="7" t="n"/>
+      <c r="AW69" s="7" t="n"/>
+      <c r="AX69" s="7" t="n"/>
+      <c r="AY69" s="7" t="n"/>
+      <c r="AZ69" s="7" t="n"/>
+      <c r="BA69" s="7" t="n"/>
+      <c r="BB69" s="7" t="n"/>
+      <c r="BC69" s="7" t="n"/>
+      <c r="BD69" s="7" t="n"/>
+      <c r="BE69" s="7" t="n"/>
+      <c r="BF69" s="7" t="n"/>
+      <c r="BG69" s="7" t="n"/>
+      <c r="BH69" s="7" t="n"/>
+      <c r="BI69" s="7" t="n"/>
+      <c r="BJ69" s="7" t="n"/>
+      <c r="BK69" s="7" t="n"/>
+      <c r="BL69" s="7" t="n"/>
+      <c r="BM69" s="7" t="n"/>
+      <c r="BN69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -33919,36 +37155,12 @@
       <c r="U70" s="7" t="n"/>
       <c r="V70" s="7" t="n"/>
       <c r="W70" s="7" t="n"/>
-      <c r="X70" s="7" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="Y70" s="7" t="inlineStr">
-        <is>
-          <t>C49670</t>
-        </is>
-      </c>
-      <c r="Z70" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA70" s="7" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="AB70" s="7" t="inlineStr">
-        <is>
-          <t>C49670</t>
-        </is>
-      </c>
-      <c r="AC70" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X70" s="7" t="n"/>
+      <c r="Y70" s="7" t="n"/>
+      <c r="Z70" s="7" t="n"/>
+      <c r="AA70" s="7" t="n"/>
+      <c r="AB70" s="7" t="n"/>
+      <c r="AC70" s="7" t="n"/>
       <c r="AD70" s="7" t="n"/>
       <c r="AE70" s="7" t="n"/>
       <c r="AF70" s="7" t="n"/>
@@ -33956,12 +37168,88 @@
       <c r="AH70" s="7" t="n"/>
       <c r="AI70" s="7" t="n"/>
       <c r="AJ70" s="7" t="n"/>
-      <c r="AK70" s="7" t="inlineStr">
+      <c r="AK70" s="7" t="n"/>
+      <c r="AL70" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AM70" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AN70" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO70" s="7" t="n"/>
+      <c r="AP70" s="7" t="n"/>
+      <c r="AQ70" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AR70" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AS70" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT70" s="7" t="n"/>
+      <c r="AU70" s="7" t="n"/>
+      <c r="AV70" s="7" t="n"/>
+      <c r="AW70" s="7" t="n"/>
+      <c r="AX70" s="7" t="n"/>
+      <c r="AY70" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ70" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+        </is>
+      </c>
+      <c r="BA70" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB70" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC70" s="7" t="inlineStr">
+        <is>
+          <t>PRONE;SEMI-RECUMBENT;SITTING;STANDING;SUPINE</t>
+        </is>
+      </c>
+      <c r="BD70" s="7" t="inlineStr">
+        <is>
+          <t>C62165;C111310;C62122;C62166;C62167</t>
+        </is>
+      </c>
+      <c r="BE70" s="7" t="n"/>
+      <c r="BF70" s="7" t="n"/>
+      <c r="BG70" s="7" t="n"/>
+      <c r="BH70" s="7" t="n"/>
+      <c r="BI70" s="7" t="n"/>
+      <c r="BJ70" s="7" t="n"/>
+      <c r="BK70" s="7" t="n"/>
+      <c r="BL70" s="7" t="n"/>
+      <c r="BM70" s="7" t="inlineStr">
         <is>
           <t>8462-4</t>
         </is>
       </c>
-      <c r="AL70" s="7" t="inlineStr">
+      <c r="BN70" s="7" t="inlineStr">
         <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
@@ -34080,12 +37368,80 @@
       <c r="AH71" s="7" t="n"/>
       <c r="AI71" s="7" t="n"/>
       <c r="AJ71" s="7" t="n"/>
-      <c r="AK71" s="7" t="inlineStr">
+      <c r="AK71" s="7" t="n"/>
+      <c r="AL71" s="7" t="n"/>
+      <c r="AM71" s="7" t="n"/>
+      <c r="AN71" s="7" t="n"/>
+      <c r="AO71" s="7" t="inlineStr">
+        <is>
+          <t>mmHg;cmHg</t>
+        </is>
+      </c>
+      <c r="AP71" s="7" t="inlineStr">
+        <is>
+          <t>C49670;C147129</t>
+        </is>
+      </c>
+      <c r="AQ71" s="7" t="n"/>
+      <c r="AR71" s="7" t="n"/>
+      <c r="AS71" s="7" t="n"/>
+      <c r="AT71" s="7" t="inlineStr">
+        <is>
+          <t>mmHg;cmHg</t>
+        </is>
+      </c>
+      <c r="AU71" s="7" t="inlineStr">
+        <is>
+          <t>C49670;C147129</t>
+        </is>
+      </c>
+      <c r="AV71" s="7" t="n"/>
+      <c r="AW71" s="7" t="n"/>
+      <c r="AX71" s="7" t="n"/>
+      <c r="AY71" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ71" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+        </is>
+      </c>
+      <c r="BA71" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB71" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC71" s="7" t="inlineStr">
+        <is>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING, LEGS DEPENDENT;SLING;STANDING;STANDING, BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+        </is>
+      </c>
+      <c r="BD71" s="7" t="inlineStr">
+        <is>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C150885;C92604;C62166;C174357;C62167;C62168;C90480</t>
+        </is>
+      </c>
+      <c r="BE71" s="7" t="n"/>
+      <c r="BF71" s="7" t="n"/>
+      <c r="BG71" s="7" t="n"/>
+      <c r="BH71" s="7" t="n"/>
+      <c r="BI71" s="7" t="n"/>
+      <c r="BJ71" s="7" t="n"/>
+      <c r="BK71" s="7" t="n"/>
+      <c r="BL71" s="7" t="n"/>
+      <c r="BM71" s="7" t="inlineStr">
         <is>
           <t>8462-4</t>
         </is>
       </c>
-      <c r="AL71" s="7" t="n"/>
+      <c r="BN71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -34202,6 +37558,50 @@
       <c r="AJ72" s="7" t="n"/>
       <c r="AK72" s="7" t="n"/>
       <c r="AL72" s="7" t="n"/>
+      <c r="AM72" s="7" t="n"/>
+      <c r="AN72" s="7" t="n"/>
+      <c r="AO72" s="7" t="inlineStr">
+        <is>
+          <t>dL;L</t>
+        </is>
+      </c>
+      <c r="AP72" s="7" t="inlineStr">
+        <is>
+          <t>C64697;C48505</t>
+        </is>
+      </c>
+      <c r="AQ72" s="7" t="n"/>
+      <c r="AR72" s="7" t="n"/>
+      <c r="AS72" s="7" t="n"/>
+      <c r="AT72" s="7" t="inlineStr">
+        <is>
+          <t>dL;L</t>
+        </is>
+      </c>
+      <c r="AU72" s="7" t="inlineStr">
+        <is>
+          <t>C64697;C48505</t>
+        </is>
+      </c>
+      <c r="AV72" s="7" t="n"/>
+      <c r="AW72" s="7" t="n"/>
+      <c r="AX72" s="7" t="n"/>
+      <c r="AY72" s="7" t="n"/>
+      <c r="AZ72" s="7" t="n"/>
+      <c r="BA72" s="7" t="n"/>
+      <c r="BB72" s="7" t="n"/>
+      <c r="BC72" s="7" t="n"/>
+      <c r="BD72" s="7" t="n"/>
+      <c r="BE72" s="7" t="n"/>
+      <c r="BF72" s="7" t="n"/>
+      <c r="BG72" s="7" t="n"/>
+      <c r="BH72" s="7" t="n"/>
+      <c r="BI72" s="7" t="n"/>
+      <c r="BJ72" s="7" t="n"/>
+      <c r="BK72" s="7" t="n"/>
+      <c r="BL72" s="7" t="n"/>
+      <c r="BM72" s="7" t="n"/>
+      <c r="BN72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -34318,6 +37718,50 @@
       <c r="AJ73" s="7" t="n"/>
       <c r="AK73" s="7" t="n"/>
       <c r="AL73" s="7" t="n"/>
+      <c r="AM73" s="7" t="n"/>
+      <c r="AN73" s="7" t="n"/>
+      <c r="AO73" s="7" t="inlineStr">
+        <is>
+          <t>%;RATIO</t>
+        </is>
+      </c>
+      <c r="AP73" s="7" t="inlineStr">
+        <is>
+          <t>C25613;C44256</t>
+        </is>
+      </c>
+      <c r="AQ73" s="7" t="n"/>
+      <c r="AR73" s="7" t="n"/>
+      <c r="AS73" s="7" t="n"/>
+      <c r="AT73" s="7" t="inlineStr">
+        <is>
+          <t>%;RATIO</t>
+        </is>
+      </c>
+      <c r="AU73" s="7" t="inlineStr">
+        <is>
+          <t>C25613;C44256</t>
+        </is>
+      </c>
+      <c r="AV73" s="7" t="n"/>
+      <c r="AW73" s="7" t="n"/>
+      <c r="AX73" s="7" t="n"/>
+      <c r="AY73" s="7" t="n"/>
+      <c r="AZ73" s="7" t="n"/>
+      <c r="BA73" s="7" t="n"/>
+      <c r="BB73" s="7" t="n"/>
+      <c r="BC73" s="7" t="n"/>
+      <c r="BD73" s="7" t="n"/>
+      <c r="BE73" s="7" t="n"/>
+      <c r="BF73" s="7" t="n"/>
+      <c r="BG73" s="7" t="n"/>
+      <c r="BH73" s="7" t="n"/>
+      <c r="BI73" s="7" t="n"/>
+      <c r="BJ73" s="7" t="n"/>
+      <c r="BK73" s="7" t="n"/>
+      <c r="BL73" s="7" t="n"/>
+      <c r="BM73" s="7" t="n"/>
+      <c r="BN73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -34434,6 +37878,50 @@
       <c r="AJ74" s="7" t="n"/>
       <c r="AK74" s="7" t="n"/>
       <c r="AL74" s="7" t="n"/>
+      <c r="AM74" s="7" t="n"/>
+      <c r="AN74" s="7" t="n"/>
+      <c r="AO74" s="7" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="AP74" s="7" t="inlineStr">
+        <is>
+          <t>C127805</t>
+        </is>
+      </c>
+      <c r="AQ74" s="7" t="n"/>
+      <c r="AR74" s="7" t="n"/>
+      <c r="AS74" s="7" t="n"/>
+      <c r="AT74" s="7" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="AU74" s="7" t="inlineStr">
+        <is>
+          <t>C127805</t>
+        </is>
+      </c>
+      <c r="AV74" s="7" t="n"/>
+      <c r="AW74" s="7" t="n"/>
+      <c r="AX74" s="7" t="n"/>
+      <c r="AY74" s="7" t="n"/>
+      <c r="AZ74" s="7" t="n"/>
+      <c r="BA74" s="7" t="n"/>
+      <c r="BB74" s="7" t="n"/>
+      <c r="BC74" s="7" t="n"/>
+      <c r="BD74" s="7" t="n"/>
+      <c r="BE74" s="7" t="n"/>
+      <c r="BF74" s="7" t="n"/>
+      <c r="BG74" s="7" t="n"/>
+      <c r="BH74" s="7" t="n"/>
+      <c r="BI74" s="7" t="n"/>
+      <c r="BJ74" s="7" t="n"/>
+      <c r="BK74" s="7" t="n"/>
+      <c r="BL74" s="7" t="n"/>
+      <c r="BM74" s="7" t="n"/>
+      <c r="BN74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -34548,12 +38036,56 @@
       <c r="AH75" s="7" t="n"/>
       <c r="AI75" s="7" t="n"/>
       <c r="AJ75" s="7" t="n"/>
-      <c r="AK75" s="7" t="inlineStr">
+      <c r="AK75" s="7" t="n"/>
+      <c r="AL75" s="7" t="n"/>
+      <c r="AM75" s="7" t="n"/>
+      <c r="AN75" s="7" t="n"/>
+      <c r="AO75" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AP75" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AQ75" s="7" t="n"/>
+      <c r="AR75" s="7" t="n"/>
+      <c r="AS75" s="7" t="n"/>
+      <c r="AT75" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AU75" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AV75" s="7" t="n"/>
+      <c r="AW75" s="7" t="n"/>
+      <c r="AX75" s="7" t="n"/>
+      <c r="AY75" s="7" t="n"/>
+      <c r="AZ75" s="7" t="n"/>
+      <c r="BA75" s="7" t="n"/>
+      <c r="BB75" s="7" t="n"/>
+      <c r="BC75" s="7" t="n"/>
+      <c r="BD75" s="7" t="n"/>
+      <c r="BE75" s="7" t="n"/>
+      <c r="BF75" s="7" t="n"/>
+      <c r="BG75" s="7" t="n"/>
+      <c r="BH75" s="7" t="n"/>
+      <c r="BI75" s="7" t="n"/>
+      <c r="BJ75" s="7" t="n"/>
+      <c r="BK75" s="7" t="n"/>
+      <c r="BL75" s="7" t="n"/>
+      <c r="BM75" s="7" t="inlineStr">
         <is>
           <t>8335-2</t>
         </is>
       </c>
-      <c r="AL75" s="7" t="n"/>
+      <c r="BN75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -34670,6 +38202,50 @@
       <c r="AJ76" s="7" t="n"/>
       <c r="AK76" s="7" t="n"/>
       <c r="AL76" s="7" t="n"/>
+      <c r="AM76" s="7" t="n"/>
+      <c r="AN76" s="7" t="n"/>
+      <c r="AO76" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP76" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ76" s="7" t="n"/>
+      <c r="AR76" s="7" t="n"/>
+      <c r="AS76" s="7" t="n"/>
+      <c r="AT76" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU76" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV76" s="7" t="n"/>
+      <c r="AW76" s="7" t="n"/>
+      <c r="AX76" s="7" t="n"/>
+      <c r="AY76" s="7" t="n"/>
+      <c r="AZ76" s="7" t="n"/>
+      <c r="BA76" s="7" t="n"/>
+      <c r="BB76" s="7" t="n"/>
+      <c r="BC76" s="7" t="n"/>
+      <c r="BD76" s="7" t="n"/>
+      <c r="BE76" s="7" t="n"/>
+      <c r="BF76" s="7" t="n"/>
+      <c r="BG76" s="7" t="n"/>
+      <c r="BH76" s="7" t="n"/>
+      <c r="BI76" s="7" t="n"/>
+      <c r="BJ76" s="7" t="n"/>
+      <c r="BK76" s="7" t="n"/>
+      <c r="BL76" s="7" t="n"/>
+      <c r="BM76" s="7" t="n"/>
+      <c r="BN76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -34786,6 +38362,50 @@
       <c r="AJ77" s="7" t="n"/>
       <c r="AK77" s="7" t="n"/>
       <c r="AL77" s="7" t="n"/>
+      <c r="AM77" s="7" t="n"/>
+      <c r="AN77" s="7" t="n"/>
+      <c r="AO77" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AP77" s="7" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
+      <c r="AQ77" s="7" t="n"/>
+      <c r="AR77" s="7" t="n"/>
+      <c r="AS77" s="7" t="n"/>
+      <c r="AT77" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AU77" s="7" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
+      <c r="AV77" s="7" t="n"/>
+      <c r="AW77" s="7" t="n"/>
+      <c r="AX77" s="7" t="n"/>
+      <c r="AY77" s="7" t="n"/>
+      <c r="AZ77" s="7" t="n"/>
+      <c r="BA77" s="7" t="n"/>
+      <c r="BB77" s="7" t="n"/>
+      <c r="BC77" s="7" t="n"/>
+      <c r="BD77" s="7" t="n"/>
+      <c r="BE77" s="7" t="n"/>
+      <c r="BF77" s="7" t="n"/>
+      <c r="BG77" s="7" t="n"/>
+      <c r="BH77" s="7" t="n"/>
+      <c r="BI77" s="7" t="n"/>
+      <c r="BJ77" s="7" t="n"/>
+      <c r="BK77" s="7" t="n"/>
+      <c r="BL77" s="7" t="n"/>
+      <c r="BM77" s="7" t="n"/>
+      <c r="BN77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -34888,8 +38508,16 @@
       <c r="Z78" s="7" t="n"/>
       <c r="AA78" s="7" t="n"/>
       <c r="AB78" s="7" t="n"/>
-      <c r="AC78" s="7" t="n"/>
-      <c r="AD78" s="7" t="n"/>
+      <c r="AC78" s="7" t="inlineStr">
+        <is>
+          <t>LARGE;MEDIUM;SMALL</t>
+        </is>
+      </c>
+      <c r="AD78" s="7" t="inlineStr">
+        <is>
+          <t>C49508;C49507;C25376</t>
+        </is>
+      </c>
       <c r="AE78" s="7" t="n"/>
       <c r="AF78" s="7" t="n"/>
       <c r="AG78" s="7" t="n"/>
@@ -34898,6 +38526,34 @@
       <c r="AJ78" s="7" t="n"/>
       <c r="AK78" s="7" t="n"/>
       <c r="AL78" s="7" t="n"/>
+      <c r="AM78" s="7" t="n"/>
+      <c r="AN78" s="7" t="n"/>
+      <c r="AO78" s="7" t="n"/>
+      <c r="AP78" s="7" t="n"/>
+      <c r="AQ78" s="7" t="n"/>
+      <c r="AR78" s="7" t="n"/>
+      <c r="AS78" s="7" t="n"/>
+      <c r="AT78" s="7" t="n"/>
+      <c r="AU78" s="7" t="n"/>
+      <c r="AV78" s="7" t="n"/>
+      <c r="AW78" s="7" t="n"/>
+      <c r="AX78" s="7" t="n"/>
+      <c r="AY78" s="7" t="n"/>
+      <c r="AZ78" s="7" t="n"/>
+      <c r="BA78" s="7" t="n"/>
+      <c r="BB78" s="7" t="n"/>
+      <c r="BC78" s="7" t="n"/>
+      <c r="BD78" s="7" t="n"/>
+      <c r="BE78" s="7" t="n"/>
+      <c r="BF78" s="7" t="n"/>
+      <c r="BG78" s="7" t="n"/>
+      <c r="BH78" s="7" t="n"/>
+      <c r="BI78" s="7" t="n"/>
+      <c r="BJ78" s="7" t="n"/>
+      <c r="BK78" s="7" t="n"/>
+      <c r="BL78" s="7" t="n"/>
+      <c r="BM78" s="7" t="n"/>
+      <c r="BN78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -35012,12 +38668,56 @@
       <c r="AH79" s="7" t="n"/>
       <c r="AI79" s="7" t="n"/>
       <c r="AJ79" s="7" t="n"/>
-      <c r="AK79" s="7" t="inlineStr">
+      <c r="AK79" s="7" t="n"/>
+      <c r="AL79" s="7" t="n"/>
+      <c r="AM79" s="7" t="n"/>
+      <c r="AN79" s="7" t="n"/>
+      <c r="AO79" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB;oz</t>
+        </is>
+      </c>
+      <c r="AP79" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AQ79" s="7" t="n"/>
+      <c r="AR79" s="7" t="n"/>
+      <c r="AS79" s="7" t="n"/>
+      <c r="AT79" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB;oz</t>
+        </is>
+      </c>
+      <c r="AU79" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531;C48519</t>
+        </is>
+      </c>
+      <c r="AV79" s="7" t="n"/>
+      <c r="AW79" s="7" t="n"/>
+      <c r="AX79" s="7" t="n"/>
+      <c r="AY79" s="7" t="n"/>
+      <c r="AZ79" s="7" t="n"/>
+      <c r="BA79" s="7" t="n"/>
+      <c r="BB79" s="7" t="n"/>
+      <c r="BC79" s="7" t="n"/>
+      <c r="BD79" s="7" t="n"/>
+      <c r="BE79" s="7" t="n"/>
+      <c r="BF79" s="7" t="n"/>
+      <c r="BG79" s="7" t="n"/>
+      <c r="BH79" s="7" t="n"/>
+      <c r="BI79" s="7" t="n"/>
+      <c r="BJ79" s="7" t="n"/>
+      <c r="BK79" s="7" t="n"/>
+      <c r="BL79" s="7" t="n"/>
+      <c r="BM79" s="7" t="inlineStr">
         <is>
           <t>89087-1</t>
         </is>
       </c>
-      <c r="AL79" s="7" t="n"/>
+      <c r="BN79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -35132,12 +38832,56 @@
       <c r="AH80" s="7" t="n"/>
       <c r="AI80" s="7" t="n"/>
       <c r="AJ80" s="7" t="n"/>
-      <c r="AK80" s="7" t="inlineStr">
+      <c r="AK80" s="7" t="n"/>
+      <c r="AL80" s="7" t="n"/>
+      <c r="AM80" s="7" t="n"/>
+      <c r="AN80" s="7" t="n"/>
+      <c r="AO80" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP80" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ80" s="7" t="n"/>
+      <c r="AR80" s="7" t="n"/>
+      <c r="AS80" s="7" t="n"/>
+      <c r="AT80" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU80" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV80" s="7" t="n"/>
+      <c r="AW80" s="7" t="n"/>
+      <c r="AX80" s="7" t="n"/>
+      <c r="AY80" s="7" t="n"/>
+      <c r="AZ80" s="7" t="n"/>
+      <c r="BA80" s="7" t="n"/>
+      <c r="BB80" s="7" t="n"/>
+      <c r="BC80" s="7" t="n"/>
+      <c r="BD80" s="7" t="n"/>
+      <c r="BE80" s="7" t="n"/>
+      <c r="BF80" s="7" t="n"/>
+      <c r="BG80" s="7" t="n"/>
+      <c r="BH80" s="7" t="n"/>
+      <c r="BI80" s="7" t="n"/>
+      <c r="BJ80" s="7" t="n"/>
+      <c r="BK80" s="7" t="n"/>
+      <c r="BL80" s="7" t="n"/>
+      <c r="BM80" s="7" t="inlineStr">
         <is>
           <t>55283-6</t>
         </is>
       </c>
-      <c r="AL80" s="7" t="n"/>
+      <c r="BN80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -35252,12 +38996,56 @@
       <c r="AH81" s="7" t="n"/>
       <c r="AI81" s="7" t="n"/>
       <c r="AJ81" s="7" t="n"/>
-      <c r="AK81" s="7" t="inlineStr">
+      <c r="AK81" s="7" t="n"/>
+      <c r="AL81" s="7" t="n"/>
+      <c r="AM81" s="7" t="n"/>
+      <c r="AN81" s="7" t="n"/>
+      <c r="AO81" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AP81" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AQ81" s="7" t="n"/>
+      <c r="AR81" s="7" t="n"/>
+      <c r="AS81" s="7" t="n"/>
+      <c r="AT81" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AU81" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AV81" s="7" t="n"/>
+      <c r="AW81" s="7" t="n"/>
+      <c r="AX81" s="7" t="n"/>
+      <c r="AY81" s="7" t="n"/>
+      <c r="AZ81" s="7" t="n"/>
+      <c r="BA81" s="7" t="n"/>
+      <c r="BB81" s="7" t="n"/>
+      <c r="BC81" s="7" t="n"/>
+      <c r="BD81" s="7" t="n"/>
+      <c r="BE81" s="7" t="n"/>
+      <c r="BF81" s="7" t="n"/>
+      <c r="BG81" s="7" t="n"/>
+      <c r="BH81" s="7" t="n"/>
+      <c r="BI81" s="7" t="n"/>
+      <c r="BJ81" s="7" t="n"/>
+      <c r="BK81" s="7" t="n"/>
+      <c r="BL81" s="7" t="n"/>
+      <c r="BM81" s="7" t="inlineStr">
         <is>
           <t>55283-6</t>
         </is>
       </c>
-      <c r="AL81" s="7" t="n"/>
+      <c r="BN81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -35374,6 +39162,50 @@
       <c r="AJ82" s="7" t="n"/>
       <c r="AK82" s="7" t="n"/>
       <c r="AL82" s="7" t="n"/>
+      <c r="AM82" s="7" t="n"/>
+      <c r="AN82" s="7" t="n"/>
+      <c r="AO82" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP82" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ82" s="7" t="n"/>
+      <c r="AR82" s="7" t="n"/>
+      <c r="AS82" s="7" t="n"/>
+      <c r="AT82" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU82" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV82" s="7" t="n"/>
+      <c r="AW82" s="7" t="n"/>
+      <c r="AX82" s="7" t="n"/>
+      <c r="AY82" s="7" t="n"/>
+      <c r="AZ82" s="7" t="n"/>
+      <c r="BA82" s="7" t="n"/>
+      <c r="BB82" s="7" t="n"/>
+      <c r="BC82" s="7" t="n"/>
+      <c r="BD82" s="7" t="n"/>
+      <c r="BE82" s="7" t="n"/>
+      <c r="BF82" s="7" t="n"/>
+      <c r="BG82" s="7" t="n"/>
+      <c r="BH82" s="7" t="n"/>
+      <c r="BI82" s="7" t="n"/>
+      <c r="BJ82" s="7" t="n"/>
+      <c r="BK82" s="7" t="n"/>
+      <c r="BL82" s="7" t="n"/>
+      <c r="BM82" s="7" t="n"/>
+      <c r="BN82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -35490,6 +39322,50 @@
       <c r="AJ83" s="7" t="n"/>
       <c r="AK83" s="7" t="n"/>
       <c r="AL83" s="7" t="n"/>
+      <c r="AM83" s="7" t="n"/>
+      <c r="AN83" s="7" t="n"/>
+      <c r="AO83" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP83" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ83" s="7" t="n"/>
+      <c r="AR83" s="7" t="n"/>
+      <c r="AS83" s="7" t="n"/>
+      <c r="AT83" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU83" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV83" s="7" t="n"/>
+      <c r="AW83" s="7" t="n"/>
+      <c r="AX83" s="7" t="n"/>
+      <c r="AY83" s="7" t="n"/>
+      <c r="AZ83" s="7" t="n"/>
+      <c r="BA83" s="7" t="n"/>
+      <c r="BB83" s="7" t="n"/>
+      <c r="BC83" s="7" t="n"/>
+      <c r="BD83" s="7" t="n"/>
+      <c r="BE83" s="7" t="n"/>
+      <c r="BF83" s="7" t="n"/>
+      <c r="BG83" s="7" t="n"/>
+      <c r="BH83" s="7" t="n"/>
+      <c r="BI83" s="7" t="n"/>
+      <c r="BJ83" s="7" t="n"/>
+      <c r="BK83" s="7" t="n"/>
+      <c r="BL83" s="7" t="n"/>
+      <c r="BM83" s="7" t="n"/>
+      <c r="BN83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -35606,6 +39482,34 @@
       <c r="AJ84" s="7" t="n"/>
       <c r="AK84" s="7" t="n"/>
       <c r="AL84" s="7" t="n"/>
+      <c r="AM84" s="7" t="n"/>
+      <c r="AN84" s="7" t="n"/>
+      <c r="AO84" s="7" t="n"/>
+      <c r="AP84" s="7" t="n"/>
+      <c r="AQ84" s="7" t="n"/>
+      <c r="AR84" s="7" t="n"/>
+      <c r="AS84" s="7" t="n"/>
+      <c r="AT84" s="7" t="n"/>
+      <c r="AU84" s="7" t="n"/>
+      <c r="AV84" s="7" t="n"/>
+      <c r="AW84" s="7" t="n"/>
+      <c r="AX84" s="7" t="n"/>
+      <c r="AY84" s="7" t="n"/>
+      <c r="AZ84" s="7" t="n"/>
+      <c r="BA84" s="7" t="n"/>
+      <c r="BB84" s="7" t="n"/>
+      <c r="BC84" s="7" t="n"/>
+      <c r="BD84" s="7" t="n"/>
+      <c r="BE84" s="7" t="n"/>
+      <c r="BF84" s="7" t="n"/>
+      <c r="BG84" s="7" t="n"/>
+      <c r="BH84" s="7" t="n"/>
+      <c r="BI84" s="7" t="n"/>
+      <c r="BJ84" s="7" t="n"/>
+      <c r="BK84" s="7" t="n"/>
+      <c r="BL84" s="7" t="n"/>
+      <c r="BM84" s="7" t="n"/>
+      <c r="BN84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -35720,12 +39624,40 @@
       <c r="AH85" s="7" t="n"/>
       <c r="AI85" s="7" t="n"/>
       <c r="AJ85" s="7" t="n"/>
-      <c r="AK85" s="7" t="inlineStr">
+      <c r="AK85" s="7" t="n"/>
+      <c r="AL85" s="7" t="n"/>
+      <c r="AM85" s="7" t="n"/>
+      <c r="AN85" s="7" t="n"/>
+      <c r="AO85" s="7" t="n"/>
+      <c r="AP85" s="7" t="n"/>
+      <c r="AQ85" s="7" t="n"/>
+      <c r="AR85" s="7" t="n"/>
+      <c r="AS85" s="7" t="n"/>
+      <c r="AT85" s="7" t="n"/>
+      <c r="AU85" s="7" t="n"/>
+      <c r="AV85" s="7" t="n"/>
+      <c r="AW85" s="7" t="n"/>
+      <c r="AX85" s="7" t="n"/>
+      <c r="AY85" s="7" t="n"/>
+      <c r="AZ85" s="7" t="n"/>
+      <c r="BA85" s="7" t="n"/>
+      <c r="BB85" s="7" t="n"/>
+      <c r="BC85" s="7" t="n"/>
+      <c r="BD85" s="7" t="n"/>
+      <c r="BE85" s="7" t="n"/>
+      <c r="BF85" s="7" t="n"/>
+      <c r="BG85" s="7" t="n"/>
+      <c r="BH85" s="7" t="n"/>
+      <c r="BI85" s="7" t="n"/>
+      <c r="BJ85" s="7" t="n"/>
+      <c r="BK85" s="7" t="n"/>
+      <c r="BL85" s="7" t="n"/>
+      <c r="BM85" s="7" t="inlineStr">
         <is>
           <t>11766-3</t>
         </is>
       </c>
-      <c r="AL85" s="7" t="n"/>
+      <c r="BN85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -35836,12 +39768,40 @@
       <c r="AH86" s="7" t="n"/>
       <c r="AI86" s="7" t="n"/>
       <c r="AJ86" s="7" t="n"/>
-      <c r="AK86" s="7" t="inlineStr">
+      <c r="AK86" s="7" t="n"/>
+      <c r="AL86" s="7" t="n"/>
+      <c r="AM86" s="7" t="n"/>
+      <c r="AN86" s="7" t="n"/>
+      <c r="AO86" s="7" t="n"/>
+      <c r="AP86" s="7" t="n"/>
+      <c r="AQ86" s="7" t="n"/>
+      <c r="AR86" s="7" t="n"/>
+      <c r="AS86" s="7" t="n"/>
+      <c r="AT86" s="7" t="n"/>
+      <c r="AU86" s="7" t="n"/>
+      <c r="AV86" s="7" t="n"/>
+      <c r="AW86" s="7" t="n"/>
+      <c r="AX86" s="7" t="n"/>
+      <c r="AY86" s="7" t="n"/>
+      <c r="AZ86" s="7" t="n"/>
+      <c r="BA86" s="7" t="n"/>
+      <c r="BB86" s="7" t="n"/>
+      <c r="BC86" s="7" t="n"/>
+      <c r="BD86" s="7" t="n"/>
+      <c r="BE86" s="7" t="n"/>
+      <c r="BF86" s="7" t="n"/>
+      <c r="BG86" s="7" t="n"/>
+      <c r="BH86" s="7" t="n"/>
+      <c r="BI86" s="7" t="n"/>
+      <c r="BJ86" s="7" t="n"/>
+      <c r="BK86" s="7" t="n"/>
+      <c r="BL86" s="7" t="n"/>
+      <c r="BM86" s="7" t="inlineStr">
         <is>
           <t>Jan-89</t>
         </is>
       </c>
-      <c r="AL86" s="7" t="n"/>
+      <c r="BN86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -35956,12 +39916,56 @@
       <c r="AH87" s="7" t="n"/>
       <c r="AI87" s="7" t="n"/>
       <c r="AJ87" s="7" t="n"/>
-      <c r="AK87" s="7" t="inlineStr">
+      <c r="AK87" s="7" t="n"/>
+      <c r="AL87" s="7" t="n"/>
+      <c r="AM87" s="7" t="n"/>
+      <c r="AN87" s="7" t="n"/>
+      <c r="AO87" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP87" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ87" s="7" t="n"/>
+      <c r="AR87" s="7" t="n"/>
+      <c r="AS87" s="7" t="n"/>
+      <c r="AT87" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU87" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV87" s="7" t="n"/>
+      <c r="AW87" s="7" t="n"/>
+      <c r="AX87" s="7" t="n"/>
+      <c r="AY87" s="7" t="n"/>
+      <c r="AZ87" s="7" t="n"/>
+      <c r="BA87" s="7" t="n"/>
+      <c r="BB87" s="7" t="n"/>
+      <c r="BC87" s="7" t="n"/>
+      <c r="BD87" s="7" t="n"/>
+      <c r="BE87" s="7" t="n"/>
+      <c r="BF87" s="7" t="n"/>
+      <c r="BG87" s="7" t="n"/>
+      <c r="BH87" s="7" t="n"/>
+      <c r="BI87" s="7" t="n"/>
+      <c r="BJ87" s="7" t="n"/>
+      <c r="BK87" s="7" t="n"/>
+      <c r="BL87" s="7" t="n"/>
+      <c r="BM87" s="7" t="inlineStr">
         <is>
           <t>9843-4</t>
         </is>
       </c>
-      <c r="AL87" s="7" t="n"/>
+      <c r="BN87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -36076,12 +40080,48 @@
       <c r="AH88" s="7" t="n"/>
       <c r="AI88" s="7" t="n"/>
       <c r="AJ88" s="7" t="n"/>
-      <c r="AK88" s="7" t="inlineStr">
+      <c r="AK88" s="7" t="n"/>
+      <c r="AL88" s="7" t="n"/>
+      <c r="AM88" s="7" t="n"/>
+      <c r="AN88" s="7" t="n"/>
+      <c r="AO88" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;m</t>
+        </is>
+      </c>
+      <c r="AP88" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C41139</t>
+        </is>
+      </c>
+      <c r="AQ88" s="7" t="n"/>
+      <c r="AR88" s="7" t="n"/>
+      <c r="AS88" s="7" t="n"/>
+      <c r="AT88" s="7" t="n"/>
+      <c r="AU88" s="7" t="n"/>
+      <c r="AV88" s="7" t="n"/>
+      <c r="AW88" s="7" t="n"/>
+      <c r="AX88" s="7" t="n"/>
+      <c r="AY88" s="7" t="n"/>
+      <c r="AZ88" s="7" t="n"/>
+      <c r="BA88" s="7" t="n"/>
+      <c r="BB88" s="7" t="n"/>
+      <c r="BC88" s="7" t="n"/>
+      <c r="BD88" s="7" t="n"/>
+      <c r="BE88" s="7" t="n"/>
+      <c r="BF88" s="7" t="n"/>
+      <c r="BG88" s="7" t="n"/>
+      <c r="BH88" s="7" t="n"/>
+      <c r="BI88" s="7" t="n"/>
+      <c r="BJ88" s="7" t="n"/>
+      <c r="BK88" s="7" t="n"/>
+      <c r="BL88" s="7" t="n"/>
+      <c r="BM88" s="7" t="inlineStr">
         <is>
           <t>8302-2</t>
         </is>
       </c>
-      <c r="AL88" s="7" t="n"/>
+      <c r="BN88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -36198,6 +40238,50 @@
       <c r="AJ89" s="7" t="n"/>
       <c r="AK89" s="7" t="n"/>
       <c r="AL89" s="7" t="n"/>
+      <c r="AM89" s="7" t="n"/>
+      <c r="AN89" s="7" t="n"/>
+      <c r="AO89" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP89" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ89" s="7" t="n"/>
+      <c r="AR89" s="7" t="n"/>
+      <c r="AS89" s="7" t="n"/>
+      <c r="AT89" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU89" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV89" s="7" t="n"/>
+      <c r="AW89" s="7" t="n"/>
+      <c r="AX89" s="7" t="n"/>
+      <c r="AY89" s="7" t="n"/>
+      <c r="AZ89" s="7" t="n"/>
+      <c r="BA89" s="7" t="n"/>
+      <c r="BB89" s="7" t="n"/>
+      <c r="BC89" s="7" t="n"/>
+      <c r="BD89" s="7" t="n"/>
+      <c r="BE89" s="7" t="n"/>
+      <c r="BF89" s="7" t="n"/>
+      <c r="BG89" s="7" t="n"/>
+      <c r="BH89" s="7" t="n"/>
+      <c r="BI89" s="7" t="n"/>
+      <c r="BJ89" s="7" t="n"/>
+      <c r="BK89" s="7" t="n"/>
+      <c r="BL89" s="7" t="n"/>
+      <c r="BM89" s="7" t="n"/>
+      <c r="BN89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -36299,36 +40383,12 @@
       <c r="U90" s="7" t="n"/>
       <c r="V90" s="7" t="n"/>
       <c r="W90" s="7" t="n"/>
-      <c r="X90" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="Y90" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="Z90" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA90" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="AB90" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="AC90" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X90" s="7" t="n"/>
+      <c r="Y90" s="7" t="n"/>
+      <c r="Z90" s="7" t="n"/>
+      <c r="AA90" s="7" t="n"/>
+      <c r="AB90" s="7" t="n"/>
+      <c r="AC90" s="7" t="n"/>
       <c r="AD90" s="7" t="n"/>
       <c r="AE90" s="7" t="n"/>
       <c r="AF90" s="7" t="n"/>
@@ -36336,12 +40396,88 @@
       <c r="AH90" s="7" t="n"/>
       <c r="AI90" s="7" t="n"/>
       <c r="AJ90" s="7" t="n"/>
-      <c r="AK90" s="7" t="inlineStr">
+      <c r="AK90" s="7" t="n"/>
+      <c r="AL90" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AM90" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AN90" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO90" s="7" t="n"/>
+      <c r="AP90" s="7" t="n"/>
+      <c r="AQ90" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AR90" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AS90" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT90" s="7" t="n"/>
+      <c r="AU90" s="7" t="n"/>
+      <c r="AV90" s="7" t="n"/>
+      <c r="AW90" s="7" t="n"/>
+      <c r="AX90" s="7" t="n"/>
+      <c r="AY90" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ90" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+        </is>
+      </c>
+      <c r="BA90" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB90" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC90" s="7" t="inlineStr">
+        <is>
+          <t>PRONE;SEMI-RECUMBENT;SITTING;STANDING;SUPINE</t>
+        </is>
+      </c>
+      <c r="BD90" s="7" t="inlineStr">
+        <is>
+          <t>C62165;C111310;C62122;C62166;C62167</t>
+        </is>
+      </c>
+      <c r="BE90" s="7" t="n"/>
+      <c r="BF90" s="7" t="n"/>
+      <c r="BG90" s="7" t="n"/>
+      <c r="BH90" s="7" t="n"/>
+      <c r="BI90" s="7" t="n"/>
+      <c r="BJ90" s="7" t="n"/>
+      <c r="BK90" s="7" t="n"/>
+      <c r="BL90" s="7" t="n"/>
+      <c r="BM90" s="7" t="inlineStr">
         <is>
           <t>8867-4</t>
         </is>
       </c>
-      <c r="AL90" s="7" t="inlineStr">
+      <c r="BN90" s="7" t="inlineStr">
         <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
@@ -36462,6 +40598,50 @@
       <c r="AJ91" s="7" t="n"/>
       <c r="AK91" s="7" t="n"/>
       <c r="AL91" s="7" t="n"/>
+      <c r="AM91" s="7" t="n"/>
+      <c r="AN91" s="7" t="n"/>
+      <c r="AO91" s="7" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="AP91" s="7" t="inlineStr">
+        <is>
+          <t>C41140</t>
+        </is>
+      </c>
+      <c r="AQ91" s="7" t="n"/>
+      <c r="AR91" s="7" t="n"/>
+      <c r="AS91" s="7" t="n"/>
+      <c r="AT91" s="7" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="AU91" s="7" t="inlineStr">
+        <is>
+          <t>C41140</t>
+        </is>
+      </c>
+      <c r="AV91" s="7" t="n"/>
+      <c r="AW91" s="7" t="n"/>
+      <c r="AX91" s="7" t="n"/>
+      <c r="AY91" s="7" t="n"/>
+      <c r="AZ91" s="7" t="n"/>
+      <c r="BA91" s="7" t="n"/>
+      <c r="BB91" s="7" t="n"/>
+      <c r="BC91" s="7" t="n"/>
+      <c r="BD91" s="7" t="n"/>
+      <c r="BE91" s="7" t="n"/>
+      <c r="BF91" s="7" t="n"/>
+      <c r="BG91" s="7" t="n"/>
+      <c r="BH91" s="7" t="n"/>
+      <c r="BI91" s="7" t="n"/>
+      <c r="BJ91" s="7" t="n"/>
+      <c r="BK91" s="7" t="n"/>
+      <c r="BL91" s="7" t="n"/>
+      <c r="BM91" s="7" t="n"/>
+      <c r="BN91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -36578,6 +40758,50 @@
       <c r="AJ92" s="7" t="n"/>
       <c r="AK92" s="7" t="n"/>
       <c r="AL92" s="7" t="n"/>
+      <c r="AM92" s="7" t="n"/>
+      <c r="AN92" s="7" t="n"/>
+      <c r="AO92" s="7" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="AP92" s="7" t="inlineStr">
+        <is>
+          <t>C41140</t>
+        </is>
+      </c>
+      <c r="AQ92" s="7" t="n"/>
+      <c r="AR92" s="7" t="n"/>
+      <c r="AS92" s="7" t="n"/>
+      <c r="AT92" s="7" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="AU92" s="7" t="inlineStr">
+        <is>
+          <t>C41140</t>
+        </is>
+      </c>
+      <c r="AV92" s="7" t="n"/>
+      <c r="AW92" s="7" t="n"/>
+      <c r="AX92" s="7" t="n"/>
+      <c r="AY92" s="7" t="n"/>
+      <c r="AZ92" s="7" t="n"/>
+      <c r="BA92" s="7" t="n"/>
+      <c r="BB92" s="7" t="n"/>
+      <c r="BC92" s="7" t="n"/>
+      <c r="BD92" s="7" t="n"/>
+      <c r="BE92" s="7" t="n"/>
+      <c r="BF92" s="7" t="n"/>
+      <c r="BG92" s="7" t="n"/>
+      <c r="BH92" s="7" t="n"/>
+      <c r="BI92" s="7" t="n"/>
+      <c r="BJ92" s="7" t="n"/>
+      <c r="BK92" s="7" t="n"/>
+      <c r="BL92" s="7" t="n"/>
+      <c r="BM92" s="7" t="n"/>
+      <c r="BN92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -36679,36 +40903,12 @@
       <c r="U93" s="7" t="n"/>
       <c r="V93" s="7" t="n"/>
       <c r="W93" s="7" t="n"/>
-      <c r="X93" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="Y93" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="Z93" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA93" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="AB93" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="AC93" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X93" s="7" t="n"/>
+      <c r="Y93" s="7" t="n"/>
+      <c r="Z93" s="7" t="n"/>
+      <c r="AA93" s="7" t="n"/>
+      <c r="AB93" s="7" t="n"/>
+      <c r="AC93" s="7" t="n"/>
       <c r="AD93" s="7" t="n"/>
       <c r="AE93" s="7" t="n"/>
       <c r="AF93" s="7" t="n"/>
@@ -36716,12 +40916,88 @@
       <c r="AH93" s="7" t="n"/>
       <c r="AI93" s="7" t="n"/>
       <c r="AJ93" s="7" t="n"/>
-      <c r="AK93" s="7" t="inlineStr">
+      <c r="AK93" s="7" t="n"/>
+      <c r="AL93" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AM93" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AN93" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO93" s="7" t="n"/>
+      <c r="AP93" s="7" t="n"/>
+      <c r="AQ93" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AR93" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AS93" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT93" s="7" t="n"/>
+      <c r="AU93" s="7" t="n"/>
+      <c r="AV93" s="7" t="n"/>
+      <c r="AW93" s="7" t="n"/>
+      <c r="AX93" s="7" t="n"/>
+      <c r="AY93" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ93" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+        </is>
+      </c>
+      <c r="BA93" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB93" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC93" s="7" t="inlineStr">
+        <is>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING, LEGS DEPENDENT;SLING;STANDING;STANDING, BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+        </is>
+      </c>
+      <c r="BD93" s="7" t="inlineStr">
+        <is>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C150885;C92604;C62166;C174357;C62167;C62168;C90480</t>
+        </is>
+      </c>
+      <c r="BE93" s="7" t="n"/>
+      <c r="BF93" s="7" t="n"/>
+      <c r="BG93" s="7" t="n"/>
+      <c r="BH93" s="7" t="n"/>
+      <c r="BI93" s="7" t="n"/>
+      <c r="BJ93" s="7" t="n"/>
+      <c r="BK93" s="7" t="n"/>
+      <c r="BL93" s="7" t="n"/>
+      <c r="BM93" s="7" t="inlineStr">
         <is>
           <t>8867-4</t>
         </is>
       </c>
-      <c r="AL93" s="7" t="inlineStr">
+      <c r="BN93" s="7" t="inlineStr">
         <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
@@ -36836,12 +41112,40 @@
       <c r="AH94" s="7" t="n"/>
       <c r="AI94" s="7" t="n"/>
       <c r="AJ94" s="7" t="n"/>
-      <c r="AK94" s="7" t="inlineStr">
+      <c r="AK94" s="7" t="n"/>
+      <c r="AL94" s="7" t="n"/>
+      <c r="AM94" s="7" t="n"/>
+      <c r="AN94" s="7" t="n"/>
+      <c r="AO94" s="7" t="n"/>
+      <c r="AP94" s="7" t="n"/>
+      <c r="AQ94" s="7" t="n"/>
+      <c r="AR94" s="7" t="n"/>
+      <c r="AS94" s="7" t="n"/>
+      <c r="AT94" s="7" t="n"/>
+      <c r="AU94" s="7" t="n"/>
+      <c r="AV94" s="7" t="n"/>
+      <c r="AW94" s="7" t="n"/>
+      <c r="AX94" s="7" t="n"/>
+      <c r="AY94" s="7" t="n"/>
+      <c r="AZ94" s="7" t="n"/>
+      <c r="BA94" s="7" t="n"/>
+      <c r="BB94" s="7" t="n"/>
+      <c r="BC94" s="7" t="n"/>
+      <c r="BD94" s="7" t="n"/>
+      <c r="BE94" s="7" t="n"/>
+      <c r="BF94" s="7" t="n"/>
+      <c r="BG94" s="7" t="n"/>
+      <c r="BH94" s="7" t="n"/>
+      <c r="BI94" s="7" t="n"/>
+      <c r="BJ94" s="7" t="n"/>
+      <c r="BK94" s="7" t="n"/>
+      <c r="BL94" s="7" t="n"/>
+      <c r="BM94" s="7" t="inlineStr">
         <is>
           <t>8303-0</t>
         </is>
       </c>
-      <c r="AL94" s="7" t="n"/>
+      <c r="BN94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -36956,12 +41260,56 @@
       <c r="AH95" s="7" t="n"/>
       <c r="AI95" s="7" t="n"/>
       <c r="AJ95" s="7" t="n"/>
-      <c r="AK95" s="7" t="inlineStr">
+      <c r="AK95" s="7" t="n"/>
+      <c r="AL95" s="7" t="n"/>
+      <c r="AM95" s="7" t="n"/>
+      <c r="AN95" s="7" t="n"/>
+      <c r="AO95" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AP95" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AQ95" s="7" t="n"/>
+      <c r="AR95" s="7" t="n"/>
+      <c r="AS95" s="7" t="n"/>
+      <c r="AT95" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AU95" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AV95" s="7" t="n"/>
+      <c r="AW95" s="7" t="n"/>
+      <c r="AX95" s="7" t="n"/>
+      <c r="AY95" s="7" t="n"/>
+      <c r="AZ95" s="7" t="n"/>
+      <c r="BA95" s="7" t="n"/>
+      <c r="BB95" s="7" t="n"/>
+      <c r="BC95" s="7" t="n"/>
+      <c r="BD95" s="7" t="n"/>
+      <c r="BE95" s="7" t="n"/>
+      <c r="BF95" s="7" t="n"/>
+      <c r="BG95" s="7" t="n"/>
+      <c r="BH95" s="7" t="n"/>
+      <c r="BI95" s="7" t="n"/>
+      <c r="BJ95" s="7" t="n"/>
+      <c r="BK95" s="7" t="n"/>
+      <c r="BL95" s="7" t="n"/>
+      <c r="BM95" s="7" t="inlineStr">
         <is>
           <t>50064-5</t>
         </is>
       </c>
-      <c r="AL95" s="7" t="n"/>
+      <c r="BN95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -37078,6 +41426,50 @@
       <c r="AJ96" s="7" t="n"/>
       <c r="AK96" s="7" t="n"/>
       <c r="AL96" s="7" t="n"/>
+      <c r="AM96" s="7" t="n"/>
+      <c r="AN96" s="7" t="n"/>
+      <c r="AO96" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP96" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ96" s="7" t="n"/>
+      <c r="AR96" s="7" t="n"/>
+      <c r="AS96" s="7" t="n"/>
+      <c r="AT96" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU96" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV96" s="7" t="n"/>
+      <c r="AW96" s="7" t="n"/>
+      <c r="AX96" s="7" t="n"/>
+      <c r="AY96" s="7" t="n"/>
+      <c r="AZ96" s="7" t="n"/>
+      <c r="BA96" s="7" t="n"/>
+      <c r="BB96" s="7" t="n"/>
+      <c r="BC96" s="7" t="n"/>
+      <c r="BD96" s="7" t="n"/>
+      <c r="BE96" s="7" t="n"/>
+      <c r="BF96" s="7" t="n"/>
+      <c r="BG96" s="7" t="n"/>
+      <c r="BH96" s="7" t="n"/>
+      <c r="BI96" s="7" t="n"/>
+      <c r="BJ96" s="7" t="n"/>
+      <c r="BK96" s="7" t="n"/>
+      <c r="BL96" s="7" t="n"/>
+      <c r="BM96" s="7" t="n"/>
+      <c r="BN96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -37192,12 +41584,56 @@
       <c r="AH97" s="7" t="n"/>
       <c r="AI97" s="7" t="n"/>
       <c r="AJ97" s="7" t="n"/>
-      <c r="AK97" s="7" t="inlineStr">
+      <c r="AK97" s="7" t="n"/>
+      <c r="AL97" s="7" t="n"/>
+      <c r="AM97" s="7" t="n"/>
+      <c r="AN97" s="7" t="n"/>
+      <c r="AO97" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AP97" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AQ97" s="7" t="n"/>
+      <c r="AR97" s="7" t="n"/>
+      <c r="AS97" s="7" t="n"/>
+      <c r="AT97" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AU97" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AV97" s="7" t="n"/>
+      <c r="AW97" s="7" t="n"/>
+      <c r="AX97" s="7" t="n"/>
+      <c r="AY97" s="7" t="n"/>
+      <c r="AZ97" s="7" t="n"/>
+      <c r="BA97" s="7" t="n"/>
+      <c r="BB97" s="7" t="n"/>
+      <c r="BC97" s="7" t="n"/>
+      <c r="BD97" s="7" t="n"/>
+      <c r="BE97" s="7" t="n"/>
+      <c r="BF97" s="7" t="n"/>
+      <c r="BG97" s="7" t="n"/>
+      <c r="BH97" s="7" t="n"/>
+      <c r="BI97" s="7" t="n"/>
+      <c r="BJ97" s="7" t="n"/>
+      <c r="BK97" s="7" t="n"/>
+      <c r="BL97" s="7" t="n"/>
+      <c r="BM97" s="7" t="inlineStr">
         <is>
           <t>91557-9</t>
         </is>
       </c>
-      <c r="AL97" s="7" t="n"/>
+      <c r="BN97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -37314,6 +41750,50 @@
       <c r="AJ98" s="7" t="n"/>
       <c r="AK98" s="7" t="n"/>
       <c r="AL98" s="7" t="n"/>
+      <c r="AM98" s="7" t="n"/>
+      <c r="AN98" s="7" t="n"/>
+      <c r="AO98" s="7" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="AP98" s="7" t="inlineStr">
+        <is>
+          <t>C44256</t>
+        </is>
+      </c>
+      <c r="AQ98" s="7" t="n"/>
+      <c r="AR98" s="7" t="n"/>
+      <c r="AS98" s="7" t="n"/>
+      <c r="AT98" s="7" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="AU98" s="7" t="inlineStr">
+        <is>
+          <t>C44256</t>
+        </is>
+      </c>
+      <c r="AV98" s="7" t="n"/>
+      <c r="AW98" s="7" t="n"/>
+      <c r="AX98" s="7" t="n"/>
+      <c r="AY98" s="7" t="n"/>
+      <c r="AZ98" s="7" t="n"/>
+      <c r="BA98" s="7" t="n"/>
+      <c r="BB98" s="7" t="n"/>
+      <c r="BC98" s="7" t="n"/>
+      <c r="BD98" s="7" t="n"/>
+      <c r="BE98" s="7" t="n"/>
+      <c r="BF98" s="7" t="n"/>
+      <c r="BG98" s="7" t="n"/>
+      <c r="BH98" s="7" t="n"/>
+      <c r="BI98" s="7" t="n"/>
+      <c r="BJ98" s="7" t="n"/>
+      <c r="BK98" s="7" t="n"/>
+      <c r="BL98" s="7" t="n"/>
+      <c r="BM98" s="7" t="n"/>
+      <c r="BN98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -37430,6 +41910,50 @@
       <c r="AJ99" s="7" t="n"/>
       <c r="AK99" s="7" t="n"/>
       <c r="AL99" s="7" t="n"/>
+      <c r="AM99" s="7" t="n"/>
+      <c r="AN99" s="7" t="n"/>
+      <c r="AO99" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AP99" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AQ99" s="7" t="n"/>
+      <c r="AR99" s="7" t="n"/>
+      <c r="AS99" s="7" t="n"/>
+      <c r="AT99" s="7" t="inlineStr">
+        <is>
+          <t>g;kg;LB</t>
+        </is>
+      </c>
+      <c r="AU99" s="7" t="inlineStr">
+        <is>
+          <t>C48155;C28252;C48531</t>
+        </is>
+      </c>
+      <c r="AV99" s="7" t="n"/>
+      <c r="AW99" s="7" t="n"/>
+      <c r="AX99" s="7" t="n"/>
+      <c r="AY99" s="7" t="n"/>
+      <c r="AZ99" s="7" t="n"/>
+      <c r="BA99" s="7" t="n"/>
+      <c r="BB99" s="7" t="n"/>
+      <c r="BC99" s="7" t="n"/>
+      <c r="BD99" s="7" t="n"/>
+      <c r="BE99" s="7" t="n"/>
+      <c r="BF99" s="7" t="n"/>
+      <c r="BG99" s="7" t="n"/>
+      <c r="BH99" s="7" t="n"/>
+      <c r="BI99" s="7" t="n"/>
+      <c r="BJ99" s="7" t="n"/>
+      <c r="BK99" s="7" t="n"/>
+      <c r="BL99" s="7" t="n"/>
+      <c r="BM99" s="7" t="n"/>
+      <c r="BN99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -37542,6 +42066,50 @@
       <c r="AJ100" s="7" t="n"/>
       <c r="AK100" s="7" t="n"/>
       <c r="AL100" s="7" t="n"/>
+      <c r="AM100" s="7" t="n"/>
+      <c r="AN100" s="7" t="n"/>
+      <c r="AO100" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP100" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ100" s="7" t="n"/>
+      <c r="AR100" s="7" t="n"/>
+      <c r="AS100" s="7" t="n"/>
+      <c r="AT100" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU100" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV100" s="7" t="n"/>
+      <c r="AW100" s="7" t="n"/>
+      <c r="AX100" s="7" t="n"/>
+      <c r="AY100" s="7" t="n"/>
+      <c r="AZ100" s="7" t="n"/>
+      <c r="BA100" s="7" t="n"/>
+      <c r="BB100" s="7" t="n"/>
+      <c r="BC100" s="7" t="n"/>
+      <c r="BD100" s="7" t="n"/>
+      <c r="BE100" s="7" t="n"/>
+      <c r="BF100" s="7" t="n"/>
+      <c r="BG100" s="7" t="n"/>
+      <c r="BH100" s="7" t="n"/>
+      <c r="BI100" s="7" t="n"/>
+      <c r="BJ100" s="7" t="n"/>
+      <c r="BK100" s="7" t="n"/>
+      <c r="BL100" s="7" t="n"/>
+      <c r="BM100" s="7" t="n"/>
+      <c r="BN100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -37658,6 +42226,50 @@
       <c r="AJ101" s="7" t="n"/>
       <c r="AK101" s="7" t="n"/>
       <c r="AL101" s="7" t="n"/>
+      <c r="AM101" s="7" t="n"/>
+      <c r="AN101" s="7" t="n"/>
+      <c r="AO101" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AP101" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AQ101" s="7" t="n"/>
+      <c r="AR101" s="7" t="n"/>
+      <c r="AS101" s="7" t="n"/>
+      <c r="AT101" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AU101" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AV101" s="7" t="n"/>
+      <c r="AW101" s="7" t="n"/>
+      <c r="AX101" s="7" t="n"/>
+      <c r="AY101" s="7" t="n"/>
+      <c r="AZ101" s="7" t="n"/>
+      <c r="BA101" s="7" t="n"/>
+      <c r="BB101" s="7" t="n"/>
+      <c r="BC101" s="7" t="n"/>
+      <c r="BD101" s="7" t="n"/>
+      <c r="BE101" s="7" t="n"/>
+      <c r="BF101" s="7" t="n"/>
+      <c r="BG101" s="7" t="n"/>
+      <c r="BH101" s="7" t="n"/>
+      <c r="BI101" s="7" t="n"/>
+      <c r="BJ101" s="7" t="n"/>
+      <c r="BK101" s="7" t="n"/>
+      <c r="BL101" s="7" t="n"/>
+      <c r="BM101" s="7" t="n"/>
+      <c r="BN101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -37774,6 +42386,50 @@
       <c r="AJ102" s="7" t="n"/>
       <c r="AK102" s="7" t="n"/>
       <c r="AL102" s="7" t="n"/>
+      <c r="AM102" s="7" t="n"/>
+      <c r="AN102" s="7" t="n"/>
+      <c r="AO102" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AP102" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AQ102" s="7" t="n"/>
+      <c r="AR102" s="7" t="n"/>
+      <c r="AS102" s="7" t="n"/>
+      <c r="AT102" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AU102" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AV102" s="7" t="n"/>
+      <c r="AW102" s="7" t="n"/>
+      <c r="AX102" s="7" t="n"/>
+      <c r="AY102" s="7" t="n"/>
+      <c r="AZ102" s="7" t="n"/>
+      <c r="BA102" s="7" t="n"/>
+      <c r="BB102" s="7" t="n"/>
+      <c r="BC102" s="7" t="n"/>
+      <c r="BD102" s="7" t="n"/>
+      <c r="BE102" s="7" t="n"/>
+      <c r="BF102" s="7" t="n"/>
+      <c r="BG102" s="7" t="n"/>
+      <c r="BH102" s="7" t="n"/>
+      <c r="BI102" s="7" t="n"/>
+      <c r="BJ102" s="7" t="n"/>
+      <c r="BK102" s="7" t="n"/>
+      <c r="BL102" s="7" t="n"/>
+      <c r="BM102" s="7" t="n"/>
+      <c r="BN102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -37890,6 +42546,50 @@
       <c r="AJ103" s="7" t="n"/>
       <c r="AK103" s="7" t="n"/>
       <c r="AL103" s="7" t="n"/>
+      <c r="AM103" s="7" t="n"/>
+      <c r="AN103" s="7" t="n"/>
+      <c r="AO103" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP103" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ103" s="7" t="n"/>
+      <c r="AR103" s="7" t="n"/>
+      <c r="AS103" s="7" t="n"/>
+      <c r="AT103" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU103" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV103" s="7" t="n"/>
+      <c r="AW103" s="7" t="n"/>
+      <c r="AX103" s="7" t="n"/>
+      <c r="AY103" s="7" t="n"/>
+      <c r="AZ103" s="7" t="n"/>
+      <c r="BA103" s="7" t="n"/>
+      <c r="BB103" s="7" t="n"/>
+      <c r="BC103" s="7" t="n"/>
+      <c r="BD103" s="7" t="n"/>
+      <c r="BE103" s="7" t="n"/>
+      <c r="BF103" s="7" t="n"/>
+      <c r="BG103" s="7" t="n"/>
+      <c r="BH103" s="7" t="n"/>
+      <c r="BI103" s="7" t="n"/>
+      <c r="BJ103" s="7" t="n"/>
+      <c r="BK103" s="7" t="n"/>
+      <c r="BL103" s="7" t="n"/>
+      <c r="BM103" s="7" t="n"/>
+      <c r="BN103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -38004,12 +42704,56 @@
       <c r="AH104" s="7" t="n"/>
       <c r="AI104" s="7" t="n"/>
       <c r="AJ104" s="7" t="n"/>
-      <c r="AK104" s="7" t="inlineStr">
+      <c r="AK104" s="7" t="n"/>
+      <c r="AL104" s="7" t="n"/>
+      <c r="AM104" s="7" t="n"/>
+      <c r="AN104" s="7" t="n"/>
+      <c r="AO104" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP104" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ104" s="7" t="n"/>
+      <c r="AR104" s="7" t="n"/>
+      <c r="AS104" s="7" t="n"/>
+      <c r="AT104" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU104" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV104" s="7" t="n"/>
+      <c r="AW104" s="7" t="n"/>
+      <c r="AX104" s="7" t="n"/>
+      <c r="AY104" s="7" t="n"/>
+      <c r="AZ104" s="7" t="n"/>
+      <c r="BA104" s="7" t="n"/>
+      <c r="BB104" s="7" t="n"/>
+      <c r="BC104" s="7" t="n"/>
+      <c r="BD104" s="7" t="n"/>
+      <c r="BE104" s="7" t="n"/>
+      <c r="BF104" s="7" t="n"/>
+      <c r="BG104" s="7" t="n"/>
+      <c r="BH104" s="7" t="n"/>
+      <c r="BI104" s="7" t="n"/>
+      <c r="BJ104" s="7" t="n"/>
+      <c r="BK104" s="7" t="n"/>
+      <c r="BL104" s="7" t="n"/>
+      <c r="BM104" s="7" t="inlineStr">
         <is>
           <t>56074-8</t>
         </is>
       </c>
-      <c r="AL104" s="7" t="n"/>
+      <c r="BN104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -38126,21 +42870,9 @@
       <c r="X105" s="7" t="n"/>
       <c r="Y105" s="7" t="n"/>
       <c r="Z105" s="7" t="n"/>
-      <c r="AA105" s="7" t="inlineStr">
-        <is>
-          <t>fraction of 1</t>
-        </is>
-      </c>
-      <c r="AB105" s="7" t="inlineStr">
-        <is>
-          <t>C105484</t>
-        </is>
-      </c>
-      <c r="AC105" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="AA105" s="7" t="n"/>
+      <c r="AB105" s="7" t="n"/>
+      <c r="AC105" s="7" t="n"/>
       <c r="AD105" s="7" t="n"/>
       <c r="AE105" s="7" t="n"/>
       <c r="AF105" s="7" t="n"/>
@@ -38150,6 +42882,70 @@
       <c r="AJ105" s="7" t="n"/>
       <c r="AK105" s="7" t="n"/>
       <c r="AL105" s="7" t="n"/>
+      <c r="AM105" s="7" t="n"/>
+      <c r="AN105" s="7" t="n"/>
+      <c r="AO105" s="7" t="inlineStr">
+        <is>
+          <t>%;fraction of 1</t>
+        </is>
+      </c>
+      <c r="AP105" s="7" t="inlineStr">
+        <is>
+          <t>C25613;</t>
+        </is>
+      </c>
+      <c r="AQ105" s="7" t="inlineStr">
+        <is>
+          <t>fraction of 1</t>
+        </is>
+      </c>
+      <c r="AR105" s="7" t="inlineStr">
+        <is>
+          <t>C105484</t>
+        </is>
+      </c>
+      <c r="AS105" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT105" s="7" t="n"/>
+      <c r="AU105" s="7" t="n"/>
+      <c r="AV105" s="7" t="n"/>
+      <c r="AW105" s="7" t="n"/>
+      <c r="AX105" s="7" t="n"/>
+      <c r="AY105" s="7" t="inlineStr">
+        <is>
+          <t>EARLOBE;FINGER</t>
+        </is>
+      </c>
+      <c r="AZ105" s="7" t="inlineStr">
+        <is>
+          <t>C32999;C32608</t>
+        </is>
+      </c>
+      <c r="BA105" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB105" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC105" s="7" t="n"/>
+      <c r="BD105" s="7" t="n"/>
+      <c r="BE105" s="7" t="n"/>
+      <c r="BF105" s="7" t="n"/>
+      <c r="BG105" s="7" t="n"/>
+      <c r="BH105" s="7" t="n"/>
+      <c r="BI105" s="7" t="n"/>
+      <c r="BJ105" s="7" t="n"/>
+      <c r="BK105" s="7" t="n"/>
+      <c r="BL105" s="7" t="n"/>
+      <c r="BM105" s="7" t="n"/>
+      <c r="BN105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -38251,36 +43047,12 @@
       <c r="U106" s="7" t="n"/>
       <c r="V106" s="7" t="n"/>
       <c r="W106" s="7" t="n"/>
-      <c r="X106" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="Y106" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="Z106" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA106" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="AB106" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="AC106" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X106" s="7" t="n"/>
+      <c r="Y106" s="7" t="n"/>
+      <c r="Z106" s="7" t="n"/>
+      <c r="AA106" s="7" t="n"/>
+      <c r="AB106" s="7" t="n"/>
+      <c r="AC106" s="7" t="n"/>
       <c r="AD106" s="7" t="n"/>
       <c r="AE106" s="7" t="n"/>
       <c r="AF106" s="7" t="n"/>
@@ -38290,6 +43062,82 @@
       <c r="AJ106" s="7" t="n"/>
       <c r="AK106" s="7" t="n"/>
       <c r="AL106" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AM106" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AN106" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO106" s="7" t="n"/>
+      <c r="AP106" s="7" t="n"/>
+      <c r="AQ106" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AR106" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AS106" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT106" s="7" t="n"/>
+      <c r="AU106" s="7" t="n"/>
+      <c r="AV106" s="7" t="n"/>
+      <c r="AW106" s="7" t="n"/>
+      <c r="AX106" s="7" t="n"/>
+      <c r="AY106" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ106" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+        </is>
+      </c>
+      <c r="BA106" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB106" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC106" s="7" t="inlineStr">
+        <is>
+          <t>PRONE;SEMI-RECUMBENT;SITTING;STANDING;SUPINE</t>
+        </is>
+      </c>
+      <c r="BD106" s="7" t="inlineStr">
+        <is>
+          <t>C62165;C111310;C62122;C62166;C62167</t>
+        </is>
+      </c>
+      <c r="BE106" s="7" t="n"/>
+      <c r="BF106" s="7" t="n"/>
+      <c r="BG106" s="7" t="n"/>
+      <c r="BH106" s="7" t="n"/>
+      <c r="BI106" s="7" t="n"/>
+      <c r="BJ106" s="7" t="n"/>
+      <c r="BK106" s="7" t="n"/>
+      <c r="BL106" s="7" t="n"/>
+      <c r="BM106" s="7" t="n"/>
+      <c r="BN106" s="7" t="inlineStr">
         <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
@@ -38408,12 +43256,64 @@
       <c r="AH107" s="7" t="n"/>
       <c r="AI107" s="7" t="n"/>
       <c r="AJ107" s="7" t="n"/>
-      <c r="AK107" s="7" t="inlineStr">
+      <c r="AK107" s="7" t="n"/>
+      <c r="AL107" s="7" t="n"/>
+      <c r="AM107" s="7" t="n"/>
+      <c r="AN107" s="7" t="n"/>
+      <c r="AO107" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AP107" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AQ107" s="7" t="n"/>
+      <c r="AR107" s="7" t="n"/>
+      <c r="AS107" s="7" t="n"/>
+      <c r="AT107" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AU107" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AV107" s="7" t="n"/>
+      <c r="AW107" s="7" t="n"/>
+      <c r="AX107" s="7" t="n"/>
+      <c r="AY107" s="7" t="n"/>
+      <c r="AZ107" s="7" t="n"/>
+      <c r="BA107" s="7" t="n"/>
+      <c r="BB107" s="7" t="n"/>
+      <c r="BC107" s="7" t="inlineStr">
+        <is>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING;LEGS DEPENDENT;SLING;STANDING;STANDING;BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+        </is>
+      </c>
+      <c r="BD107" s="7" t="inlineStr">
+        <is>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C62122;;C92604;C62166;C62166;;C62167;C62168;C90480</t>
+        </is>
+      </c>
+      <c r="BE107" s="7" t="n"/>
+      <c r="BF107" s="7" t="n"/>
+      <c r="BG107" s="7" t="n"/>
+      <c r="BH107" s="7" t="n"/>
+      <c r="BI107" s="7" t="n"/>
+      <c r="BJ107" s="7" t="n"/>
+      <c r="BK107" s="7" t="n"/>
+      <c r="BL107" s="7" t="n"/>
+      <c r="BM107" s="7" t="inlineStr">
         <is>
           <t>107146-3</t>
         </is>
       </c>
-      <c r="AL107" s="7" t="n"/>
+      <c r="BN107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
@@ -38515,36 +43415,12 @@
       <c r="U108" s="7" t="n"/>
       <c r="V108" s="7" t="n"/>
       <c r="W108" s="7" t="n"/>
-      <c r="X108" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="Y108" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="Z108" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA108" s="7" t="inlineStr">
-        <is>
-          <t>beats/min</t>
-        </is>
-      </c>
-      <c r="AB108" s="7" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-      <c r="AC108" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X108" s="7" t="n"/>
+      <c r="Y108" s="7" t="n"/>
+      <c r="Z108" s="7" t="n"/>
+      <c r="AA108" s="7" t="n"/>
+      <c r="AB108" s="7" t="n"/>
+      <c r="AC108" s="7" t="n"/>
       <c r="AD108" s="7" t="n"/>
       <c r="AE108" s="7" t="n"/>
       <c r="AF108" s="7" t="n"/>
@@ -38555,6 +43431,82 @@
       <c r="AK108" s="7" t="n"/>
       <c r="AL108" s="7" t="inlineStr">
         <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AM108" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AN108" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO108" s="7" t="n"/>
+      <c r="AP108" s="7" t="n"/>
+      <c r="AQ108" s="7" t="inlineStr">
+        <is>
+          <t>beats/min</t>
+        </is>
+      </c>
+      <c r="AR108" s="7" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
+      <c r="AS108" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT108" s="7" t="n"/>
+      <c r="AU108" s="7" t="n"/>
+      <c r="AV108" s="7" t="n"/>
+      <c r="AW108" s="7" t="n"/>
+      <c r="AX108" s="7" t="n"/>
+      <c r="AY108" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ108" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+        </is>
+      </c>
+      <c r="BA108" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB108" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC108" s="7" t="inlineStr">
+        <is>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING;LEGS DEPENDENT;SLING;STANDING;STANDING;BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+        </is>
+      </c>
+      <c r="BD108" s="7" t="inlineStr">
+        <is>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C62122;;C92604;C62166;C62166;;C62167;C62168;C90480</t>
+        </is>
+      </c>
+      <c r="BE108" s="7" t="n"/>
+      <c r="BF108" s="7" t="n"/>
+      <c r="BG108" s="7" t="n"/>
+      <c r="BH108" s="7" t="n"/>
+      <c r="BI108" s="7" t="n"/>
+      <c r="BJ108" s="7" t="n"/>
+      <c r="BK108" s="7" t="n"/>
+      <c r="BL108" s="7" t="n"/>
+      <c r="BM108" s="7" t="n"/>
+      <c r="BN108" s="7" t="inlineStr">
+        <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
       </c>
@@ -38659,36 +43611,12 @@
       <c r="U109" s="7" t="n"/>
       <c r="V109" s="7" t="n"/>
       <c r="W109" s="7" t="n"/>
-      <c r="X109" s="7" t="inlineStr">
-        <is>
-          <t>breaths/min</t>
-        </is>
-      </c>
-      <c r="Y109" s="7" t="inlineStr">
-        <is>
-          <t>C49674</t>
-        </is>
-      </c>
-      <c r="Z109" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA109" s="7" t="inlineStr">
-        <is>
-          <t>breaths/min</t>
-        </is>
-      </c>
-      <c r="AB109" s="7" t="inlineStr">
-        <is>
-          <t>C49674</t>
-        </is>
-      </c>
-      <c r="AC109" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X109" s="7" t="n"/>
+      <c r="Y109" s="7" t="n"/>
+      <c r="Z109" s="7" t="n"/>
+      <c r="AA109" s="7" t="n"/>
+      <c r="AB109" s="7" t="n"/>
+      <c r="AC109" s="7" t="n"/>
       <c r="AD109" s="7" t="n"/>
       <c r="AE109" s="7" t="n"/>
       <c r="AF109" s="7" t="n"/>
@@ -38696,12 +43624,64 @@
       <c r="AH109" s="7" t="n"/>
       <c r="AI109" s="7" t="n"/>
       <c r="AJ109" s="7" t="n"/>
-      <c r="AK109" s="7" t="inlineStr">
+      <c r="AK109" s="7" t="n"/>
+      <c r="AL109" s="7" t="inlineStr">
+        <is>
+          <t>breaths/min</t>
+        </is>
+      </c>
+      <c r="AM109" s="7" t="inlineStr">
+        <is>
+          <t>C49674</t>
+        </is>
+      </c>
+      <c r="AN109" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO109" s="7" t="n"/>
+      <c r="AP109" s="7" t="n"/>
+      <c r="AQ109" s="7" t="inlineStr">
+        <is>
+          <t>breaths/min</t>
+        </is>
+      </c>
+      <c r="AR109" s="7" t="inlineStr">
+        <is>
+          <t>C49674</t>
+        </is>
+      </c>
+      <c r="AS109" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT109" s="7" t="n"/>
+      <c r="AU109" s="7" t="n"/>
+      <c r="AV109" s="7" t="n"/>
+      <c r="AW109" s="7" t="n"/>
+      <c r="AX109" s="7" t="n"/>
+      <c r="AY109" s="7" t="n"/>
+      <c r="AZ109" s="7" t="n"/>
+      <c r="BA109" s="7" t="n"/>
+      <c r="BB109" s="7" t="n"/>
+      <c r="BC109" s="7" t="n"/>
+      <c r="BD109" s="7" t="n"/>
+      <c r="BE109" s="7" t="n"/>
+      <c r="BF109" s="7" t="n"/>
+      <c r="BG109" s="7" t="n"/>
+      <c r="BH109" s="7" t="n"/>
+      <c r="BI109" s="7" t="n"/>
+      <c r="BJ109" s="7" t="n"/>
+      <c r="BK109" s="7" t="n"/>
+      <c r="BL109" s="7" t="n"/>
+      <c r="BM109" s="7" t="inlineStr">
         <is>
           <t>9279-1</t>
         </is>
       </c>
-      <c r="AL109" s="7" t="inlineStr">
+      <c r="BN109" s="7" t="inlineStr">
         <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
@@ -38822,6 +43802,50 @@
       <c r="AJ110" s="7" t="n"/>
       <c r="AK110" s="7" t="n"/>
       <c r="AL110" s="7" t="n"/>
+      <c r="AM110" s="7" t="n"/>
+      <c r="AN110" s="7" t="n"/>
+      <c r="AO110" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP110" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ110" s="7" t="n"/>
+      <c r="AR110" s="7" t="n"/>
+      <c r="AS110" s="7" t="n"/>
+      <c r="AT110" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU110" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV110" s="7" t="n"/>
+      <c r="AW110" s="7" t="n"/>
+      <c r="AX110" s="7" t="n"/>
+      <c r="AY110" s="7" t="n"/>
+      <c r="AZ110" s="7" t="n"/>
+      <c r="BA110" s="7" t="n"/>
+      <c r="BB110" s="7" t="n"/>
+      <c r="BC110" s="7" t="n"/>
+      <c r="BD110" s="7" t="n"/>
+      <c r="BE110" s="7" t="n"/>
+      <c r="BF110" s="7" t="n"/>
+      <c r="BG110" s="7" t="n"/>
+      <c r="BH110" s="7" t="n"/>
+      <c r="BI110" s="7" t="n"/>
+      <c r="BJ110" s="7" t="n"/>
+      <c r="BK110" s="7" t="n"/>
+      <c r="BL110" s="7" t="n"/>
+      <c r="BM110" s="7" t="n"/>
+      <c r="BN110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
@@ -38938,6 +43962,50 @@
       <c r="AJ111" s="7" t="n"/>
       <c r="AK111" s="7" t="n"/>
       <c r="AL111" s="7" t="n"/>
+      <c r="AM111" s="7" t="n"/>
+      <c r="AN111" s="7" t="n"/>
+      <c r="AO111" s="7" t="inlineStr">
+        <is>
+          <t>%;RATIO</t>
+        </is>
+      </c>
+      <c r="AP111" s="7" t="inlineStr">
+        <is>
+          <t>C25613;C44256</t>
+        </is>
+      </c>
+      <c r="AQ111" s="7" t="n"/>
+      <c r="AR111" s="7" t="n"/>
+      <c r="AS111" s="7" t="n"/>
+      <c r="AT111" s="7" t="inlineStr">
+        <is>
+          <t>%;RATIO</t>
+        </is>
+      </c>
+      <c r="AU111" s="7" t="inlineStr">
+        <is>
+          <t>C25613;C44256</t>
+        </is>
+      </c>
+      <c r="AV111" s="7" t="n"/>
+      <c r="AW111" s="7" t="n"/>
+      <c r="AX111" s="7" t="n"/>
+      <c r="AY111" s="7" t="n"/>
+      <c r="AZ111" s="7" t="n"/>
+      <c r="BA111" s="7" t="n"/>
+      <c r="BB111" s="7" t="n"/>
+      <c r="BC111" s="7" t="n"/>
+      <c r="BD111" s="7" t="n"/>
+      <c r="BE111" s="7" t="n"/>
+      <c r="BF111" s="7" t="n"/>
+      <c r="BG111" s="7" t="n"/>
+      <c r="BH111" s="7" t="n"/>
+      <c r="BI111" s="7" t="n"/>
+      <c r="BJ111" s="7" t="n"/>
+      <c r="BK111" s="7" t="n"/>
+      <c r="BL111" s="7" t="n"/>
+      <c r="BM111" s="7" t="n"/>
+      <c r="BN111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -39050,6 +44118,34 @@
       <c r="AJ112" s="7" t="n"/>
       <c r="AK112" s="7" t="n"/>
       <c r="AL112" s="7" t="n"/>
+      <c r="AM112" s="7" t="n"/>
+      <c r="AN112" s="7" t="n"/>
+      <c r="AO112" s="7" t="n"/>
+      <c r="AP112" s="7" t="n"/>
+      <c r="AQ112" s="7" t="n"/>
+      <c r="AR112" s="7" t="n"/>
+      <c r="AS112" s="7" t="n"/>
+      <c r="AT112" s="7" t="n"/>
+      <c r="AU112" s="7" t="n"/>
+      <c r="AV112" s="7" t="n"/>
+      <c r="AW112" s="7" t="n"/>
+      <c r="AX112" s="7" t="n"/>
+      <c r="AY112" s="7" t="n"/>
+      <c r="AZ112" s="7" t="n"/>
+      <c r="BA112" s="7" t="n"/>
+      <c r="BB112" s="7" t="n"/>
+      <c r="BC112" s="7" t="n"/>
+      <c r="BD112" s="7" t="n"/>
+      <c r="BE112" s="7" t="n"/>
+      <c r="BF112" s="7" t="n"/>
+      <c r="BG112" s="7" t="n"/>
+      <c r="BH112" s="7" t="n"/>
+      <c r="BI112" s="7" t="n"/>
+      <c r="BJ112" s="7" t="n"/>
+      <c r="BK112" s="7" t="n"/>
+      <c r="BL112" s="7" t="n"/>
+      <c r="BM112" s="7" t="n"/>
+      <c r="BN112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -39162,6 +44258,34 @@
       <c r="AJ113" s="7" t="n"/>
       <c r="AK113" s="7" t="n"/>
       <c r="AL113" s="7" t="n"/>
+      <c r="AM113" s="7" t="n"/>
+      <c r="AN113" s="7" t="n"/>
+      <c r="AO113" s="7" t="n"/>
+      <c r="AP113" s="7" t="n"/>
+      <c r="AQ113" s="7" t="n"/>
+      <c r="AR113" s="7" t="n"/>
+      <c r="AS113" s="7" t="n"/>
+      <c r="AT113" s="7" t="n"/>
+      <c r="AU113" s="7" t="n"/>
+      <c r="AV113" s="7" t="n"/>
+      <c r="AW113" s="7" t="n"/>
+      <c r="AX113" s="7" t="n"/>
+      <c r="AY113" s="7" t="n"/>
+      <c r="AZ113" s="7" t="n"/>
+      <c r="BA113" s="7" t="n"/>
+      <c r="BB113" s="7" t="n"/>
+      <c r="BC113" s="7" t="n"/>
+      <c r="BD113" s="7" t="n"/>
+      <c r="BE113" s="7" t="n"/>
+      <c r="BF113" s="7" t="n"/>
+      <c r="BG113" s="7" t="n"/>
+      <c r="BH113" s="7" t="n"/>
+      <c r="BI113" s="7" t="n"/>
+      <c r="BJ113" s="7" t="n"/>
+      <c r="BK113" s="7" t="n"/>
+      <c r="BL113" s="7" t="n"/>
+      <c r="BM113" s="7" t="n"/>
+      <c r="BN113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
@@ -39278,6 +44402,50 @@
       <c r="AJ114" s="7" t="n"/>
       <c r="AK114" s="7" t="n"/>
       <c r="AL114" s="7" t="n"/>
+      <c r="AM114" s="7" t="n"/>
+      <c r="AN114" s="7" t="n"/>
+      <c r="AO114" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP114" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ114" s="7" t="n"/>
+      <c r="AR114" s="7" t="n"/>
+      <c r="AS114" s="7" t="n"/>
+      <c r="AT114" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU114" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV114" s="7" t="n"/>
+      <c r="AW114" s="7" t="n"/>
+      <c r="AX114" s="7" t="n"/>
+      <c r="AY114" s="7" t="n"/>
+      <c r="AZ114" s="7" t="n"/>
+      <c r="BA114" s="7" t="n"/>
+      <c r="BB114" s="7" t="n"/>
+      <c r="BC114" s="7" t="n"/>
+      <c r="BD114" s="7" t="n"/>
+      <c r="BE114" s="7" t="n"/>
+      <c r="BF114" s="7" t="n"/>
+      <c r="BG114" s="7" t="n"/>
+      <c r="BH114" s="7" t="n"/>
+      <c r="BI114" s="7" t="n"/>
+      <c r="BJ114" s="7" t="n"/>
+      <c r="BK114" s="7" t="n"/>
+      <c r="BL114" s="7" t="n"/>
+      <c r="BM114" s="7" t="n"/>
+      <c r="BN114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
@@ -39379,36 +44547,12 @@
       <c r="U115" s="7" t="n"/>
       <c r="V115" s="7" t="n"/>
       <c r="W115" s="7" t="n"/>
-      <c r="X115" s="7" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="Y115" s="7" t="inlineStr">
-        <is>
-          <t>C49670</t>
-        </is>
-      </c>
-      <c r="Z115" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
-      <c r="AA115" s="7" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="AB115" s="7" t="inlineStr">
-        <is>
-          <t>C49670</t>
-        </is>
-      </c>
-      <c r="AC115" s="7" t="inlineStr">
-        <is>
-          <t>VSRESU</t>
-        </is>
-      </c>
+      <c r="X115" s="7" t="n"/>
+      <c r="Y115" s="7" t="n"/>
+      <c r="Z115" s="7" t="n"/>
+      <c r="AA115" s="7" t="n"/>
+      <c r="AB115" s="7" t="n"/>
+      <c r="AC115" s="7" t="n"/>
       <c r="AD115" s="7" t="n"/>
       <c r="AE115" s="7" t="n"/>
       <c r="AF115" s="7" t="n"/>
@@ -39416,12 +44560,88 @@
       <c r="AH115" s="7" t="n"/>
       <c r="AI115" s="7" t="n"/>
       <c r="AJ115" s="7" t="n"/>
-      <c r="AK115" s="7" t="inlineStr">
+      <c r="AK115" s="7" t="n"/>
+      <c r="AL115" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AM115" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AN115" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AO115" s="7" t="n"/>
+      <c r="AP115" s="7" t="n"/>
+      <c r="AQ115" s="7" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="AR115" s="7" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
+      <c r="AS115" s="7" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="AT115" s="7" t="n"/>
+      <c r="AU115" s="7" t="n"/>
+      <c r="AV115" s="7" t="n"/>
+      <c r="AW115" s="7" t="n"/>
+      <c r="AX115" s="7" t="n"/>
+      <c r="AY115" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ115" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+        </is>
+      </c>
+      <c r="BA115" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB115" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC115" s="7" t="inlineStr">
+        <is>
+          <t>PRONE;SEMI-RECUMBENT;SITTING;STANDING;SUPINE</t>
+        </is>
+      </c>
+      <c r="BD115" s="7" t="inlineStr">
+        <is>
+          <t>C62165;C111310;C62122;C62166;C62167</t>
+        </is>
+      </c>
+      <c r="BE115" s="7" t="n"/>
+      <c r="BF115" s="7" t="n"/>
+      <c r="BG115" s="7" t="n"/>
+      <c r="BH115" s="7" t="n"/>
+      <c r="BI115" s="7" t="n"/>
+      <c r="BJ115" s="7" t="n"/>
+      <c r="BK115" s="7" t="n"/>
+      <c r="BL115" s="7" t="n"/>
+      <c r="BM115" s="7" t="inlineStr">
         <is>
           <t>8480-6</t>
         </is>
       </c>
-      <c r="AL115" s="7" t="inlineStr">
+      <c r="BN115" s="7" t="inlineStr">
         <is>
           <t>%; C; F; Hz; K; L; LB; MET; Pa; RATIO; Watt; beats/min; breaths/min; cm; cmHg; dL; ft; g; in; kcal/day; kg; kg/m2; m; m2; mm; mmHg; ms; oz; s</t>
         </is>
@@ -39540,12 +44760,80 @@
       <c r="AH116" s="7" t="n"/>
       <c r="AI116" s="7" t="n"/>
       <c r="AJ116" s="7" t="n"/>
-      <c r="AK116" s="7" t="inlineStr">
+      <c r="AK116" s="7" t="n"/>
+      <c r="AL116" s="7" t="n"/>
+      <c r="AM116" s="7" t="n"/>
+      <c r="AN116" s="7" t="n"/>
+      <c r="AO116" s="7" t="inlineStr">
+        <is>
+          <t>mmHg;cmHg</t>
+        </is>
+      </c>
+      <c r="AP116" s="7" t="inlineStr">
+        <is>
+          <t>C49670;C147129</t>
+        </is>
+      </c>
+      <c r="AQ116" s="7" t="n"/>
+      <c r="AR116" s="7" t="n"/>
+      <c r="AS116" s="7" t="n"/>
+      <c r="AT116" s="7" t="inlineStr">
+        <is>
+          <t>mmHg;cmHg</t>
+        </is>
+      </c>
+      <c r="AU116" s="7" t="inlineStr">
+        <is>
+          <t>C49670;C147129</t>
+        </is>
+      </c>
+      <c r="AV116" s="7" t="n"/>
+      <c r="AW116" s="7" t="n"/>
+      <c r="AX116" s="7" t="n"/>
+      <c r="AY116" s="7" t="inlineStr">
+        <is>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+        </is>
+      </c>
+      <c r="AZ116" s="7" t="inlineStr">
+        <is>
+          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+        </is>
+      </c>
+      <c r="BA116" s="7" t="inlineStr">
+        <is>
+          <t>LEFT;RIGHT</t>
+        </is>
+      </c>
+      <c r="BB116" s="7" t="inlineStr">
+        <is>
+          <t>C25229;C25228</t>
+        </is>
+      </c>
+      <c r="BC116" s="7" t="inlineStr">
+        <is>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING, LEGS DEPENDENT;SLING;STANDING;STANDING, BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+        </is>
+      </c>
+      <c r="BD116" s="7" t="inlineStr">
+        <is>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C150885;C92604;C62166;C174357;C62167;C62168;C90480</t>
+        </is>
+      </c>
+      <c r="BE116" s="7" t="n"/>
+      <c r="BF116" s="7" t="n"/>
+      <c r="BG116" s="7" t="n"/>
+      <c r="BH116" s="7" t="n"/>
+      <c r="BI116" s="7" t="n"/>
+      <c r="BJ116" s="7" t="n"/>
+      <c r="BK116" s="7" t="n"/>
+      <c r="BL116" s="7" t="n"/>
+      <c r="BM116" s="7" t="inlineStr">
         <is>
           <t>8480-6</t>
         </is>
       </c>
-      <c r="AL116" s="7" t="n"/>
+      <c r="BN116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
@@ -39662,6 +44950,50 @@
       <c r="AJ117" s="7" t="n"/>
       <c r="AK117" s="7" t="n"/>
       <c r="AL117" s="7" t="n"/>
+      <c r="AM117" s="7" t="n"/>
+      <c r="AN117" s="7" t="n"/>
+      <c r="AO117" s="7" t="inlineStr">
+        <is>
+          <t>L;dL</t>
+        </is>
+      </c>
+      <c r="AP117" s="7" t="inlineStr">
+        <is>
+          <t>C48505;C64697</t>
+        </is>
+      </c>
+      <c r="AQ117" s="7" t="n"/>
+      <c r="AR117" s="7" t="n"/>
+      <c r="AS117" s="7" t="n"/>
+      <c r="AT117" s="7" t="inlineStr">
+        <is>
+          <t>L;dL</t>
+        </is>
+      </c>
+      <c r="AU117" s="7" t="inlineStr">
+        <is>
+          <t>C48505;C64697</t>
+        </is>
+      </c>
+      <c r="AV117" s="7" t="n"/>
+      <c r="AW117" s="7" t="n"/>
+      <c r="AX117" s="7" t="n"/>
+      <c r="AY117" s="7" t="n"/>
+      <c r="AZ117" s="7" t="n"/>
+      <c r="BA117" s="7" t="n"/>
+      <c r="BB117" s="7" t="n"/>
+      <c r="BC117" s="7" t="n"/>
+      <c r="BD117" s="7" t="n"/>
+      <c r="BE117" s="7" t="n"/>
+      <c r="BF117" s="7" t="n"/>
+      <c r="BG117" s="7" t="n"/>
+      <c r="BH117" s="7" t="n"/>
+      <c r="BI117" s="7" t="n"/>
+      <c r="BJ117" s="7" t="n"/>
+      <c r="BK117" s="7" t="n"/>
+      <c r="BL117" s="7" t="n"/>
+      <c r="BM117" s="7" t="n"/>
+      <c r="BN117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -39772,12 +45104,56 @@
       <c r="AH118" s="7" t="n"/>
       <c r="AI118" s="7" t="n"/>
       <c r="AJ118" s="7" t="n"/>
-      <c r="AK118" s="7" t="inlineStr">
+      <c r="AK118" s="7" t="n"/>
+      <c r="AL118" s="7" t="n"/>
+      <c r="AM118" s="7" t="n"/>
+      <c r="AN118" s="7" t="n"/>
+      <c r="AO118" s="7" t="inlineStr">
+        <is>
+          <t>C;F;K</t>
+        </is>
+      </c>
+      <c r="AP118" s="7" t="inlineStr">
+        <is>
+          <t>C42559;C44277;C42537</t>
+        </is>
+      </c>
+      <c r="AQ118" s="7" t="n"/>
+      <c r="AR118" s="7" t="n"/>
+      <c r="AS118" s="7" t="n"/>
+      <c r="AT118" s="7" t="n"/>
+      <c r="AU118" s="7" t="n"/>
+      <c r="AV118" s="7" t="n"/>
+      <c r="AW118" s="7" t="n"/>
+      <c r="AX118" s="7" t="n"/>
+      <c r="AY118" s="7" t="inlineStr">
+        <is>
+          <t>AXILLA;EAR;FOREHEAD;ORAL CAVITY;RECTUM</t>
+        </is>
+      </c>
+      <c r="AZ118" s="7" t="inlineStr">
+        <is>
+          <t>C12674;C12394;C89803;C12421;C12390</t>
+        </is>
+      </c>
+      <c r="BA118" s="7" t="n"/>
+      <c r="BB118" s="7" t="n"/>
+      <c r="BC118" s="7" t="n"/>
+      <c r="BD118" s="7" t="n"/>
+      <c r="BE118" s="7" t="n"/>
+      <c r="BF118" s="7" t="n"/>
+      <c r="BG118" s="7" t="n"/>
+      <c r="BH118" s="7" t="n"/>
+      <c r="BI118" s="7" t="n"/>
+      <c r="BJ118" s="7" t="n"/>
+      <c r="BK118" s="7" t="n"/>
+      <c r="BL118" s="7" t="n"/>
+      <c r="BM118" s="7" t="inlineStr">
         <is>
           <t>8310-5</t>
         </is>
       </c>
-      <c r="AL118" s="7" t="n"/>
+      <c r="BN118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -39892,12 +45268,64 @@
       <c r="AH119" s="7" t="n"/>
       <c r="AI119" s="7" t="n"/>
       <c r="AJ119" s="7" t="n"/>
-      <c r="AK119" s="7" t="inlineStr">
+      <c r="AK119" s="7" t="n"/>
+      <c r="AL119" s="7" t="n"/>
+      <c r="AM119" s="7" t="n"/>
+      <c r="AN119" s="7" t="n"/>
+      <c r="AO119" s="7" t="inlineStr">
+        <is>
+          <t>C;F</t>
+        </is>
+      </c>
+      <c r="AP119" s="7" t="inlineStr">
+        <is>
+          <t>C42559;C44277</t>
+        </is>
+      </c>
+      <c r="AQ119" s="7" t="n"/>
+      <c r="AR119" s="7" t="n"/>
+      <c r="AS119" s="7" t="n"/>
+      <c r="AT119" s="7" t="inlineStr">
+        <is>
+          <t>C;F</t>
+        </is>
+      </c>
+      <c r="AU119" s="7" t="inlineStr">
+        <is>
+          <t>C42559;C44277</t>
+        </is>
+      </c>
+      <c r="AV119" s="7" t="n"/>
+      <c r="AW119" s="7" t="n"/>
+      <c r="AX119" s="7" t="n"/>
+      <c r="AY119" s="7" t="inlineStr">
+        <is>
+          <t>TYMPANIC MEMBRANE;NASOPHARYNX;ESOPHAGUS;PULMONARY ARTERY BRANCH;SUBLINGUAL REGION;RECTUM</t>
+        </is>
+      </c>
+      <c r="AZ119" s="7" t="inlineStr">
+        <is>
+          <t>C12502;C12423;C12389;C12774;C102349;C12390</t>
+        </is>
+      </c>
+      <c r="BA119" s="7" t="n"/>
+      <c r="BB119" s="7" t="n"/>
+      <c r="BC119" s="7" t="n"/>
+      <c r="BD119" s="7" t="n"/>
+      <c r="BE119" s="7" t="n"/>
+      <c r="BF119" s="7" t="n"/>
+      <c r="BG119" s="7" t="n"/>
+      <c r="BH119" s="7" t="n"/>
+      <c r="BI119" s="7" t="n"/>
+      <c r="BJ119" s="7" t="n"/>
+      <c r="BK119" s="7" t="n"/>
+      <c r="BL119" s="7" t="n"/>
+      <c r="BM119" s="7" t="inlineStr">
         <is>
           <t>8329-5</t>
         </is>
       </c>
-      <c r="AL119" s="7" t="n"/>
+      <c r="BN119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -40014,6 +45442,58 @@
       <c r="AJ120" s="7" t="n"/>
       <c r="AK120" s="7" t="n"/>
       <c r="AL120" s="7" t="n"/>
+      <c r="AM120" s="7" t="n"/>
+      <c r="AN120" s="7" t="n"/>
+      <c r="AO120" s="7" t="inlineStr">
+        <is>
+          <t>C;F</t>
+        </is>
+      </c>
+      <c r="AP120" s="7" t="inlineStr">
+        <is>
+          <t>C42559;C44277</t>
+        </is>
+      </c>
+      <c r="AQ120" s="7" t="n"/>
+      <c r="AR120" s="7" t="n"/>
+      <c r="AS120" s="7" t="n"/>
+      <c r="AT120" s="7" t="inlineStr">
+        <is>
+          <t>C;F</t>
+        </is>
+      </c>
+      <c r="AU120" s="7" t="inlineStr">
+        <is>
+          <t>C42559;C44277</t>
+        </is>
+      </c>
+      <c r="AV120" s="7" t="n"/>
+      <c r="AW120" s="7" t="n"/>
+      <c r="AX120" s="7" t="n"/>
+      <c r="AY120" s="7" t="inlineStr">
+        <is>
+          <t>RECTUM;AXILLA;EAR;FOREHEAD;SUBLINGUAL REGION</t>
+        </is>
+      </c>
+      <c r="AZ120" s="7" t="inlineStr">
+        <is>
+          <t>C12390;C12674;C12394;C89803;C102349</t>
+        </is>
+      </c>
+      <c r="BA120" s="7" t="n"/>
+      <c r="BB120" s="7" t="n"/>
+      <c r="BC120" s="7" t="n"/>
+      <c r="BD120" s="7" t="n"/>
+      <c r="BE120" s="7" t="n"/>
+      <c r="BF120" s="7" t="n"/>
+      <c r="BG120" s="7" t="n"/>
+      <c r="BH120" s="7" t="n"/>
+      <c r="BI120" s="7" t="n"/>
+      <c r="BJ120" s="7" t="n"/>
+      <c r="BK120" s="7" t="n"/>
+      <c r="BL120" s="7" t="n"/>
+      <c r="BM120" s="7" t="n"/>
+      <c r="BN120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
@@ -40130,6 +45610,50 @@
       <c r="AJ121" s="7" t="n"/>
       <c r="AK121" s="7" t="n"/>
       <c r="AL121" s="7" t="n"/>
+      <c r="AM121" s="7" t="n"/>
+      <c r="AN121" s="7" t="n"/>
+      <c r="AO121" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP121" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ121" s="7" t="n"/>
+      <c r="AR121" s="7" t="n"/>
+      <c r="AS121" s="7" t="n"/>
+      <c r="AT121" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU121" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV121" s="7" t="n"/>
+      <c r="AW121" s="7" t="n"/>
+      <c r="AX121" s="7" t="n"/>
+      <c r="AY121" s="7" t="n"/>
+      <c r="AZ121" s="7" t="n"/>
+      <c r="BA121" s="7" t="n"/>
+      <c r="BB121" s="7" t="n"/>
+      <c r="BC121" s="7" t="n"/>
+      <c r="BD121" s="7" t="n"/>
+      <c r="BE121" s="7" t="n"/>
+      <c r="BF121" s="7" t="n"/>
+      <c r="BG121" s="7" t="n"/>
+      <c r="BH121" s="7" t="n"/>
+      <c r="BI121" s="7" t="n"/>
+      <c r="BJ121" s="7" t="n"/>
+      <c r="BK121" s="7" t="n"/>
+      <c r="BL121" s="7" t="n"/>
+      <c r="BM121" s="7" t="n"/>
+      <c r="BN121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
@@ -40244,12 +45768,56 @@
       <c r="AH122" s="7" t="n"/>
       <c r="AI122" s="7" t="n"/>
       <c r="AJ122" s="7" t="n"/>
-      <c r="AK122" s="7" t="inlineStr">
+      <c r="AK122" s="7" t="n"/>
+      <c r="AL122" s="7" t="n"/>
+      <c r="AM122" s="7" t="n"/>
+      <c r="AN122" s="7" t="n"/>
+      <c r="AO122" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP122" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ122" s="7" t="n"/>
+      <c r="AR122" s="7" t="n"/>
+      <c r="AS122" s="7" t="n"/>
+      <c r="AT122" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU122" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV122" s="7" t="n"/>
+      <c r="AW122" s="7" t="n"/>
+      <c r="AX122" s="7" t="n"/>
+      <c r="AY122" s="7" t="n"/>
+      <c r="AZ122" s="7" t="n"/>
+      <c r="BA122" s="7" t="n"/>
+      <c r="BB122" s="7" t="n"/>
+      <c r="BC122" s="7" t="n"/>
+      <c r="BD122" s="7" t="n"/>
+      <c r="BE122" s="7" t="n"/>
+      <c r="BF122" s="7" t="n"/>
+      <c r="BG122" s="7" t="n"/>
+      <c r="BH122" s="7" t="n"/>
+      <c r="BI122" s="7" t="n"/>
+      <c r="BJ122" s="7" t="n"/>
+      <c r="BK122" s="7" t="n"/>
+      <c r="BL122" s="7" t="n"/>
+      <c r="BM122" s="7" t="inlineStr">
         <is>
           <t>8354-3</t>
         </is>
       </c>
-      <c r="AL122" s="7" t="n"/>
+      <c r="BN122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
@@ -40366,6 +45934,50 @@
       <c r="AJ123" s="7" t="n"/>
       <c r="AK123" s="7" t="n"/>
       <c r="AL123" s="7" t="n"/>
+      <c r="AM123" s="7" t="n"/>
+      <c r="AN123" s="7" t="n"/>
+      <c r="AO123" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP123" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ123" s="7" t="n"/>
+      <c r="AR123" s="7" t="n"/>
+      <c r="AS123" s="7" t="n"/>
+      <c r="AT123" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AU123" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AV123" s="7" t="n"/>
+      <c r="AW123" s="7" t="n"/>
+      <c r="AX123" s="7" t="n"/>
+      <c r="AY123" s="7" t="n"/>
+      <c r="AZ123" s="7" t="n"/>
+      <c r="BA123" s="7" t="n"/>
+      <c r="BB123" s="7" t="n"/>
+      <c r="BC123" s="7" t="n"/>
+      <c r="BD123" s="7" t="n"/>
+      <c r="BE123" s="7" t="n"/>
+      <c r="BF123" s="7" t="n"/>
+      <c r="BG123" s="7" t="n"/>
+      <c r="BH123" s="7" t="n"/>
+      <c r="BI123" s="7" t="n"/>
+      <c r="BJ123" s="7" t="n"/>
+      <c r="BK123" s="7" t="n"/>
+      <c r="BL123" s="7" t="n"/>
+      <c r="BM123" s="7" t="n"/>
+      <c r="BN123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
@@ -40482,6 +46094,50 @@
       <c r="AJ124" s="7" t="n"/>
       <c r="AK124" s="7" t="n"/>
       <c r="AL124" s="7" t="n"/>
+      <c r="AM124" s="7" t="n"/>
+      <c r="AN124" s="7" t="n"/>
+      <c r="AO124" s="7" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="AP124" s="7" t="inlineStr">
+        <is>
+          <t>C44256</t>
+        </is>
+      </c>
+      <c r="AQ124" s="7" t="n"/>
+      <c r="AR124" s="7" t="n"/>
+      <c r="AS124" s="7" t="n"/>
+      <c r="AT124" s="7" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="AU124" s="7" t="inlineStr">
+        <is>
+          <t>C44256</t>
+        </is>
+      </c>
+      <c r="AV124" s="7" t="n"/>
+      <c r="AW124" s="7" t="n"/>
+      <c r="AX124" s="7" t="n"/>
+      <c r="AY124" s="7" t="n"/>
+      <c r="AZ124" s="7" t="n"/>
+      <c r="BA124" s="7" t="n"/>
+      <c r="BB124" s="7" t="n"/>
+      <c r="BC124" s="7" t="n"/>
+      <c r="BD124" s="7" t="n"/>
+      <c r="BE124" s="7" t="n"/>
+      <c r="BF124" s="7" t="n"/>
+      <c r="BG124" s="7" t="n"/>
+      <c r="BH124" s="7" t="n"/>
+      <c r="BI124" s="7" t="n"/>
+      <c r="BJ124" s="7" t="n"/>
+      <c r="BK124" s="7" t="n"/>
+      <c r="BL124" s="7" t="n"/>
+      <c r="BM124" s="7" t="n"/>
+      <c r="BN124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
@@ -40598,6 +46254,50 @@
       <c r="AJ125" s="7" t="n"/>
       <c r="AK125" s="7" t="n"/>
       <c r="AL125" s="7" t="n"/>
+      <c r="AM125" s="7" t="n"/>
+      <c r="AN125" s="7" t="n"/>
+      <c r="AO125" s="7" t="inlineStr">
+        <is>
+          <t>cm;ft;in;m</t>
+        </is>
+      </c>
+      <c r="AP125" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C71253;C48500;C41139</t>
+        </is>
+      </c>
+      <c r="AQ125" s="7" t="n"/>
+      <c r="AR125" s="7" t="n"/>
+      <c r="AS125" s="7" t="n"/>
+      <c r="AT125" s="7" t="inlineStr">
+        <is>
+          <t>cm;ft;in;m</t>
+        </is>
+      </c>
+      <c r="AU125" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C71253;C48500;C41139</t>
+        </is>
+      </c>
+      <c r="AV125" s="7" t="n"/>
+      <c r="AW125" s="7" t="n"/>
+      <c r="AX125" s="7" t="n"/>
+      <c r="AY125" s="7" t="n"/>
+      <c r="AZ125" s="7" t="n"/>
+      <c r="BA125" s="7" t="n"/>
+      <c r="BB125" s="7" t="n"/>
+      <c r="BC125" s="7" t="n"/>
+      <c r="BD125" s="7" t="n"/>
+      <c r="BE125" s="7" t="n"/>
+      <c r="BF125" s="7" t="n"/>
+      <c r="BG125" s="7" t="n"/>
+      <c r="BH125" s="7" t="n"/>
+      <c r="BI125" s="7" t="n"/>
+      <c r="BJ125" s="7" t="n"/>
+      <c r="BK125" s="7" t="n"/>
+      <c r="BL125" s="7" t="n"/>
+      <c r="BM125" s="7" t="n"/>
+      <c r="BN125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -40712,12 +46412,48 @@
       <c r="AH126" s="7" t="n"/>
       <c r="AI126" s="7" t="n"/>
       <c r="AJ126" s="7" t="n"/>
-      <c r="AK126" s="7" t="inlineStr">
+      <c r="AK126" s="7" t="n"/>
+      <c r="AL126" s="7" t="n"/>
+      <c r="AM126" s="7" t="n"/>
+      <c r="AN126" s="7" t="n"/>
+      <c r="AO126" s="7" t="inlineStr">
+        <is>
+          <t>LB;g;kg</t>
+        </is>
+      </c>
+      <c r="AP126" s="7" t="inlineStr">
+        <is>
+          <t>C48531;C48155;C28252</t>
+        </is>
+      </c>
+      <c r="AQ126" s="7" t="n"/>
+      <c r="AR126" s="7" t="n"/>
+      <c r="AS126" s="7" t="n"/>
+      <c r="AT126" s="7" t="n"/>
+      <c r="AU126" s="7" t="n"/>
+      <c r="AV126" s="7" t="n"/>
+      <c r="AW126" s="7" t="n"/>
+      <c r="AX126" s="7" t="n"/>
+      <c r="AY126" s="7" t="n"/>
+      <c r="AZ126" s="7" t="n"/>
+      <c r="BA126" s="7" t="n"/>
+      <c r="BB126" s="7" t="n"/>
+      <c r="BC126" s="7" t="n"/>
+      <c r="BD126" s="7" t="n"/>
+      <c r="BE126" s="7" t="n"/>
+      <c r="BF126" s="7" t="n"/>
+      <c r="BG126" s="7" t="n"/>
+      <c r="BH126" s="7" t="n"/>
+      <c r="BI126" s="7" t="n"/>
+      <c r="BJ126" s="7" t="n"/>
+      <c r="BK126" s="7" t="n"/>
+      <c r="BL126" s="7" t="n"/>
+      <c r="BM126" s="7" t="inlineStr">
         <is>
           <t>29463-7</t>
         </is>
       </c>
-      <c r="AL126" s="7" t="n"/>
+      <c r="BN126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -40821,31 +46557,67 @@
       <c r="AA127" s="7" t="n"/>
       <c r="AB127" s="7" t="n"/>
       <c r="AC127" s="7" t="n"/>
-      <c r="AD127" s="7" t="inlineStr">
-        <is>
-          <t>WAIST</t>
-        </is>
-      </c>
-      <c r="AE127" s="7" t="inlineStr">
-        <is>
-          <t>C64192</t>
-        </is>
-      </c>
-      <c r="AF127" s="7" t="inlineStr">
-        <is>
-          <t>LOC</t>
-        </is>
-      </c>
+      <c r="AD127" s="7" t="n"/>
+      <c r="AE127" s="7" t="n"/>
+      <c r="AF127" s="7" t="n"/>
       <c r="AG127" s="7" t="n"/>
       <c r="AH127" s="7" t="n"/>
       <c r="AI127" s="7" t="n"/>
       <c r="AJ127" s="7" t="n"/>
-      <c r="AK127" s="7" t="inlineStr">
+      <c r="AK127" s="7" t="n"/>
+      <c r="AL127" s="7" t="n"/>
+      <c r="AM127" s="7" t="n"/>
+      <c r="AN127" s="7" t="n"/>
+      <c r="AO127" s="7" t="inlineStr">
+        <is>
+          <t>cm;in;mm</t>
+        </is>
+      </c>
+      <c r="AP127" s="7" t="inlineStr">
+        <is>
+          <t>C49668;C48500;C28251</t>
+        </is>
+      </c>
+      <c r="AQ127" s="7" t="n"/>
+      <c r="AR127" s="7" t="n"/>
+      <c r="AS127" s="7" t="n"/>
+      <c r="AT127" s="7" t="n"/>
+      <c r="AU127" s="7" t="n"/>
+      <c r="AV127" s="7" t="inlineStr">
+        <is>
+          <t>WAIST</t>
+        </is>
+      </c>
+      <c r="AW127" s="7" t="inlineStr">
+        <is>
+          <t>C64192</t>
+        </is>
+      </c>
+      <c r="AX127" s="7" t="inlineStr">
+        <is>
+          <t>LOC</t>
+        </is>
+      </c>
+      <c r="AY127" s="7" t="n"/>
+      <c r="AZ127" s="7" t="n"/>
+      <c r="BA127" s="7" t="n"/>
+      <c r="BB127" s="7" t="n"/>
+      <c r="BC127" s="7" t="n"/>
+      <c r="BD127" s="7" t="n"/>
+      <c r="BE127" s="7" t="n"/>
+      <c r="BF127" s="7" t="n"/>
+      <c r="BG127" s="7" t="n"/>
+      <c r="BH127" s="7" t="n"/>
+      <c r="BI127" s="7" t="n"/>
+      <c r="BJ127" s="7" t="n"/>
+      <c r="BK127" s="7" t="n"/>
+      <c r="BL127" s="7" t="n"/>
+      <c r="BM127" s="7" t="inlineStr">
         <is>
           <t>56115-9</t>
         </is>
       </c>
-      <c r="AL127" s="7" t="n"/>
+      <c r="BN127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
@@ -40956,12 +46728,40 @@
       <c r="AH128" s="7" t="n"/>
       <c r="AI128" s="7" t="n"/>
       <c r="AJ128" s="7" t="n"/>
-      <c r="AK128" s="7" t="inlineStr">
+      <c r="AK128" s="7" t="n"/>
+      <c r="AL128" s="7" t="n"/>
+      <c r="AM128" s="7" t="n"/>
+      <c r="AN128" s="7" t="n"/>
+      <c r="AO128" s="7" t="n"/>
+      <c r="AP128" s="7" t="n"/>
+      <c r="AQ128" s="7" t="n"/>
+      <c r="AR128" s="7" t="n"/>
+      <c r="AS128" s="7" t="n"/>
+      <c r="AT128" s="7" t="n"/>
+      <c r="AU128" s="7" t="n"/>
+      <c r="AV128" s="7" t="n"/>
+      <c r="AW128" s="7" t="n"/>
+      <c r="AX128" s="7" t="n"/>
+      <c r="AY128" s="7" t="n"/>
+      <c r="AZ128" s="7" t="n"/>
+      <c r="BA128" s="7" t="n"/>
+      <c r="BB128" s="7" t="n"/>
+      <c r="BC128" s="7" t="n"/>
+      <c r="BD128" s="7" t="n"/>
+      <c r="BE128" s="7" t="n"/>
+      <c r="BF128" s="7" t="n"/>
+      <c r="BG128" s="7" t="n"/>
+      <c r="BH128" s="7" t="n"/>
+      <c r="BI128" s="7" t="n"/>
+      <c r="BJ128" s="7" t="n"/>
+      <c r="BK128" s="7" t="n"/>
+      <c r="BL128" s="7" t="n"/>
+      <c r="BM128" s="7" t="inlineStr">
         <is>
           <t>8336-0</t>
         </is>
       </c>
-      <c r="AL128" s="7" t="n"/>
+      <c r="BN128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
@@ -41074,9 +46874,37 @@
       <c r="AJ129" s="7" t="n"/>
       <c r="AK129" s="7" t="n"/>
       <c r="AL129" s="7" t="n"/>
+      <c r="AM129" s="7" t="n"/>
+      <c r="AN129" s="7" t="n"/>
+      <c r="AO129" s="7" t="n"/>
+      <c r="AP129" s="7" t="n"/>
+      <c r="AQ129" s="7" t="n"/>
+      <c r="AR129" s="7" t="n"/>
+      <c r="AS129" s="7" t="n"/>
+      <c r="AT129" s="7" t="n"/>
+      <c r="AU129" s="7" t="n"/>
+      <c r="AV129" s="7" t="n"/>
+      <c r="AW129" s="7" t="n"/>
+      <c r="AX129" s="7" t="n"/>
+      <c r="AY129" s="7" t="n"/>
+      <c r="AZ129" s="7" t="n"/>
+      <c r="BA129" s="7" t="n"/>
+      <c r="BB129" s="7" t="n"/>
+      <c r="BC129" s="7" t="n"/>
+      <c r="BD129" s="7" t="n"/>
+      <c r="BE129" s="7" t="n"/>
+      <c r="BF129" s="7" t="n"/>
+      <c r="BG129" s="7" t="n"/>
+      <c r="BH129" s="7" t="n"/>
+      <c r="BI129" s="7" t="n"/>
+      <c r="BJ129" s="7" t="n"/>
+      <c r="BK129" s="7" t="n"/>
+      <c r="BL129" s="7" t="n"/>
+      <c r="BM129" s="7" t="n"/>
+      <c r="BN129" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL1"/>
+  <autoFilter ref="A1:BN1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sdtm-findings-graph/machine_actionable/Measurement_Findings.xlsx
+++ b/sdtm-findings-graph/machine_actionable/Measurement_Findings.xlsx
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-30 22:51</t>
+          <t>Generated: 2026-06-12 21:38</t>
         </is>
       </c>
     </row>
@@ -25852,7 +25852,7 @@
       <c r="R2" s="7" t="n"/>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T2" s="7" t="inlineStr">
@@ -26040,7 +26040,7 @@
       <c r="R3" s="7" t="n"/>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T3" s="7" t="inlineStr">
@@ -26070,20 +26070,24 @@
       <c r="AN3" s="7" t="n"/>
       <c r="AO3" s="7" t="inlineStr">
         <is>
-          <t>Kg;g;LB;oz</t>
+          <t>kg;g;LB;oz</t>
         </is>
       </c>
       <c r="AP3" s="7" t="inlineStr">
         <is>
-          <t>;C48155;C48531;C48519</t>
+          <t>C28252;C48155;C48531;C48519</t>
         </is>
       </c>
       <c r="AQ3" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR3" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR3" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS3" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -26208,7 +26212,7 @@
       <c r="R4" s="7" t="n"/>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T4" s="7" t="inlineStr">
@@ -26396,7 +26400,7 @@
       <c r="R5" s="7" t="n"/>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
@@ -26426,20 +26430,24 @@
       <c r="AN5" s="7" t="n"/>
       <c r="AO5" s="7" t="inlineStr">
         <is>
-          <t>Kg;g</t>
+          <t>kg;g</t>
         </is>
       </c>
       <c r="AP5" s="7" t="inlineStr">
         <is>
-          <t>;C48155</t>
+          <t>C28252;C48155</t>
         </is>
       </c>
       <c r="AQ5" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR5" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR5" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS5" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -26564,7 +26572,7 @@
       <c r="R6" s="7" t="n"/>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
@@ -26736,7 +26744,7 @@
       <c r="R7" s="7" t="n"/>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T7" s="7" t="inlineStr">
@@ -26888,7 +26896,7 @@
       <c r="R8" s="7" t="n"/>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
@@ -27040,7 +27048,7 @@
       <c r="R9" s="7" t="n"/>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T9" s="7" t="inlineStr">
@@ -27204,7 +27212,7 @@
       <c r="R10" s="7" t="n"/>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
@@ -27368,7 +27376,7 @@
       <c r="R11" s="7" t="n"/>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T11" s="7" t="inlineStr">
@@ -27532,7 +27540,7 @@
       <c r="R12" s="7" t="n"/>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
@@ -27696,7 +27704,7 @@
       <c r="R13" s="7" t="n"/>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
@@ -27860,7 +27868,7 @@
       <c r="R14" s="7" t="n"/>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
@@ -28024,7 +28032,7 @@
       <c r="R15" s="7" t="n"/>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T15" s="7" t="inlineStr">
@@ -28188,7 +28196,7 @@
       <c r="R16" s="7" t="n"/>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr">
@@ -28291,7 +28299,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Body Fat Percentage</t>
+          <t>Total Body Fat/Total Body Mass</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -28301,7 +28309,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Body Fat Percentage</t>
+          <t>Total Body Fat to Total Body Mass Ratio Measurement</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -28321,7 +28329,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Personal Attribute (C19332); Body Fat Percentage (C139218)</t>
+          <t>Personal Attribute (C19332); Total Body Fat to Total Body Mass Ratio Measurement (C139218)</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -28341,7 +28349,7 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>Body Fat Percentage</t>
+          <t>Total Body Fat/Total Body Mass</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -28352,7 +28360,7 @@
       <c r="R17" s="7" t="n"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
@@ -28520,7 +28528,7 @@
       <c r="R18" s="7" t="n"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
@@ -28696,7 +28704,7 @@
       <c r="R19" s="7" t="n"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T19" s="7" t="inlineStr">
@@ -28726,20 +28734,24 @@
       <c r="AN19" s="7" t="n"/>
       <c r="AO19" s="7" t="inlineStr">
         <is>
-          <t>Kg;g;LB;oz</t>
+          <t>kg;g;LB;oz</t>
         </is>
       </c>
       <c r="AP19" s="7" t="inlineStr">
         <is>
-          <t>;C48155;C48531;C48519</t>
+          <t>C28252;C48155;C48531;C48519</t>
         </is>
       </c>
       <c r="AQ19" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR19" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR19" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -28843,7 +28855,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Ordinal</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
@@ -28864,7 +28876,7 @@
       <c r="R20" s="7" t="n"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
@@ -29036,7 +29048,7 @@
       <c r="R21" s="7" t="n"/>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T21" s="7" t="inlineStr">
@@ -29204,7 +29216,7 @@
       <c r="R22" s="7" t="n"/>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T22" s="7" t="inlineStr">
@@ -29252,10 +29264,14 @@
       </c>
       <c r="AQ22" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR22" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR22" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -29380,7 +29396,7 @@
       <c r="R23" s="7" t="n"/>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr">
@@ -29428,10 +29444,14 @@
       </c>
       <c r="AQ23" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR23" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR23" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -29556,7 +29576,7 @@
       <c r="R24" s="7" t="n"/>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">
@@ -29604,10 +29624,14 @@
       </c>
       <c r="AQ24" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR24" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR24" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -29732,7 +29756,7 @@
       <c r="R25" s="7" t="n"/>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T25" s="7" t="inlineStr">
@@ -29780,10 +29804,14 @@
       </c>
       <c r="AQ25" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR25" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR25" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -29908,7 +29936,7 @@
       <c r="R26" s="7" t="n"/>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T26" s="7" t="inlineStr">
@@ -30068,7 +30096,7 @@
       <c r="R27" s="7" t="n"/>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T27" s="7" t="inlineStr">
@@ -30116,10 +30144,14 @@
       </c>
       <c r="AQ27" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR27" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR27" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS27" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -30244,7 +30276,7 @@
       <c r="R28" s="7" t="n"/>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T28" s="7" t="inlineStr">
@@ -30292,10 +30324,14 @@
       </c>
       <c r="AQ28" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR28" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR28" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS28" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -30420,7 +30456,7 @@
       <c r="R29" s="7" t="n"/>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T29" s="7" t="inlineStr">
@@ -30580,7 +30616,7 @@
       <c r="R30" s="7" t="n"/>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T30" s="7" t="inlineStr">
@@ -30610,20 +30646,24 @@
       <c r="AN30" s="7" t="n"/>
       <c r="AO30" s="7" t="inlineStr">
         <is>
-          <t>Kg;g;LB;oz</t>
+          <t>kg;g;LB;oz</t>
         </is>
       </c>
       <c r="AP30" s="7" t="inlineStr">
         <is>
-          <t>;C48155;C48531;C48519</t>
+          <t>C28252;C48155;C48531;C48519</t>
         </is>
       </c>
       <c r="AQ30" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR30" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR30" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS30" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -30748,7 +30788,7 @@
       <c r="R31" s="7" t="n"/>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T31" s="7" t="inlineStr">
@@ -30912,7 +30952,7 @@
       <c r="R32" s="7" t="n"/>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T32" s="7" t="inlineStr">
@@ -31076,7 +31116,7 @@
       <c r="R33" s="7" t="n"/>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T33" s="7" t="inlineStr">
@@ -31240,7 +31280,7 @@
       <c r="R34" s="7" t="n"/>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T34" s="7" t="inlineStr">
@@ -31404,7 +31444,7 @@
       <c r="R35" s="7" t="n"/>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T35" s="7" t="inlineStr">
@@ -31568,7 +31608,7 @@
       <c r="R36" s="7" t="n"/>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T36" s="7" t="inlineStr">
@@ -31732,7 +31772,7 @@
       <c r="R37" s="7" t="n"/>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T37" s="7" t="inlineStr">
@@ -31896,7 +31936,7 @@
       <c r="R38" s="7" t="n"/>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T38" s="7" t="inlineStr">
@@ -32060,7 +32100,7 @@
       <c r="R39" s="7" t="n"/>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T39" s="7" t="inlineStr">
@@ -32224,7 +32264,7 @@
       <c r="R40" s="7" t="n"/>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T40" s="7" t="inlineStr">
@@ -32237,12 +32277,12 @@
       <c r="W40" s="7" t="n"/>
       <c r="X40" s="7" t="inlineStr">
         <is>
-          <t>DYNAMOMETRY;PINCH DYNAMOMETRY</t>
+          <t>DYNAMOMETRY</t>
         </is>
       </c>
       <c r="Y40" s="7" t="inlineStr">
         <is>
-          <t>C161407;</t>
+          <t>C161407</t>
         </is>
       </c>
       <c r="Z40" s="7" t="n"/>
@@ -32272,10 +32312,14 @@
       </c>
       <c r="AQ40" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR40" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR40" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS40" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -32400,7 +32444,7 @@
       <c r="R41" s="7" t="n"/>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T41" s="7" t="inlineStr">
@@ -32576,7 +32620,7 @@
       <c r="R42" s="7" t="n"/>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T42" s="7" t="inlineStr">
@@ -32752,7 +32796,7 @@
       <c r="R43" s="7" t="n"/>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T43" s="7" t="inlineStr">
@@ -32928,7 +32972,7 @@
       <c r="R44" s="7" t="n"/>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T44" s="7" t="inlineStr">
@@ -33100,7 +33144,7 @@
       <c r="R45" s="7" t="n"/>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T45" s="7" t="inlineStr">
@@ -33296,7 +33340,7 @@
       <c r="R46" s="7" t="n"/>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T46" s="7" t="inlineStr">
@@ -33356,12 +33400,12 @@
       <c r="AX46" s="7" t="n"/>
       <c r="AY46" s="7" t="inlineStr">
         <is>
-          <t>INTERPHALANGEAL JOINT 1;PROXIMAL INTERPHALANGEAL JOINT 2 OF THE HAND;PROXIMAL INTERPHALANGEAL JOINT 3 OF THE HAND;PROXIMAL INTERPHALANGEAL;PROXIMAL INTERPHALANGEAL JOINT 5 OF THE HAND JOINT 4 OF THE HAND;METACARPOPHALANGEAL JOINT 1;METACARPOPHALANGEAL JOINT 2;METACARPOPHALANGEAL JOINT 4 METACARPOPHALANGEAL JOINT 3;METACARPOPHALANGEAL JOINT 4;METACARPOPHALANGEAL JOINT 5;CARPOMETACARPAL JOINTS 3-5;SCAPHOID-LUNATE-CAPITATE JOINT;RADIOCARPAL JOINT</t>
+          <t>INTERPHALANGEAL JOINT 1;PROXIMAL INTERPHALANGEAL JOINT 2 OF THE HAND;PROXIMAL INTERPHALANGEAL JOINT 3 OF THE HAND;PROXIMAL INTERPHALANGEAL JOINT 4 OF THE HAND;PROXIMAL INTERPHALANGEAL JOINT 5 OF THE HAND;METACARPOPHALANGEAL JOINT 1;METACARPOPHALANGEAL JOINT 2;METACARPOPHALANGEAL JOINT 3;METACARPOPHALANGEAL JOINT 4;METACARPOPHALANGEAL JOINT 5;CARPOMETACARPAL JOINT 3;CARPOMETACARPAL JOINT 4;CARPOMETACARPAL JOINT 5;SCAPHOID-LUNATE-CAPITATE JOINT;WRIST JOINT</t>
         </is>
       </c>
       <c r="AZ46" s="7" t="inlineStr">
         <is>
-          <t>C102301;C114194;C114195;;;C102316;C102317;;C102319;C102320;;C127677;</t>
+          <t>C102301;C114194;C114195;C114196;C114197;C102316;C102317;C102318;C102319;C102320;C103914;C103915;C103916;C127677;C33894</t>
         </is>
       </c>
       <c r="BA46" s="7" t="inlineStr">
@@ -33492,7 +33536,7 @@
       <c r="R47" s="7" t="n"/>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T47" s="7" t="inlineStr">
@@ -33522,20 +33566,24 @@
       <c r="AN47" s="7" t="n"/>
       <c r="AO47" s="7" t="inlineStr">
         <is>
-          <t>Kg;g;LB;oz</t>
+          <t>kg;g;LB;oz</t>
         </is>
       </c>
       <c r="AP47" s="7" t="inlineStr">
         <is>
-          <t>;C48155;C48531;C48519</t>
+          <t>C28252;C48155;C48531;C48519</t>
         </is>
       </c>
       <c r="AQ47" s="7" t="inlineStr">
         <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="AR47" s="7" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR47" s="7" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
       <c r="AS47" s="7" t="inlineStr">
         <is>
           <t>UNIT</t>
@@ -33660,7 +33708,7 @@
       <c r="R48" s="7" t="n"/>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T48" s="7" t="inlineStr">
@@ -33832,7 +33880,7 @@
       <c r="R49" s="7" t="n"/>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T49" s="7" t="inlineStr">
@@ -33983,7 +34031,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>Ordinal</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
@@ -34004,7 +34052,7 @@
       <c r="R50" s="7" t="n"/>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T50" s="7" t="inlineStr">
@@ -34151,7 +34199,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Ordinal</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
@@ -34172,7 +34220,7 @@
       <c r="R51" s="7" t="n"/>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T51" s="7" t="inlineStr">
@@ -34340,7 +34388,7 @@
       <c r="R52" s="7" t="n"/>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T52" s="7" t="inlineStr">
@@ -34488,7 +34536,7 @@
       <c r="R53" s="7" t="n"/>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T53" s="7" t="inlineStr">
@@ -34648,7 +34696,7 @@
       <c r="R54" s="7" t="n"/>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T54" s="7" t="inlineStr">
@@ -34812,7 +34860,7 @@
       <c r="R55" s="7" t="n"/>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T55" s="7" t="inlineStr">
@@ -34968,7 +35016,7 @@
       <c r="R56" s="7" t="n"/>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T56" s="7" t="inlineStr">
@@ -35108,7 +35156,7 @@
       <c r="R57" s="7" t="n"/>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T57" s="7" t="inlineStr">
@@ -35260,7 +35308,7 @@
       <c r="R58" s="7" t="n"/>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T58" s="7" t="inlineStr">
@@ -35404,7 +35452,7 @@
       <c r="R59" s="7" t="n"/>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T59" s="7" t="inlineStr">
@@ -35568,7 +35616,7 @@
       <c r="R60" s="7" t="n"/>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T60" s="7" t="inlineStr">
@@ -35728,7 +35776,7 @@
       <c r="R61" s="7" t="n"/>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T61" s="7" t="inlineStr">
@@ -35892,7 +35940,7 @@
       <c r="R62" s="7" t="n"/>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T62" s="7" t="inlineStr">
@@ -36056,7 +36104,7 @@
       <c r="R63" s="7" t="n"/>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T63" s="7" t="inlineStr">
@@ -36220,7 +36268,7 @@
       <c r="R64" s="7" t="n"/>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T64" s="7" t="inlineStr">
@@ -36380,7 +36428,7 @@
       <c r="R65" s="7" t="n"/>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T65" s="7" t="inlineStr">
@@ -36540,7 +36588,7 @@
       <c r="R66" s="7" t="n"/>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T66" s="7" t="inlineStr">
@@ -36704,7 +36752,7 @@
       <c r="R67" s="7" t="n"/>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T67" s="7" t="inlineStr">
@@ -36860,7 +36908,7 @@
       <c r="R68" s="7" t="n"/>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T68" s="7" t="inlineStr">
@@ -37000,7 +37048,7 @@
       <c r="R69" s="7" t="n"/>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T69" s="7" t="inlineStr">
@@ -37144,7 +37192,7 @@
       <c r="R70" s="7" t="n"/>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T70" s="7" t="inlineStr">
@@ -37208,12 +37256,12 @@
       <c r="AX70" s="7" t="n"/>
       <c r="AY70" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ70" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+          <t>C12681;C12687;C32478;C12715;C32608;C12838</t>
         </is>
       </c>
       <c r="BA70" s="7" t="inlineStr">
@@ -37344,7 +37392,7 @@
       <c r="R71" s="7" t="n"/>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T71" s="7" t="inlineStr">
@@ -37400,12 +37448,12 @@
       <c r="AX71" s="7" t="n"/>
       <c r="AY71" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ71" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+          <t>C12681;C12687;C32478;C12715;C32608;C12838</t>
         </is>
       </c>
       <c r="BA71" s="7" t="inlineStr">
@@ -37532,7 +37580,7 @@
       <c r="R72" s="7" t="n"/>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T72" s="7" t="inlineStr">
@@ -37692,7 +37740,7 @@
       <c r="R73" s="7" t="n"/>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T73" s="7" t="inlineStr">
@@ -37852,7 +37900,7 @@
       <c r="R74" s="7" t="n"/>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T74" s="7" t="inlineStr">
@@ -38012,7 +38060,7 @@
       <c r="R75" s="7" t="n"/>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T75" s="7" t="inlineStr">
@@ -38176,7 +38224,7 @@
       <c r="R76" s="7" t="n"/>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T76" s="7" t="inlineStr">
@@ -38336,7 +38384,7 @@
       <c r="R77" s="7" t="n"/>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T77" s="7" t="inlineStr">
@@ -38492,7 +38540,7 @@
       <c r="R78" s="7" t="n"/>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T78" s="7" t="inlineStr">
@@ -38644,7 +38692,7 @@
       <c r="R79" s="7" t="n"/>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T79" s="7" t="inlineStr">
@@ -38808,7 +38856,7 @@
       <c r="R80" s="7" t="n"/>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T80" s="7" t="inlineStr">
@@ -38878,7 +38926,7 @@
       <c r="BL80" s="7" t="n"/>
       <c r="BM80" s="7" t="inlineStr">
         <is>
-          <t>55283-6</t>
+          <t>11984-2</t>
         </is>
       </c>
       <c r="BN80" s="7" t="n"/>
@@ -38972,7 +39020,7 @@
       <c r="R81" s="7" t="n"/>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T81" s="7" t="inlineStr">
@@ -39136,7 +39184,7 @@
       <c r="R82" s="7" t="n"/>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T82" s="7" t="inlineStr">
@@ -39296,7 +39344,7 @@
       <c r="R83" s="7" t="n"/>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T83" s="7" t="inlineStr">
@@ -39456,7 +39504,7 @@
       <c r="R84" s="7" t="n"/>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T84" s="7" t="inlineStr">
@@ -39600,7 +39648,7 @@
       <c r="R85" s="7" t="n"/>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T85" s="7" t="inlineStr">
@@ -39744,7 +39792,7 @@
       <c r="R86" s="7" t="n"/>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T86" s="7" t="inlineStr">
@@ -39798,7 +39846,7 @@
       <c r="BL86" s="7" t="n"/>
       <c r="BM86" s="7" t="inlineStr">
         <is>
-          <t>Jan-89</t>
+          <t>8289-1</t>
         </is>
       </c>
       <c r="BN86" s="7" t="n"/>
@@ -39892,7 +39940,7 @@
       <c r="R87" s="7" t="n"/>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T87" s="7" t="inlineStr">
@@ -40056,7 +40104,7 @@
       <c r="R88" s="7" t="n"/>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T88" s="7" t="inlineStr">
@@ -40212,7 +40260,7 @@
       <c r="R89" s="7" t="n"/>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T89" s="7" t="inlineStr">
@@ -40372,7 +40420,7 @@
       <c r="R90" s="7" t="n"/>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T90" s="7" t="inlineStr">
@@ -40436,12 +40484,12 @@
       <c r="AX90" s="7" t="n"/>
       <c r="AY90" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ90" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+          <t>C12681;C12687;C12691;C32478;C12715;C12838</t>
         </is>
       </c>
       <c r="BA90" s="7" t="inlineStr">
@@ -40572,7 +40620,7 @@
       <c r="R91" s="7" t="n"/>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T91" s="7" t="inlineStr">
@@ -40732,7 +40780,7 @@
       <c r="R92" s="7" t="n"/>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T92" s="7" t="inlineStr">
@@ -40892,7 +40940,7 @@
       <c r="R93" s="7" t="n"/>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T93" s="7" t="inlineStr">
@@ -40956,12 +41004,12 @@
       <c r="AX93" s="7" t="n"/>
       <c r="AY93" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ93" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+          <t>C12681;C12687;C12691;C32478;C12715;C12838</t>
         </is>
       </c>
       <c r="BA93" s="7" t="inlineStr">
@@ -41088,7 +41136,7 @@
       <c r="R94" s="7" t="n"/>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T94" s="7" t="inlineStr">
@@ -41236,7 +41284,7 @@
       <c r="R95" s="7" t="n"/>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T95" s="7" t="inlineStr">
@@ -41400,7 +41448,7 @@
       <c r="R96" s="7" t="n"/>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T96" s="7" t="inlineStr">
@@ -41560,7 +41608,7 @@
       <c r="R97" s="7" t="n"/>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T97" s="7" t="inlineStr">
@@ -41663,7 +41711,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Lean Body Mass to Total Body Mass Ratio</t>
+          <t>Lean Body Mass/Total Body Mass</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -41673,7 +41721,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Lean Body Mass to Total Body Mass Ratio</t>
+          <t>Lean Body Mass to Total Body Mass Ratio Measurement</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -41693,7 +41741,7 @@
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>Personal Attribute (C19332); Lean Body Mass to Total Body Mass Ratio (C139219)</t>
+          <t>Personal Attribute (C19332); Lean Body Mass to Total Body Mass Ratio Measurement (C139219)</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -41713,7 +41761,7 @@
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
-          <t>Lean Body Mass to Total Body Mass Ratio</t>
+          <t>Lean Body Mass/Total Body Mass</t>
         </is>
       </c>
       <c r="Q98" s="7" t="inlineStr">
@@ -41724,7 +41772,7 @@
       <c r="R98" s="7" t="n"/>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T98" s="7" t="inlineStr">
@@ -41884,7 +41932,7 @@
       <c r="R99" s="7" t="n"/>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T99" s="7" t="inlineStr">
@@ -42040,7 +42088,7 @@
       <c r="R100" s="7" t="n"/>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T100" s="7" t="inlineStr">
@@ -42200,7 +42248,7 @@
       <c r="R101" s="7" t="n"/>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T101" s="7" t="inlineStr">
@@ -42360,7 +42408,7 @@
       <c r="R102" s="7" t="n"/>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T102" s="7" t="inlineStr">
@@ -42520,7 +42568,7 @@
       <c r="R103" s="7" t="n"/>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T103" s="7" t="inlineStr">
@@ -42680,7 +42728,7 @@
       <c r="R104" s="7" t="n"/>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T104" s="7" t="inlineStr">
@@ -42844,7 +42892,7 @@
       <c r="R105" s="7" t="n"/>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T105" s="7" t="inlineStr">
@@ -42886,22 +42934,22 @@
       <c r="AN105" s="7" t="n"/>
       <c r="AO105" s="7" t="inlineStr">
         <is>
-          <t>%;fraction of 1</t>
+          <t>%</t>
         </is>
       </c>
       <c r="AP105" s="7" t="inlineStr">
         <is>
-          <t>C25613;</t>
+          <t>C25613</t>
         </is>
       </c>
       <c r="AQ105" s="7" t="inlineStr">
         <is>
-          <t>fraction of 1</t>
+          <t>%</t>
         </is>
       </c>
       <c r="AR105" s="7" t="inlineStr">
         <is>
-          <t>C105484</t>
+          <t>C25613</t>
         </is>
       </c>
       <c r="AS105" s="7" t="inlineStr">
@@ -43036,7 +43084,7 @@
       <c r="R106" s="7" t="n"/>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T106" s="7" t="inlineStr">
@@ -43100,12 +43148,12 @@
       <c r="AX106" s="7" t="n"/>
       <c r="AY106" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ106" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+          <t>C12681;C12687;C12691;C32478;C12715;C12838</t>
         </is>
       </c>
       <c r="BA106" s="7" t="inlineStr">
@@ -43232,7 +43280,7 @@
       <c r="R107" s="7" t="n"/>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T107" s="7" t="inlineStr">
@@ -43292,12 +43340,12 @@
       <c r="BB107" s="7" t="n"/>
       <c r="BC107" s="7" t="inlineStr">
         <is>
-          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING;LEGS DEPENDENT;SLING;STANDING;STANDING;BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SLING;STANDING;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
         </is>
       </c>
       <c r="BD107" s="7" t="inlineStr">
         <is>
-          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C62122;;C92604;C62166;C62166;;C62167;C62168;C90480</t>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C92604;C62166;C62167;C62168;C90480</t>
         </is>
       </c>
       <c r="BE107" s="7" t="n"/>
@@ -43404,7 +43452,7 @@
       <c r="R108" s="7" t="n"/>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T108" s="7" t="inlineStr">
@@ -43468,12 +43516,12 @@
       <c r="AX108" s="7" t="n"/>
       <c r="AY108" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;CEREBRAL ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ108" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C12691;C32478;C12715;;C12838</t>
+          <t>C12681;C12687;C12691;C32478;C12715;C12838</t>
         </is>
       </c>
       <c r="BA108" s="7" t="inlineStr">
@@ -43488,12 +43536,12 @@
       </c>
       <c r="BC108" s="7" t="inlineStr">
         <is>
-          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SITTING;LEGS DEPENDENT;SLING;STANDING;STANDING;BENT FORWARD;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
+          <t>DECUBITUS;FOWLERS;LATERAL DECUBITUS;LEFT LATERAL DECUBITUS;PRONE;REVERSE TRENDELENBURG;RIGHT LATERAL DECUBITUS;SEMI-FOWLERS;SEMI-RECUMBENT;SITTING;SLING;STANDING;SUPINE;TRENDELENBURG;UNCONSTRAINED</t>
         </is>
       </c>
       <c r="BD108" s="7" t="inlineStr">
         <is>
-          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C62122;;C92604;C62166;C62166;;C62167;C62168;C90480</t>
+          <t>C77532;C62173;C100758;C62172;C62165;C62169;C62171;C62174;C111310;C62122;C92604;C62166;C62167;C62168;C90480</t>
         </is>
       </c>
       <c r="BE108" s="7" t="n"/>
@@ -43600,7 +43648,7 @@
       <c r="R109" s="7" t="n"/>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T109" s="7" t="inlineStr">
@@ -43776,7 +43824,7 @@
       <c r="R110" s="7" t="n"/>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T110" s="7" t="inlineStr">
@@ -43936,7 +43984,7 @@
       <c r="R111" s="7" t="n"/>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T111" s="7" t="inlineStr">
@@ -44092,7 +44140,7 @@
       <c r="R112" s="7" t="n"/>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T112" s="7" t="inlineStr">
@@ -44232,7 +44280,7 @@
       <c r="R113" s="7" t="n"/>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T113" s="7" t="inlineStr">
@@ -44376,7 +44424,7 @@
       <c r="R114" s="7" t="n"/>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T114" s="7" t="inlineStr">
@@ -44536,7 +44584,7 @@
       <c r="R115" s="7" t="n"/>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T115" s="7" t="inlineStr">
@@ -44600,12 +44648,12 @@
       <c r="AX115" s="7" t="n"/>
       <c r="AY115" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ115" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+          <t>C12681;C12687;C32478;C12715;C32608;C12838</t>
         </is>
       </c>
       <c r="BA115" s="7" t="inlineStr">
@@ -44736,7 +44784,7 @@
       <c r="R116" s="7" t="n"/>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T116" s="7" t="inlineStr">
@@ -44792,12 +44840,12 @@
       <c r="AX116" s="7" t="n"/>
       <c r="AY116" s="7" t="inlineStr">
         <is>
-          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;PERIPHERAL ARTERY;RADIAL ARTERY</t>
+          <t>BRACHIAL ARTERY;CAROTID ARTERY;DORSALIS PEDIS ARTERY;FEMORAL ARTERY;FINGER;RADIAL ARTERY</t>
         </is>
       </c>
       <c r="AZ116" s="7" t="inlineStr">
         <is>
-          <t>C12681;C12687;C32478;C12715;C32608;;C12838</t>
+          <t>C12681;C12687;C32478;C12715;C32608;C12838</t>
         </is>
       </c>
       <c r="BA116" s="7" t="inlineStr">
@@ -44924,7 +44972,7 @@
       <c r="R117" s="7" t="n"/>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T117" s="7" t="inlineStr">
@@ -45080,7 +45128,7 @@
       <c r="R118" s="7" t="n"/>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T118" s="7" t="inlineStr">
@@ -45244,7 +45292,7 @@
       <c r="R119" s="7" t="n"/>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T119" s="7" t="inlineStr">
@@ -45416,7 +45464,7 @@
       <c r="R120" s="7" t="n"/>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T120" s="7" t="inlineStr">
@@ -45584,7 +45632,7 @@
       <c r="R121" s="7" t="n"/>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T121" s="7" t="inlineStr">
@@ -45744,7 +45792,7 @@
       <c r="R122" s="7" t="n"/>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T122" s="7" t="inlineStr">
@@ -45908,7 +45956,7 @@
       <c r="R123" s="7" t="n"/>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T123" s="7" t="inlineStr">
@@ -46068,7 +46116,7 @@
       <c r="R124" s="7" t="n"/>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T124" s="7" t="inlineStr">
@@ -46228,7 +46276,7 @@
       <c r="R125" s="7" t="n"/>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T125" s="7" t="inlineStr">
@@ -46388,7 +46436,7 @@
       <c r="R126" s="7" t="n"/>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T126" s="7" t="inlineStr">
@@ -46540,7 +46588,7 @@
       <c r="R127" s="7" t="n"/>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T127" s="7" t="inlineStr">
@@ -46704,7 +46752,7 @@
       <c r="R128" s="7" t="n"/>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T128" s="7" t="inlineStr">
@@ -46848,7 +46896,7 @@
       <c r="R129" s="7" t="n"/>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="T129" s="7" t="inlineStr">

--- a/sdtm-findings-graph/machine_actionable/Measurement_Findings.xlsx
+++ b/sdtm-findings-graph/machine_actionable/Measurement_Findings.xlsx
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-12 21:38</t>
+          <t>Generated: 2026-08-23 19:06</t>
         </is>
       </c>
     </row>
